--- a/app/Excel/ATA-F-HD-005-Couse Outline.xlsx
+++ b/app/Excel/ATA-F-HD-005-Couse Outline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aisingroupap01.sharepoint.com/sites/AT-A_HRD/Shared Documents/เอกสารWI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trainee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{3D123890-6E7E-4930-81B4-4F6C091AC983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD75DCDF-8F61-4D61-BDCD-CB113A1EA5AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECE0244-6E60-4F48-B5C2-A8934D305137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{BC99A250-FEBB-43EA-840D-941C3158CE7C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{BC99A250-FEBB-43EA-840D-941C3158CE7C}"/>
   </bookViews>
   <sheets>
     <sheet name="ฟอร์มTH" sheetId="1" r:id="rId1"/>
@@ -81,6 +81,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -179,15 +182,15 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="[$-107041E]d\ mmmm\ yyyy;@"/>
+    <numFmt numFmtId="187" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="188" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="189" formatCode="[$-107041E]d\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -226,12 +229,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="16"/>
-      <name val="Cordia New"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="18"/>
       <name val="Cordia New"/>
       <family val="2"/>
@@ -245,7 +242,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <charset val="222"/>
       <scheme val="minor"/>
@@ -651,9 +648,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -674,14 +671,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="187" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -709,25 +706,19 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -736,13 +727,19 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -751,31 +748,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
@@ -794,37 +775,25 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="188" fontId="5" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1"/>
@@ -843,7 +812,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="189" fontId="5" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -856,13 +825,41 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma 2" xfId="4" xr:uid="{6DF0FABA-4126-411C-A835-D05B76F8B823}"/>
@@ -1107,7 +1104,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="68580" y="76200"/>
-          <a:ext cx="2301240" cy="579120"/>
+          <a:ext cx="2514600" cy="579120"/>
           <a:chOff x="600075" y="314325"/>
           <a:chExt cx="2233216" cy="438799"/>
         </a:xfrm>
@@ -1217,7 +1214,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="60960" y="76200"/>
-          <a:ext cx="2301240" cy="579120"/>
+          <a:ext cx="2514600" cy="579120"/>
           <a:chOff x="600075" y="314325"/>
           <a:chExt cx="2233216" cy="438799"/>
         </a:xfrm>
@@ -1847,1192 +1844,1192 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA62"/>
-  <sheetFormatPr defaultRowHeight="24.6"/>
+  <sheetFormatPr defaultRowHeight="24.6" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="2.296875" style="4" customWidth="1"/>
     <col min="2" max="2" width="4" style="4" customWidth="1"/>
-    <col min="3" max="4" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5" max="6" width="8.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="4" customWidth="1"/>
+    <col min="3" max="4" width="6.796875" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="6.796875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="4.69921875" style="4" customWidth="1"/>
     <col min="10" max="10" width="5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="4" customWidth="1"/>
-    <col min="12" max="14" width="15.77734375" style="4" customWidth="1"/>
-    <col min="15" max="15" width="2.33203125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.296875" style="4" customWidth="1"/>
+    <col min="12" max="14" width="15.796875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="2.296875" style="4" customWidth="1"/>
     <col min="16" max="16" width="9" style="4"/>
-    <col min="17" max="17" width="11.6640625" style="4" customWidth="1"/>
-    <col min="18" max="18" width="2.33203125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.69921875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="2.296875" style="4" customWidth="1"/>
+    <col min="19" max="19" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="20" max="189" width="9" style="4"/>
-    <col min="190" max="190" width="2.77734375" style="4" customWidth="1"/>
-    <col min="191" max="191" width="17.33203125" style="4" customWidth="1"/>
-    <col min="192" max="192" width="6.77734375" style="4" customWidth="1"/>
-    <col min="193" max="193" width="5.33203125" style="4" customWidth="1"/>
-    <col min="194" max="195" width="6.33203125" style="4" customWidth="1"/>
-    <col min="196" max="197" width="4.33203125" style="4" customWidth="1"/>
-    <col min="198" max="198" width="3.88671875" style="4" customWidth="1"/>
+    <col min="190" max="190" width="2.796875" style="4" customWidth="1"/>
+    <col min="191" max="191" width="17.296875" style="4" customWidth="1"/>
+    <col min="192" max="192" width="6.796875" style="4" customWidth="1"/>
+    <col min="193" max="193" width="5.296875" style="4" customWidth="1"/>
+    <col min="194" max="195" width="6.296875" style="4" customWidth="1"/>
+    <col min="196" max="197" width="4.296875" style="4" customWidth="1"/>
+    <col min="198" max="198" width="3.8984375" style="4" customWidth="1"/>
     <col min="199" max="199" width="3" style="4" customWidth="1"/>
-    <col min="200" max="200" width="3.21875" style="4" customWidth="1"/>
+    <col min="200" max="200" width="3.19921875" style="4" customWidth="1"/>
     <col min="201" max="201" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="202" max="202" width="6.77734375" style="4" customWidth="1"/>
+    <col min="202" max="202" width="6.796875" style="4" customWidth="1"/>
     <col min="203" max="205" width="9" style="4"/>
-    <col min="206" max="206" width="11.6640625" style="4" customWidth="1"/>
+    <col min="206" max="206" width="11.69921875" style="4" customWidth="1"/>
     <col min="207" max="207" width="7" style="4" customWidth="1"/>
     <col min="208" max="208" width="9" style="4"/>
-    <col min="209" max="209" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="209" max="209" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="210" max="445" width="9" style="4"/>
-    <col min="446" max="446" width="2.77734375" style="4" customWidth="1"/>
-    <col min="447" max="447" width="17.33203125" style="4" customWidth="1"/>
-    <col min="448" max="448" width="6.77734375" style="4" customWidth="1"/>
-    <col min="449" max="449" width="5.33203125" style="4" customWidth="1"/>
-    <col min="450" max="451" width="6.33203125" style="4" customWidth="1"/>
-    <col min="452" max="453" width="4.33203125" style="4" customWidth="1"/>
-    <col min="454" max="454" width="3.88671875" style="4" customWidth="1"/>
+    <col min="446" max="446" width="2.796875" style="4" customWidth="1"/>
+    <col min="447" max="447" width="17.296875" style="4" customWidth="1"/>
+    <col min="448" max="448" width="6.796875" style="4" customWidth="1"/>
+    <col min="449" max="449" width="5.296875" style="4" customWidth="1"/>
+    <col min="450" max="451" width="6.296875" style="4" customWidth="1"/>
+    <col min="452" max="453" width="4.296875" style="4" customWidth="1"/>
+    <col min="454" max="454" width="3.8984375" style="4" customWidth="1"/>
     <col min="455" max="455" width="3" style="4" customWidth="1"/>
-    <col min="456" max="456" width="3.21875" style="4" customWidth="1"/>
+    <col min="456" max="456" width="3.19921875" style="4" customWidth="1"/>
     <col min="457" max="457" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="458" max="458" width="6.77734375" style="4" customWidth="1"/>
+    <col min="458" max="458" width="6.796875" style="4" customWidth="1"/>
     <col min="459" max="461" width="9" style="4"/>
-    <col min="462" max="462" width="11.6640625" style="4" customWidth="1"/>
+    <col min="462" max="462" width="11.69921875" style="4" customWidth="1"/>
     <col min="463" max="463" width="7" style="4" customWidth="1"/>
     <col min="464" max="464" width="9" style="4"/>
-    <col min="465" max="465" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="465" max="465" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="466" max="701" width="9" style="4"/>
-    <col min="702" max="702" width="2.77734375" style="4" customWidth="1"/>
-    <col min="703" max="703" width="17.33203125" style="4" customWidth="1"/>
-    <col min="704" max="704" width="6.77734375" style="4" customWidth="1"/>
-    <col min="705" max="705" width="5.33203125" style="4" customWidth="1"/>
-    <col min="706" max="707" width="6.33203125" style="4" customWidth="1"/>
-    <col min="708" max="709" width="4.33203125" style="4" customWidth="1"/>
-    <col min="710" max="710" width="3.88671875" style="4" customWidth="1"/>
+    <col min="702" max="702" width="2.796875" style="4" customWidth="1"/>
+    <col min="703" max="703" width="17.296875" style="4" customWidth="1"/>
+    <col min="704" max="704" width="6.796875" style="4" customWidth="1"/>
+    <col min="705" max="705" width="5.296875" style="4" customWidth="1"/>
+    <col min="706" max="707" width="6.296875" style="4" customWidth="1"/>
+    <col min="708" max="709" width="4.296875" style="4" customWidth="1"/>
+    <col min="710" max="710" width="3.8984375" style="4" customWidth="1"/>
     <col min="711" max="711" width="3" style="4" customWidth="1"/>
-    <col min="712" max="712" width="3.21875" style="4" customWidth="1"/>
+    <col min="712" max="712" width="3.19921875" style="4" customWidth="1"/>
     <col min="713" max="713" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="714" max="714" width="6.77734375" style="4" customWidth="1"/>
+    <col min="714" max="714" width="6.796875" style="4" customWidth="1"/>
     <col min="715" max="717" width="9" style="4"/>
-    <col min="718" max="718" width="11.6640625" style="4" customWidth="1"/>
+    <col min="718" max="718" width="11.69921875" style="4" customWidth="1"/>
     <col min="719" max="719" width="7" style="4" customWidth="1"/>
     <col min="720" max="720" width="9" style="4"/>
-    <col min="721" max="721" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="721" max="721" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="722" max="957" width="9" style="4"/>
-    <col min="958" max="958" width="2.77734375" style="4" customWidth="1"/>
-    <col min="959" max="959" width="17.33203125" style="4" customWidth="1"/>
-    <col min="960" max="960" width="6.77734375" style="4" customWidth="1"/>
-    <col min="961" max="961" width="5.33203125" style="4" customWidth="1"/>
-    <col min="962" max="963" width="6.33203125" style="4" customWidth="1"/>
-    <col min="964" max="965" width="4.33203125" style="4" customWidth="1"/>
-    <col min="966" max="966" width="3.88671875" style="4" customWidth="1"/>
+    <col min="958" max="958" width="2.796875" style="4" customWidth="1"/>
+    <col min="959" max="959" width="17.296875" style="4" customWidth="1"/>
+    <col min="960" max="960" width="6.796875" style="4" customWidth="1"/>
+    <col min="961" max="961" width="5.296875" style="4" customWidth="1"/>
+    <col min="962" max="963" width="6.296875" style="4" customWidth="1"/>
+    <col min="964" max="965" width="4.296875" style="4" customWidth="1"/>
+    <col min="966" max="966" width="3.8984375" style="4" customWidth="1"/>
     <col min="967" max="967" width="3" style="4" customWidth="1"/>
-    <col min="968" max="968" width="3.21875" style="4" customWidth="1"/>
+    <col min="968" max="968" width="3.19921875" style="4" customWidth="1"/>
     <col min="969" max="969" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="970" max="970" width="6.77734375" style="4" customWidth="1"/>
+    <col min="970" max="970" width="6.796875" style="4" customWidth="1"/>
     <col min="971" max="973" width="9" style="4"/>
-    <col min="974" max="974" width="11.6640625" style="4" customWidth="1"/>
+    <col min="974" max="974" width="11.69921875" style="4" customWidth="1"/>
     <col min="975" max="975" width="7" style="4" customWidth="1"/>
     <col min="976" max="976" width="9" style="4"/>
-    <col min="977" max="977" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="977" max="977" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="978" max="1213" width="9" style="4"/>
-    <col min="1214" max="1214" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1215" max="1215" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1216" max="1216" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1217" max="1217" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1218" max="1219" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1220" max="1221" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1222" max="1222" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1214" max="1214" width="2.796875" style="4" customWidth="1"/>
+    <col min="1215" max="1215" width="17.296875" style="4" customWidth="1"/>
+    <col min="1216" max="1216" width="6.796875" style="4" customWidth="1"/>
+    <col min="1217" max="1217" width="5.296875" style="4" customWidth="1"/>
+    <col min="1218" max="1219" width="6.296875" style="4" customWidth="1"/>
+    <col min="1220" max="1221" width="4.296875" style="4" customWidth="1"/>
+    <col min="1222" max="1222" width="3.8984375" style="4" customWidth="1"/>
     <col min="1223" max="1223" width="3" style="4" customWidth="1"/>
-    <col min="1224" max="1224" width="3.21875" style="4" customWidth="1"/>
+    <col min="1224" max="1224" width="3.19921875" style="4" customWidth="1"/>
     <col min="1225" max="1225" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1226" max="1226" width="6.77734375" style="4" customWidth="1"/>
+    <col min="1226" max="1226" width="6.796875" style="4" customWidth="1"/>
     <col min="1227" max="1229" width="9" style="4"/>
-    <col min="1230" max="1230" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1230" max="1230" width="11.69921875" style="4" customWidth="1"/>
     <col min="1231" max="1231" width="7" style="4" customWidth="1"/>
     <col min="1232" max="1232" width="9" style="4"/>
-    <col min="1233" max="1233" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1233" max="1233" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="1234" max="1469" width="9" style="4"/>
-    <col min="1470" max="1470" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1471" max="1471" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1472" max="1472" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1473" max="1473" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1474" max="1475" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1476" max="1477" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1478" max="1478" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1470" max="1470" width="2.796875" style="4" customWidth="1"/>
+    <col min="1471" max="1471" width="17.296875" style="4" customWidth="1"/>
+    <col min="1472" max="1472" width="6.796875" style="4" customWidth="1"/>
+    <col min="1473" max="1473" width="5.296875" style="4" customWidth="1"/>
+    <col min="1474" max="1475" width="6.296875" style="4" customWidth="1"/>
+    <col min="1476" max="1477" width="4.296875" style="4" customWidth="1"/>
+    <col min="1478" max="1478" width="3.8984375" style="4" customWidth="1"/>
     <col min="1479" max="1479" width="3" style="4" customWidth="1"/>
-    <col min="1480" max="1480" width="3.21875" style="4" customWidth="1"/>
+    <col min="1480" max="1480" width="3.19921875" style="4" customWidth="1"/>
     <col min="1481" max="1481" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1482" max="1482" width="6.77734375" style="4" customWidth="1"/>
+    <col min="1482" max="1482" width="6.796875" style="4" customWidth="1"/>
     <col min="1483" max="1485" width="9" style="4"/>
-    <col min="1486" max="1486" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1486" max="1486" width="11.69921875" style="4" customWidth="1"/>
     <col min="1487" max="1487" width="7" style="4" customWidth="1"/>
     <col min="1488" max="1488" width="9" style="4"/>
-    <col min="1489" max="1489" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1489" max="1489" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="1490" max="1725" width="9" style="4"/>
-    <col min="1726" max="1726" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1727" max="1727" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1728" max="1728" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1729" max="1729" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1730" max="1731" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1732" max="1733" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1734" max="1734" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1726" max="1726" width="2.796875" style="4" customWidth="1"/>
+    <col min="1727" max="1727" width="17.296875" style="4" customWidth="1"/>
+    <col min="1728" max="1728" width="6.796875" style="4" customWidth="1"/>
+    <col min="1729" max="1729" width="5.296875" style="4" customWidth="1"/>
+    <col min="1730" max="1731" width="6.296875" style="4" customWidth="1"/>
+    <col min="1732" max="1733" width="4.296875" style="4" customWidth="1"/>
+    <col min="1734" max="1734" width="3.8984375" style="4" customWidth="1"/>
     <col min="1735" max="1735" width="3" style="4" customWidth="1"/>
-    <col min="1736" max="1736" width="3.21875" style="4" customWidth="1"/>
+    <col min="1736" max="1736" width="3.19921875" style="4" customWidth="1"/>
     <col min="1737" max="1737" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1738" max="1738" width="6.77734375" style="4" customWidth="1"/>
+    <col min="1738" max="1738" width="6.796875" style="4" customWidth="1"/>
     <col min="1739" max="1741" width="9" style="4"/>
-    <col min="1742" max="1742" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1742" max="1742" width="11.69921875" style="4" customWidth="1"/>
     <col min="1743" max="1743" width="7" style="4" customWidth="1"/>
     <col min="1744" max="1744" width="9" style="4"/>
-    <col min="1745" max="1745" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1745" max="1745" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="1746" max="1981" width="9" style="4"/>
-    <col min="1982" max="1982" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1983" max="1983" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1984" max="1984" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1985" max="1985" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1986" max="1987" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1988" max="1989" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1990" max="1990" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1982" max="1982" width="2.796875" style="4" customWidth="1"/>
+    <col min="1983" max="1983" width="17.296875" style="4" customWidth="1"/>
+    <col min="1984" max="1984" width="6.796875" style="4" customWidth="1"/>
+    <col min="1985" max="1985" width="5.296875" style="4" customWidth="1"/>
+    <col min="1986" max="1987" width="6.296875" style="4" customWidth="1"/>
+    <col min="1988" max="1989" width="4.296875" style="4" customWidth="1"/>
+    <col min="1990" max="1990" width="3.8984375" style="4" customWidth="1"/>
     <col min="1991" max="1991" width="3" style="4" customWidth="1"/>
-    <col min="1992" max="1992" width="3.21875" style="4" customWidth="1"/>
+    <col min="1992" max="1992" width="3.19921875" style="4" customWidth="1"/>
     <col min="1993" max="1993" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1994" max="1994" width="6.77734375" style="4" customWidth="1"/>
+    <col min="1994" max="1994" width="6.796875" style="4" customWidth="1"/>
     <col min="1995" max="1997" width="9" style="4"/>
-    <col min="1998" max="1998" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1998" max="1998" width="11.69921875" style="4" customWidth="1"/>
     <col min="1999" max="1999" width="7" style="4" customWidth="1"/>
     <col min="2000" max="2000" width="9" style="4"/>
-    <col min="2001" max="2001" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2001" max="2001" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="2002" max="2237" width="9" style="4"/>
-    <col min="2238" max="2238" width="2.77734375" style="4" customWidth="1"/>
-    <col min="2239" max="2239" width="17.33203125" style="4" customWidth="1"/>
-    <col min="2240" max="2240" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2241" max="2241" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2242" max="2243" width="6.33203125" style="4" customWidth="1"/>
-    <col min="2244" max="2245" width="4.33203125" style="4" customWidth="1"/>
-    <col min="2246" max="2246" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2238" max="2238" width="2.796875" style="4" customWidth="1"/>
+    <col min="2239" max="2239" width="17.296875" style="4" customWidth="1"/>
+    <col min="2240" max="2240" width="6.796875" style="4" customWidth="1"/>
+    <col min="2241" max="2241" width="5.296875" style="4" customWidth="1"/>
+    <col min="2242" max="2243" width="6.296875" style="4" customWidth="1"/>
+    <col min="2244" max="2245" width="4.296875" style="4" customWidth="1"/>
+    <col min="2246" max="2246" width="3.8984375" style="4" customWidth="1"/>
     <col min="2247" max="2247" width="3" style="4" customWidth="1"/>
-    <col min="2248" max="2248" width="3.21875" style="4" customWidth="1"/>
+    <col min="2248" max="2248" width="3.19921875" style="4" customWidth="1"/>
     <col min="2249" max="2249" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2250" max="2250" width="6.77734375" style="4" customWidth="1"/>
+    <col min="2250" max="2250" width="6.796875" style="4" customWidth="1"/>
     <col min="2251" max="2253" width="9" style="4"/>
-    <col min="2254" max="2254" width="11.6640625" style="4" customWidth="1"/>
+    <col min="2254" max="2254" width="11.69921875" style="4" customWidth="1"/>
     <col min="2255" max="2255" width="7" style="4" customWidth="1"/>
     <col min="2256" max="2256" width="9" style="4"/>
-    <col min="2257" max="2257" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2257" max="2257" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="2258" max="2493" width="9" style="4"/>
-    <col min="2494" max="2494" width="2.77734375" style="4" customWidth="1"/>
-    <col min="2495" max="2495" width="17.33203125" style="4" customWidth="1"/>
-    <col min="2496" max="2496" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2497" max="2497" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2498" max="2499" width="6.33203125" style="4" customWidth="1"/>
-    <col min="2500" max="2501" width="4.33203125" style="4" customWidth="1"/>
-    <col min="2502" max="2502" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2494" max="2494" width="2.796875" style="4" customWidth="1"/>
+    <col min="2495" max="2495" width="17.296875" style="4" customWidth="1"/>
+    <col min="2496" max="2496" width="6.796875" style="4" customWidth="1"/>
+    <col min="2497" max="2497" width="5.296875" style="4" customWidth="1"/>
+    <col min="2498" max="2499" width="6.296875" style="4" customWidth="1"/>
+    <col min="2500" max="2501" width="4.296875" style="4" customWidth="1"/>
+    <col min="2502" max="2502" width="3.8984375" style="4" customWidth="1"/>
     <col min="2503" max="2503" width="3" style="4" customWidth="1"/>
-    <col min="2504" max="2504" width="3.21875" style="4" customWidth="1"/>
+    <col min="2504" max="2504" width="3.19921875" style="4" customWidth="1"/>
     <col min="2505" max="2505" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2506" max="2506" width="6.77734375" style="4" customWidth="1"/>
+    <col min="2506" max="2506" width="6.796875" style="4" customWidth="1"/>
     <col min="2507" max="2509" width="9" style="4"/>
-    <col min="2510" max="2510" width="11.6640625" style="4" customWidth="1"/>
+    <col min="2510" max="2510" width="11.69921875" style="4" customWidth="1"/>
     <col min="2511" max="2511" width="7" style="4" customWidth="1"/>
     <col min="2512" max="2512" width="9" style="4"/>
-    <col min="2513" max="2513" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2513" max="2513" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="2514" max="2749" width="9" style="4"/>
-    <col min="2750" max="2750" width="2.77734375" style="4" customWidth="1"/>
-    <col min="2751" max="2751" width="17.33203125" style="4" customWidth="1"/>
-    <col min="2752" max="2752" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2753" max="2753" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2754" max="2755" width="6.33203125" style="4" customWidth="1"/>
-    <col min="2756" max="2757" width="4.33203125" style="4" customWidth="1"/>
-    <col min="2758" max="2758" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2750" max="2750" width="2.796875" style="4" customWidth="1"/>
+    <col min="2751" max="2751" width="17.296875" style="4" customWidth="1"/>
+    <col min="2752" max="2752" width="6.796875" style="4" customWidth="1"/>
+    <col min="2753" max="2753" width="5.296875" style="4" customWidth="1"/>
+    <col min="2754" max="2755" width="6.296875" style="4" customWidth="1"/>
+    <col min="2756" max="2757" width="4.296875" style="4" customWidth="1"/>
+    <col min="2758" max="2758" width="3.8984375" style="4" customWidth="1"/>
     <col min="2759" max="2759" width="3" style="4" customWidth="1"/>
-    <col min="2760" max="2760" width="3.21875" style="4" customWidth="1"/>
+    <col min="2760" max="2760" width="3.19921875" style="4" customWidth="1"/>
     <col min="2761" max="2761" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2762" max="2762" width="6.77734375" style="4" customWidth="1"/>
+    <col min="2762" max="2762" width="6.796875" style="4" customWidth="1"/>
     <col min="2763" max="2765" width="9" style="4"/>
-    <col min="2766" max="2766" width="11.6640625" style="4" customWidth="1"/>
+    <col min="2766" max="2766" width="11.69921875" style="4" customWidth="1"/>
     <col min="2767" max="2767" width="7" style="4" customWidth="1"/>
     <col min="2768" max="2768" width="9" style="4"/>
-    <col min="2769" max="2769" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2769" max="2769" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="2770" max="3005" width="9" style="4"/>
-    <col min="3006" max="3006" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3007" max="3007" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3008" max="3008" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3009" max="3009" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3010" max="3011" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3012" max="3013" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3014" max="3014" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3006" max="3006" width="2.796875" style="4" customWidth="1"/>
+    <col min="3007" max="3007" width="17.296875" style="4" customWidth="1"/>
+    <col min="3008" max="3008" width="6.796875" style="4" customWidth="1"/>
+    <col min="3009" max="3009" width="5.296875" style="4" customWidth="1"/>
+    <col min="3010" max="3011" width="6.296875" style="4" customWidth="1"/>
+    <col min="3012" max="3013" width="4.296875" style="4" customWidth="1"/>
+    <col min="3014" max="3014" width="3.8984375" style="4" customWidth="1"/>
     <col min="3015" max="3015" width="3" style="4" customWidth="1"/>
-    <col min="3016" max="3016" width="3.21875" style="4" customWidth="1"/>
+    <col min="3016" max="3016" width="3.19921875" style="4" customWidth="1"/>
     <col min="3017" max="3017" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3018" max="3018" width="6.77734375" style="4" customWidth="1"/>
+    <col min="3018" max="3018" width="6.796875" style="4" customWidth="1"/>
     <col min="3019" max="3021" width="9" style="4"/>
-    <col min="3022" max="3022" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3022" max="3022" width="11.69921875" style="4" customWidth="1"/>
     <col min="3023" max="3023" width="7" style="4" customWidth="1"/>
     <col min="3024" max="3024" width="9" style="4"/>
-    <col min="3025" max="3025" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3025" max="3025" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="3026" max="3261" width="9" style="4"/>
-    <col min="3262" max="3262" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3263" max="3263" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3264" max="3264" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3265" max="3265" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3266" max="3267" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3268" max="3269" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3270" max="3270" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3262" max="3262" width="2.796875" style="4" customWidth="1"/>
+    <col min="3263" max="3263" width="17.296875" style="4" customWidth="1"/>
+    <col min="3264" max="3264" width="6.796875" style="4" customWidth="1"/>
+    <col min="3265" max="3265" width="5.296875" style="4" customWidth="1"/>
+    <col min="3266" max="3267" width="6.296875" style="4" customWidth="1"/>
+    <col min="3268" max="3269" width="4.296875" style="4" customWidth="1"/>
+    <col min="3270" max="3270" width="3.8984375" style="4" customWidth="1"/>
     <col min="3271" max="3271" width="3" style="4" customWidth="1"/>
-    <col min="3272" max="3272" width="3.21875" style="4" customWidth="1"/>
+    <col min="3272" max="3272" width="3.19921875" style="4" customWidth="1"/>
     <col min="3273" max="3273" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3274" max="3274" width="6.77734375" style="4" customWidth="1"/>
+    <col min="3274" max="3274" width="6.796875" style="4" customWidth="1"/>
     <col min="3275" max="3277" width="9" style="4"/>
-    <col min="3278" max="3278" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3278" max="3278" width="11.69921875" style="4" customWidth="1"/>
     <col min="3279" max="3279" width="7" style="4" customWidth="1"/>
     <col min="3280" max="3280" width="9" style="4"/>
-    <col min="3281" max="3281" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3281" max="3281" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="3282" max="3517" width="9" style="4"/>
-    <col min="3518" max="3518" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3519" max="3519" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3520" max="3520" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3521" max="3521" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3522" max="3523" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3524" max="3525" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3526" max="3526" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3518" max="3518" width="2.796875" style="4" customWidth="1"/>
+    <col min="3519" max="3519" width="17.296875" style="4" customWidth="1"/>
+    <col min="3520" max="3520" width="6.796875" style="4" customWidth="1"/>
+    <col min="3521" max="3521" width="5.296875" style="4" customWidth="1"/>
+    <col min="3522" max="3523" width="6.296875" style="4" customWidth="1"/>
+    <col min="3524" max="3525" width="4.296875" style="4" customWidth="1"/>
+    <col min="3526" max="3526" width="3.8984375" style="4" customWidth="1"/>
     <col min="3527" max="3527" width="3" style="4" customWidth="1"/>
-    <col min="3528" max="3528" width="3.21875" style="4" customWidth="1"/>
+    <col min="3528" max="3528" width="3.19921875" style="4" customWidth="1"/>
     <col min="3529" max="3529" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3530" max="3530" width="6.77734375" style="4" customWidth="1"/>
+    <col min="3530" max="3530" width="6.796875" style="4" customWidth="1"/>
     <col min="3531" max="3533" width="9" style="4"/>
-    <col min="3534" max="3534" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3534" max="3534" width="11.69921875" style="4" customWidth="1"/>
     <col min="3535" max="3535" width="7" style="4" customWidth="1"/>
     <col min="3536" max="3536" width="9" style="4"/>
-    <col min="3537" max="3537" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3537" max="3537" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="3538" max="3773" width="9" style="4"/>
-    <col min="3774" max="3774" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3775" max="3775" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3776" max="3776" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3777" max="3777" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3778" max="3779" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3780" max="3781" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3782" max="3782" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3774" max="3774" width="2.796875" style="4" customWidth="1"/>
+    <col min="3775" max="3775" width="17.296875" style="4" customWidth="1"/>
+    <col min="3776" max="3776" width="6.796875" style="4" customWidth="1"/>
+    <col min="3777" max="3777" width="5.296875" style="4" customWidth="1"/>
+    <col min="3778" max="3779" width="6.296875" style="4" customWidth="1"/>
+    <col min="3780" max="3781" width="4.296875" style="4" customWidth="1"/>
+    <col min="3782" max="3782" width="3.8984375" style="4" customWidth="1"/>
     <col min="3783" max="3783" width="3" style="4" customWidth="1"/>
-    <col min="3784" max="3784" width="3.21875" style="4" customWidth="1"/>
+    <col min="3784" max="3784" width="3.19921875" style="4" customWidth="1"/>
     <col min="3785" max="3785" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3786" max="3786" width="6.77734375" style="4" customWidth="1"/>
+    <col min="3786" max="3786" width="6.796875" style="4" customWidth="1"/>
     <col min="3787" max="3789" width="9" style="4"/>
-    <col min="3790" max="3790" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3790" max="3790" width="11.69921875" style="4" customWidth="1"/>
     <col min="3791" max="3791" width="7" style="4" customWidth="1"/>
     <col min="3792" max="3792" width="9" style="4"/>
-    <col min="3793" max="3793" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="3793" max="3793" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="3794" max="4029" width="9" style="4"/>
-    <col min="4030" max="4030" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4031" max="4031" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4032" max="4032" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4033" max="4033" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4034" max="4035" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4036" max="4037" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4038" max="4038" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4030" max="4030" width="2.796875" style="4" customWidth="1"/>
+    <col min="4031" max="4031" width="17.296875" style="4" customWidth="1"/>
+    <col min="4032" max="4032" width="6.796875" style="4" customWidth="1"/>
+    <col min="4033" max="4033" width="5.296875" style="4" customWidth="1"/>
+    <col min="4034" max="4035" width="6.296875" style="4" customWidth="1"/>
+    <col min="4036" max="4037" width="4.296875" style="4" customWidth="1"/>
+    <col min="4038" max="4038" width="3.8984375" style="4" customWidth="1"/>
     <col min="4039" max="4039" width="3" style="4" customWidth="1"/>
-    <col min="4040" max="4040" width="3.21875" style="4" customWidth="1"/>
+    <col min="4040" max="4040" width="3.19921875" style="4" customWidth="1"/>
     <col min="4041" max="4041" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4042" max="4042" width="6.77734375" style="4" customWidth="1"/>
+    <col min="4042" max="4042" width="6.796875" style="4" customWidth="1"/>
     <col min="4043" max="4045" width="9" style="4"/>
-    <col min="4046" max="4046" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4046" max="4046" width="11.69921875" style="4" customWidth="1"/>
     <col min="4047" max="4047" width="7" style="4" customWidth="1"/>
     <col min="4048" max="4048" width="9" style="4"/>
-    <col min="4049" max="4049" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4049" max="4049" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="4050" max="4285" width="9" style="4"/>
-    <col min="4286" max="4286" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4287" max="4287" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4288" max="4288" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4289" max="4289" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4290" max="4291" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4292" max="4293" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4294" max="4294" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4286" max="4286" width="2.796875" style="4" customWidth="1"/>
+    <col min="4287" max="4287" width="17.296875" style="4" customWidth="1"/>
+    <col min="4288" max="4288" width="6.796875" style="4" customWidth="1"/>
+    <col min="4289" max="4289" width="5.296875" style="4" customWidth="1"/>
+    <col min="4290" max="4291" width="6.296875" style="4" customWidth="1"/>
+    <col min="4292" max="4293" width="4.296875" style="4" customWidth="1"/>
+    <col min="4294" max="4294" width="3.8984375" style="4" customWidth="1"/>
     <col min="4295" max="4295" width="3" style="4" customWidth="1"/>
-    <col min="4296" max="4296" width="3.21875" style="4" customWidth="1"/>
+    <col min="4296" max="4296" width="3.19921875" style="4" customWidth="1"/>
     <col min="4297" max="4297" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4298" max="4298" width="6.77734375" style="4" customWidth="1"/>
+    <col min="4298" max="4298" width="6.796875" style="4" customWidth="1"/>
     <col min="4299" max="4301" width="9" style="4"/>
-    <col min="4302" max="4302" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4302" max="4302" width="11.69921875" style="4" customWidth="1"/>
     <col min="4303" max="4303" width="7" style="4" customWidth="1"/>
     <col min="4304" max="4304" width="9" style="4"/>
-    <col min="4305" max="4305" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4305" max="4305" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="4306" max="4541" width="9" style="4"/>
-    <col min="4542" max="4542" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4543" max="4543" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4544" max="4544" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4545" max="4545" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4546" max="4547" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4548" max="4549" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4550" max="4550" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4542" max="4542" width="2.796875" style="4" customWidth="1"/>
+    <col min="4543" max="4543" width="17.296875" style="4" customWidth="1"/>
+    <col min="4544" max="4544" width="6.796875" style="4" customWidth="1"/>
+    <col min="4545" max="4545" width="5.296875" style="4" customWidth="1"/>
+    <col min="4546" max="4547" width="6.296875" style="4" customWidth="1"/>
+    <col min="4548" max="4549" width="4.296875" style="4" customWidth="1"/>
+    <col min="4550" max="4550" width="3.8984375" style="4" customWidth="1"/>
     <col min="4551" max="4551" width="3" style="4" customWidth="1"/>
-    <col min="4552" max="4552" width="3.21875" style="4" customWidth="1"/>
+    <col min="4552" max="4552" width="3.19921875" style="4" customWidth="1"/>
     <col min="4553" max="4553" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4554" max="4554" width="6.77734375" style="4" customWidth="1"/>
+    <col min="4554" max="4554" width="6.796875" style="4" customWidth="1"/>
     <col min="4555" max="4557" width="9" style="4"/>
-    <col min="4558" max="4558" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4558" max="4558" width="11.69921875" style="4" customWidth="1"/>
     <col min="4559" max="4559" width="7" style="4" customWidth="1"/>
     <col min="4560" max="4560" width="9" style="4"/>
-    <col min="4561" max="4561" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4561" max="4561" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="4562" max="4797" width="9" style="4"/>
-    <col min="4798" max="4798" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4799" max="4799" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4800" max="4800" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4801" max="4801" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4802" max="4803" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4804" max="4805" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4806" max="4806" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4798" max="4798" width="2.796875" style="4" customWidth="1"/>
+    <col min="4799" max="4799" width="17.296875" style="4" customWidth="1"/>
+    <col min="4800" max="4800" width="6.796875" style="4" customWidth="1"/>
+    <col min="4801" max="4801" width="5.296875" style="4" customWidth="1"/>
+    <col min="4802" max="4803" width="6.296875" style="4" customWidth="1"/>
+    <col min="4804" max="4805" width="4.296875" style="4" customWidth="1"/>
+    <col min="4806" max="4806" width="3.8984375" style="4" customWidth="1"/>
     <col min="4807" max="4807" width="3" style="4" customWidth="1"/>
-    <col min="4808" max="4808" width="3.21875" style="4" customWidth="1"/>
+    <col min="4808" max="4808" width="3.19921875" style="4" customWidth="1"/>
     <col min="4809" max="4809" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4810" max="4810" width="6.77734375" style="4" customWidth="1"/>
+    <col min="4810" max="4810" width="6.796875" style="4" customWidth="1"/>
     <col min="4811" max="4813" width="9" style="4"/>
-    <col min="4814" max="4814" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4814" max="4814" width="11.69921875" style="4" customWidth="1"/>
     <col min="4815" max="4815" width="7" style="4" customWidth="1"/>
     <col min="4816" max="4816" width="9" style="4"/>
-    <col min="4817" max="4817" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4817" max="4817" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="4818" max="5053" width="9" style="4"/>
-    <col min="5054" max="5054" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5055" max="5055" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5056" max="5056" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5057" max="5057" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5058" max="5059" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5060" max="5061" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5062" max="5062" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5054" max="5054" width="2.796875" style="4" customWidth="1"/>
+    <col min="5055" max="5055" width="17.296875" style="4" customWidth="1"/>
+    <col min="5056" max="5056" width="6.796875" style="4" customWidth="1"/>
+    <col min="5057" max="5057" width="5.296875" style="4" customWidth="1"/>
+    <col min="5058" max="5059" width="6.296875" style="4" customWidth="1"/>
+    <col min="5060" max="5061" width="4.296875" style="4" customWidth="1"/>
+    <col min="5062" max="5062" width="3.8984375" style="4" customWidth="1"/>
     <col min="5063" max="5063" width="3" style="4" customWidth="1"/>
-    <col min="5064" max="5064" width="3.21875" style="4" customWidth="1"/>
+    <col min="5064" max="5064" width="3.19921875" style="4" customWidth="1"/>
     <col min="5065" max="5065" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5066" max="5066" width="6.77734375" style="4" customWidth="1"/>
+    <col min="5066" max="5066" width="6.796875" style="4" customWidth="1"/>
     <col min="5067" max="5069" width="9" style="4"/>
-    <col min="5070" max="5070" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5070" max="5070" width="11.69921875" style="4" customWidth="1"/>
     <col min="5071" max="5071" width="7" style="4" customWidth="1"/>
     <col min="5072" max="5072" width="9" style="4"/>
-    <col min="5073" max="5073" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5073" max="5073" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="5074" max="5309" width="9" style="4"/>
-    <col min="5310" max="5310" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5311" max="5311" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5312" max="5312" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5313" max="5313" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5314" max="5315" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5316" max="5317" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5318" max="5318" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5310" max="5310" width="2.796875" style="4" customWidth="1"/>
+    <col min="5311" max="5311" width="17.296875" style="4" customWidth="1"/>
+    <col min="5312" max="5312" width="6.796875" style="4" customWidth="1"/>
+    <col min="5313" max="5313" width="5.296875" style="4" customWidth="1"/>
+    <col min="5314" max="5315" width="6.296875" style="4" customWidth="1"/>
+    <col min="5316" max="5317" width="4.296875" style="4" customWidth="1"/>
+    <col min="5318" max="5318" width="3.8984375" style="4" customWidth="1"/>
     <col min="5319" max="5319" width="3" style="4" customWidth="1"/>
-    <col min="5320" max="5320" width="3.21875" style="4" customWidth="1"/>
+    <col min="5320" max="5320" width="3.19921875" style="4" customWidth="1"/>
     <col min="5321" max="5321" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5322" max="5322" width="6.77734375" style="4" customWidth="1"/>
+    <col min="5322" max="5322" width="6.796875" style="4" customWidth="1"/>
     <col min="5323" max="5325" width="9" style="4"/>
-    <col min="5326" max="5326" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5326" max="5326" width="11.69921875" style="4" customWidth="1"/>
     <col min="5327" max="5327" width="7" style="4" customWidth="1"/>
     <col min="5328" max="5328" width="9" style="4"/>
-    <col min="5329" max="5329" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5329" max="5329" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="5330" max="5565" width="9" style="4"/>
-    <col min="5566" max="5566" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5567" max="5567" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5568" max="5568" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5569" max="5569" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5570" max="5571" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5572" max="5573" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5574" max="5574" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5566" max="5566" width="2.796875" style="4" customWidth="1"/>
+    <col min="5567" max="5567" width="17.296875" style="4" customWidth="1"/>
+    <col min="5568" max="5568" width="6.796875" style="4" customWidth="1"/>
+    <col min="5569" max="5569" width="5.296875" style="4" customWidth="1"/>
+    <col min="5570" max="5571" width="6.296875" style="4" customWidth="1"/>
+    <col min="5572" max="5573" width="4.296875" style="4" customWidth="1"/>
+    <col min="5574" max="5574" width="3.8984375" style="4" customWidth="1"/>
     <col min="5575" max="5575" width="3" style="4" customWidth="1"/>
-    <col min="5576" max="5576" width="3.21875" style="4" customWidth="1"/>
+    <col min="5576" max="5576" width="3.19921875" style="4" customWidth="1"/>
     <col min="5577" max="5577" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5578" max="5578" width="6.77734375" style="4" customWidth="1"/>
+    <col min="5578" max="5578" width="6.796875" style="4" customWidth="1"/>
     <col min="5579" max="5581" width="9" style="4"/>
-    <col min="5582" max="5582" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5582" max="5582" width="11.69921875" style="4" customWidth="1"/>
     <col min="5583" max="5583" width="7" style="4" customWidth="1"/>
     <col min="5584" max="5584" width="9" style="4"/>
-    <col min="5585" max="5585" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5585" max="5585" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="5586" max="5821" width="9" style="4"/>
-    <col min="5822" max="5822" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5823" max="5823" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5824" max="5824" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5825" max="5825" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5826" max="5827" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5828" max="5829" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5830" max="5830" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5822" max="5822" width="2.796875" style="4" customWidth="1"/>
+    <col min="5823" max="5823" width="17.296875" style="4" customWidth="1"/>
+    <col min="5824" max="5824" width="6.796875" style="4" customWidth="1"/>
+    <col min="5825" max="5825" width="5.296875" style="4" customWidth="1"/>
+    <col min="5826" max="5827" width="6.296875" style="4" customWidth="1"/>
+    <col min="5828" max="5829" width="4.296875" style="4" customWidth="1"/>
+    <col min="5830" max="5830" width="3.8984375" style="4" customWidth="1"/>
     <col min="5831" max="5831" width="3" style="4" customWidth="1"/>
-    <col min="5832" max="5832" width="3.21875" style="4" customWidth="1"/>
+    <col min="5832" max="5832" width="3.19921875" style="4" customWidth="1"/>
     <col min="5833" max="5833" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5834" max="5834" width="6.77734375" style="4" customWidth="1"/>
+    <col min="5834" max="5834" width="6.796875" style="4" customWidth="1"/>
     <col min="5835" max="5837" width="9" style="4"/>
-    <col min="5838" max="5838" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5838" max="5838" width="11.69921875" style="4" customWidth="1"/>
     <col min="5839" max="5839" width="7" style="4" customWidth="1"/>
     <col min="5840" max="5840" width="9" style="4"/>
-    <col min="5841" max="5841" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5841" max="5841" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="5842" max="6077" width="9" style="4"/>
-    <col min="6078" max="6078" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6079" max="6079" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6080" max="6080" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6081" max="6081" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6082" max="6083" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6084" max="6085" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6086" max="6086" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6078" max="6078" width="2.796875" style="4" customWidth="1"/>
+    <col min="6079" max="6079" width="17.296875" style="4" customWidth="1"/>
+    <col min="6080" max="6080" width="6.796875" style="4" customWidth="1"/>
+    <col min="6081" max="6081" width="5.296875" style="4" customWidth="1"/>
+    <col min="6082" max="6083" width="6.296875" style="4" customWidth="1"/>
+    <col min="6084" max="6085" width="4.296875" style="4" customWidth="1"/>
+    <col min="6086" max="6086" width="3.8984375" style="4" customWidth="1"/>
     <col min="6087" max="6087" width="3" style="4" customWidth="1"/>
-    <col min="6088" max="6088" width="3.21875" style="4" customWidth="1"/>
+    <col min="6088" max="6088" width="3.19921875" style="4" customWidth="1"/>
     <col min="6089" max="6089" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6090" max="6090" width="6.77734375" style="4" customWidth="1"/>
+    <col min="6090" max="6090" width="6.796875" style="4" customWidth="1"/>
     <col min="6091" max="6093" width="9" style="4"/>
-    <col min="6094" max="6094" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6094" max="6094" width="11.69921875" style="4" customWidth="1"/>
     <col min="6095" max="6095" width="7" style="4" customWidth="1"/>
     <col min="6096" max="6096" width="9" style="4"/>
-    <col min="6097" max="6097" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6097" max="6097" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="6098" max="6333" width="9" style="4"/>
-    <col min="6334" max="6334" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6335" max="6335" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6336" max="6336" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6337" max="6337" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6338" max="6339" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6340" max="6341" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6342" max="6342" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6334" max="6334" width="2.796875" style="4" customWidth="1"/>
+    <col min="6335" max="6335" width="17.296875" style="4" customWidth="1"/>
+    <col min="6336" max="6336" width="6.796875" style="4" customWidth="1"/>
+    <col min="6337" max="6337" width="5.296875" style="4" customWidth="1"/>
+    <col min="6338" max="6339" width="6.296875" style="4" customWidth="1"/>
+    <col min="6340" max="6341" width="4.296875" style="4" customWidth="1"/>
+    <col min="6342" max="6342" width="3.8984375" style="4" customWidth="1"/>
     <col min="6343" max="6343" width="3" style="4" customWidth="1"/>
-    <col min="6344" max="6344" width="3.21875" style="4" customWidth="1"/>
+    <col min="6344" max="6344" width="3.19921875" style="4" customWidth="1"/>
     <col min="6345" max="6345" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6346" max="6346" width="6.77734375" style="4" customWidth="1"/>
+    <col min="6346" max="6346" width="6.796875" style="4" customWidth="1"/>
     <col min="6347" max="6349" width="9" style="4"/>
-    <col min="6350" max="6350" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6350" max="6350" width="11.69921875" style="4" customWidth="1"/>
     <col min="6351" max="6351" width="7" style="4" customWidth="1"/>
     <col min="6352" max="6352" width="9" style="4"/>
-    <col min="6353" max="6353" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6353" max="6353" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="6354" max="6589" width="9" style="4"/>
-    <col min="6590" max="6590" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6591" max="6591" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6592" max="6592" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6593" max="6593" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6594" max="6595" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6596" max="6597" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6598" max="6598" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6590" max="6590" width="2.796875" style="4" customWidth="1"/>
+    <col min="6591" max="6591" width="17.296875" style="4" customWidth="1"/>
+    <col min="6592" max="6592" width="6.796875" style="4" customWidth="1"/>
+    <col min="6593" max="6593" width="5.296875" style="4" customWidth="1"/>
+    <col min="6594" max="6595" width="6.296875" style="4" customWidth="1"/>
+    <col min="6596" max="6597" width="4.296875" style="4" customWidth="1"/>
+    <col min="6598" max="6598" width="3.8984375" style="4" customWidth="1"/>
     <col min="6599" max="6599" width="3" style="4" customWidth="1"/>
-    <col min="6600" max="6600" width="3.21875" style="4" customWidth="1"/>
+    <col min="6600" max="6600" width="3.19921875" style="4" customWidth="1"/>
     <col min="6601" max="6601" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6602" max="6602" width="6.77734375" style="4" customWidth="1"/>
+    <col min="6602" max="6602" width="6.796875" style="4" customWidth="1"/>
     <col min="6603" max="6605" width="9" style="4"/>
-    <col min="6606" max="6606" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6606" max="6606" width="11.69921875" style="4" customWidth="1"/>
     <col min="6607" max="6607" width="7" style="4" customWidth="1"/>
     <col min="6608" max="6608" width="9" style="4"/>
-    <col min="6609" max="6609" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6609" max="6609" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="6610" max="6845" width="9" style="4"/>
-    <col min="6846" max="6846" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6847" max="6847" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6848" max="6848" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6849" max="6849" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6850" max="6851" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6852" max="6853" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6854" max="6854" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6846" max="6846" width="2.796875" style="4" customWidth="1"/>
+    <col min="6847" max="6847" width="17.296875" style="4" customWidth="1"/>
+    <col min="6848" max="6848" width="6.796875" style="4" customWidth="1"/>
+    <col min="6849" max="6849" width="5.296875" style="4" customWidth="1"/>
+    <col min="6850" max="6851" width="6.296875" style="4" customWidth="1"/>
+    <col min="6852" max="6853" width="4.296875" style="4" customWidth="1"/>
+    <col min="6854" max="6854" width="3.8984375" style="4" customWidth="1"/>
     <col min="6855" max="6855" width="3" style="4" customWidth="1"/>
-    <col min="6856" max="6856" width="3.21875" style="4" customWidth="1"/>
+    <col min="6856" max="6856" width="3.19921875" style="4" customWidth="1"/>
     <col min="6857" max="6857" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6858" max="6858" width="6.77734375" style="4" customWidth="1"/>
+    <col min="6858" max="6858" width="6.796875" style="4" customWidth="1"/>
     <col min="6859" max="6861" width="9" style="4"/>
-    <col min="6862" max="6862" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6862" max="6862" width="11.69921875" style="4" customWidth="1"/>
     <col min="6863" max="6863" width="7" style="4" customWidth="1"/>
     <col min="6864" max="6864" width="9" style="4"/>
-    <col min="6865" max="6865" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6865" max="6865" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="6866" max="7101" width="9" style="4"/>
-    <col min="7102" max="7102" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7103" max="7103" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7104" max="7104" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7105" max="7105" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7106" max="7107" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7108" max="7109" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7110" max="7110" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7102" max="7102" width="2.796875" style="4" customWidth="1"/>
+    <col min="7103" max="7103" width="17.296875" style="4" customWidth="1"/>
+    <col min="7104" max="7104" width="6.796875" style="4" customWidth="1"/>
+    <col min="7105" max="7105" width="5.296875" style="4" customWidth="1"/>
+    <col min="7106" max="7107" width="6.296875" style="4" customWidth="1"/>
+    <col min="7108" max="7109" width="4.296875" style="4" customWidth="1"/>
+    <col min="7110" max="7110" width="3.8984375" style="4" customWidth="1"/>
     <col min="7111" max="7111" width="3" style="4" customWidth="1"/>
-    <col min="7112" max="7112" width="3.21875" style="4" customWidth="1"/>
+    <col min="7112" max="7112" width="3.19921875" style="4" customWidth="1"/>
     <col min="7113" max="7113" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7114" max="7114" width="6.77734375" style="4" customWidth="1"/>
+    <col min="7114" max="7114" width="6.796875" style="4" customWidth="1"/>
     <col min="7115" max="7117" width="9" style="4"/>
-    <col min="7118" max="7118" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7118" max="7118" width="11.69921875" style="4" customWidth="1"/>
     <col min="7119" max="7119" width="7" style="4" customWidth="1"/>
     <col min="7120" max="7120" width="9" style="4"/>
-    <col min="7121" max="7121" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7121" max="7121" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="7122" max="7357" width="9" style="4"/>
-    <col min="7358" max="7358" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7359" max="7359" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7360" max="7360" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7361" max="7361" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7362" max="7363" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7364" max="7365" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7366" max="7366" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7358" max="7358" width="2.796875" style="4" customWidth="1"/>
+    <col min="7359" max="7359" width="17.296875" style="4" customWidth="1"/>
+    <col min="7360" max="7360" width="6.796875" style="4" customWidth="1"/>
+    <col min="7361" max="7361" width="5.296875" style="4" customWidth="1"/>
+    <col min="7362" max="7363" width="6.296875" style="4" customWidth="1"/>
+    <col min="7364" max="7365" width="4.296875" style="4" customWidth="1"/>
+    <col min="7366" max="7366" width="3.8984375" style="4" customWidth="1"/>
     <col min="7367" max="7367" width="3" style="4" customWidth="1"/>
-    <col min="7368" max="7368" width="3.21875" style="4" customWidth="1"/>
+    <col min="7368" max="7368" width="3.19921875" style="4" customWidth="1"/>
     <col min="7369" max="7369" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7370" max="7370" width="6.77734375" style="4" customWidth="1"/>
+    <col min="7370" max="7370" width="6.796875" style="4" customWidth="1"/>
     <col min="7371" max="7373" width="9" style="4"/>
-    <col min="7374" max="7374" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7374" max="7374" width="11.69921875" style="4" customWidth="1"/>
     <col min="7375" max="7375" width="7" style="4" customWidth="1"/>
     <col min="7376" max="7376" width="9" style="4"/>
-    <col min="7377" max="7377" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7377" max="7377" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="7378" max="7613" width="9" style="4"/>
-    <col min="7614" max="7614" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7615" max="7615" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7616" max="7616" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7617" max="7617" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7618" max="7619" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7620" max="7621" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7622" max="7622" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7614" max="7614" width="2.796875" style="4" customWidth="1"/>
+    <col min="7615" max="7615" width="17.296875" style="4" customWidth="1"/>
+    <col min="7616" max="7616" width="6.796875" style="4" customWidth="1"/>
+    <col min="7617" max="7617" width="5.296875" style="4" customWidth="1"/>
+    <col min="7618" max="7619" width="6.296875" style="4" customWidth="1"/>
+    <col min="7620" max="7621" width="4.296875" style="4" customWidth="1"/>
+    <col min="7622" max="7622" width="3.8984375" style="4" customWidth="1"/>
     <col min="7623" max="7623" width="3" style="4" customWidth="1"/>
-    <col min="7624" max="7624" width="3.21875" style="4" customWidth="1"/>
+    <col min="7624" max="7624" width="3.19921875" style="4" customWidth="1"/>
     <col min="7625" max="7625" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7626" max="7626" width="6.77734375" style="4" customWidth="1"/>
+    <col min="7626" max="7626" width="6.796875" style="4" customWidth="1"/>
     <col min="7627" max="7629" width="9" style="4"/>
-    <col min="7630" max="7630" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7630" max="7630" width="11.69921875" style="4" customWidth="1"/>
     <col min="7631" max="7631" width="7" style="4" customWidth="1"/>
     <col min="7632" max="7632" width="9" style="4"/>
-    <col min="7633" max="7633" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7633" max="7633" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="7634" max="7869" width="9" style="4"/>
-    <col min="7870" max="7870" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7871" max="7871" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7872" max="7872" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7873" max="7873" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7874" max="7875" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7876" max="7877" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7878" max="7878" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7870" max="7870" width="2.796875" style="4" customWidth="1"/>
+    <col min="7871" max="7871" width="17.296875" style="4" customWidth="1"/>
+    <col min="7872" max="7872" width="6.796875" style="4" customWidth="1"/>
+    <col min="7873" max="7873" width="5.296875" style="4" customWidth="1"/>
+    <col min="7874" max="7875" width="6.296875" style="4" customWidth="1"/>
+    <col min="7876" max="7877" width="4.296875" style="4" customWidth="1"/>
+    <col min="7878" max="7878" width="3.8984375" style="4" customWidth="1"/>
     <col min="7879" max="7879" width="3" style="4" customWidth="1"/>
-    <col min="7880" max="7880" width="3.21875" style="4" customWidth="1"/>
+    <col min="7880" max="7880" width="3.19921875" style="4" customWidth="1"/>
     <col min="7881" max="7881" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7882" max="7882" width="6.77734375" style="4" customWidth="1"/>
+    <col min="7882" max="7882" width="6.796875" style="4" customWidth="1"/>
     <col min="7883" max="7885" width="9" style="4"/>
-    <col min="7886" max="7886" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7886" max="7886" width="11.69921875" style="4" customWidth="1"/>
     <col min="7887" max="7887" width="7" style="4" customWidth="1"/>
     <col min="7888" max="7888" width="9" style="4"/>
-    <col min="7889" max="7889" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7889" max="7889" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="7890" max="8125" width="9" style="4"/>
-    <col min="8126" max="8126" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8127" max="8127" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8128" max="8128" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8129" max="8129" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8130" max="8131" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8132" max="8133" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8134" max="8134" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8126" max="8126" width="2.796875" style="4" customWidth="1"/>
+    <col min="8127" max="8127" width="17.296875" style="4" customWidth="1"/>
+    <col min="8128" max="8128" width="6.796875" style="4" customWidth="1"/>
+    <col min="8129" max="8129" width="5.296875" style="4" customWidth="1"/>
+    <col min="8130" max="8131" width="6.296875" style="4" customWidth="1"/>
+    <col min="8132" max="8133" width="4.296875" style="4" customWidth="1"/>
+    <col min="8134" max="8134" width="3.8984375" style="4" customWidth="1"/>
     <col min="8135" max="8135" width="3" style="4" customWidth="1"/>
-    <col min="8136" max="8136" width="3.21875" style="4" customWidth="1"/>
+    <col min="8136" max="8136" width="3.19921875" style="4" customWidth="1"/>
     <col min="8137" max="8137" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8138" max="8138" width="6.77734375" style="4" customWidth="1"/>
+    <col min="8138" max="8138" width="6.796875" style="4" customWidth="1"/>
     <col min="8139" max="8141" width="9" style="4"/>
-    <col min="8142" max="8142" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8142" max="8142" width="11.69921875" style="4" customWidth="1"/>
     <col min="8143" max="8143" width="7" style="4" customWidth="1"/>
     <col min="8144" max="8144" width="9" style="4"/>
-    <col min="8145" max="8145" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8145" max="8145" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="8146" max="8381" width="9" style="4"/>
-    <col min="8382" max="8382" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8383" max="8383" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8384" max="8384" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8385" max="8385" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8386" max="8387" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8388" max="8389" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8390" max="8390" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8382" max="8382" width="2.796875" style="4" customWidth="1"/>
+    <col min="8383" max="8383" width="17.296875" style="4" customWidth="1"/>
+    <col min="8384" max="8384" width="6.796875" style="4" customWidth="1"/>
+    <col min="8385" max="8385" width="5.296875" style="4" customWidth="1"/>
+    <col min="8386" max="8387" width="6.296875" style="4" customWidth="1"/>
+    <col min="8388" max="8389" width="4.296875" style="4" customWidth="1"/>
+    <col min="8390" max="8390" width="3.8984375" style="4" customWidth="1"/>
     <col min="8391" max="8391" width="3" style="4" customWidth="1"/>
-    <col min="8392" max="8392" width="3.21875" style="4" customWidth="1"/>
+    <col min="8392" max="8392" width="3.19921875" style="4" customWidth="1"/>
     <col min="8393" max="8393" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8394" max="8394" width="6.77734375" style="4" customWidth="1"/>
+    <col min="8394" max="8394" width="6.796875" style="4" customWidth="1"/>
     <col min="8395" max="8397" width="9" style="4"/>
-    <col min="8398" max="8398" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8398" max="8398" width="11.69921875" style="4" customWidth="1"/>
     <col min="8399" max="8399" width="7" style="4" customWidth="1"/>
     <col min="8400" max="8400" width="9" style="4"/>
-    <col min="8401" max="8401" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8401" max="8401" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="8402" max="8637" width="9" style="4"/>
-    <col min="8638" max="8638" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8639" max="8639" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8640" max="8640" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8641" max="8641" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8642" max="8643" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8644" max="8645" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8646" max="8646" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8638" max="8638" width="2.796875" style="4" customWidth="1"/>
+    <col min="8639" max="8639" width="17.296875" style="4" customWidth="1"/>
+    <col min="8640" max="8640" width="6.796875" style="4" customWidth="1"/>
+    <col min="8641" max="8641" width="5.296875" style="4" customWidth="1"/>
+    <col min="8642" max="8643" width="6.296875" style="4" customWidth="1"/>
+    <col min="8644" max="8645" width="4.296875" style="4" customWidth="1"/>
+    <col min="8646" max="8646" width="3.8984375" style="4" customWidth="1"/>
     <col min="8647" max="8647" width="3" style="4" customWidth="1"/>
-    <col min="8648" max="8648" width="3.21875" style="4" customWidth="1"/>
+    <col min="8648" max="8648" width="3.19921875" style="4" customWidth="1"/>
     <col min="8649" max="8649" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8650" max="8650" width="6.77734375" style="4" customWidth="1"/>
+    <col min="8650" max="8650" width="6.796875" style="4" customWidth="1"/>
     <col min="8651" max="8653" width="9" style="4"/>
-    <col min="8654" max="8654" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8654" max="8654" width="11.69921875" style="4" customWidth="1"/>
     <col min="8655" max="8655" width="7" style="4" customWidth="1"/>
     <col min="8656" max="8656" width="9" style="4"/>
-    <col min="8657" max="8657" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8657" max="8657" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="8658" max="8893" width="9" style="4"/>
-    <col min="8894" max="8894" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8895" max="8895" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8896" max="8896" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8897" max="8897" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8898" max="8899" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8900" max="8901" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8902" max="8902" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8894" max="8894" width="2.796875" style="4" customWidth="1"/>
+    <col min="8895" max="8895" width="17.296875" style="4" customWidth="1"/>
+    <col min="8896" max="8896" width="6.796875" style="4" customWidth="1"/>
+    <col min="8897" max="8897" width="5.296875" style="4" customWidth="1"/>
+    <col min="8898" max="8899" width="6.296875" style="4" customWidth="1"/>
+    <col min="8900" max="8901" width="4.296875" style="4" customWidth="1"/>
+    <col min="8902" max="8902" width="3.8984375" style="4" customWidth="1"/>
     <col min="8903" max="8903" width="3" style="4" customWidth="1"/>
-    <col min="8904" max="8904" width="3.21875" style="4" customWidth="1"/>
+    <col min="8904" max="8904" width="3.19921875" style="4" customWidth="1"/>
     <col min="8905" max="8905" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8906" max="8906" width="6.77734375" style="4" customWidth="1"/>
+    <col min="8906" max="8906" width="6.796875" style="4" customWidth="1"/>
     <col min="8907" max="8909" width="9" style="4"/>
-    <col min="8910" max="8910" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8910" max="8910" width="11.69921875" style="4" customWidth="1"/>
     <col min="8911" max="8911" width="7" style="4" customWidth="1"/>
     <col min="8912" max="8912" width="9" style="4"/>
-    <col min="8913" max="8913" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8913" max="8913" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="8914" max="9149" width="9" style="4"/>
-    <col min="9150" max="9150" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9151" max="9151" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9152" max="9152" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9153" max="9153" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9154" max="9155" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9156" max="9157" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9158" max="9158" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9150" max="9150" width="2.796875" style="4" customWidth="1"/>
+    <col min="9151" max="9151" width="17.296875" style="4" customWidth="1"/>
+    <col min="9152" max="9152" width="6.796875" style="4" customWidth="1"/>
+    <col min="9153" max="9153" width="5.296875" style="4" customWidth="1"/>
+    <col min="9154" max="9155" width="6.296875" style="4" customWidth="1"/>
+    <col min="9156" max="9157" width="4.296875" style="4" customWidth="1"/>
+    <col min="9158" max="9158" width="3.8984375" style="4" customWidth="1"/>
     <col min="9159" max="9159" width="3" style="4" customWidth="1"/>
-    <col min="9160" max="9160" width="3.21875" style="4" customWidth="1"/>
+    <col min="9160" max="9160" width="3.19921875" style="4" customWidth="1"/>
     <col min="9161" max="9161" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9162" max="9162" width="6.77734375" style="4" customWidth="1"/>
+    <col min="9162" max="9162" width="6.796875" style="4" customWidth="1"/>
     <col min="9163" max="9165" width="9" style="4"/>
-    <col min="9166" max="9166" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9166" max="9166" width="11.69921875" style="4" customWidth="1"/>
     <col min="9167" max="9167" width="7" style="4" customWidth="1"/>
     <col min="9168" max="9168" width="9" style="4"/>
-    <col min="9169" max="9169" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9169" max="9169" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9170" max="9405" width="9" style="4"/>
-    <col min="9406" max="9406" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9407" max="9407" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9408" max="9408" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9409" max="9409" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9410" max="9411" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9412" max="9413" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9414" max="9414" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9406" max="9406" width="2.796875" style="4" customWidth="1"/>
+    <col min="9407" max="9407" width="17.296875" style="4" customWidth="1"/>
+    <col min="9408" max="9408" width="6.796875" style="4" customWidth="1"/>
+    <col min="9409" max="9409" width="5.296875" style="4" customWidth="1"/>
+    <col min="9410" max="9411" width="6.296875" style="4" customWidth="1"/>
+    <col min="9412" max="9413" width="4.296875" style="4" customWidth="1"/>
+    <col min="9414" max="9414" width="3.8984375" style="4" customWidth="1"/>
     <col min="9415" max="9415" width="3" style="4" customWidth="1"/>
-    <col min="9416" max="9416" width="3.21875" style="4" customWidth="1"/>
+    <col min="9416" max="9416" width="3.19921875" style="4" customWidth="1"/>
     <col min="9417" max="9417" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9418" max="9418" width="6.77734375" style="4" customWidth="1"/>
+    <col min="9418" max="9418" width="6.796875" style="4" customWidth="1"/>
     <col min="9419" max="9421" width="9" style="4"/>
-    <col min="9422" max="9422" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9422" max="9422" width="11.69921875" style="4" customWidth="1"/>
     <col min="9423" max="9423" width="7" style="4" customWidth="1"/>
     <col min="9424" max="9424" width="9" style="4"/>
-    <col min="9425" max="9425" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9425" max="9425" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9426" max="9661" width="9" style="4"/>
-    <col min="9662" max="9662" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9663" max="9663" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9664" max="9664" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9665" max="9665" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9666" max="9667" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9668" max="9669" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9670" max="9670" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9662" max="9662" width="2.796875" style="4" customWidth="1"/>
+    <col min="9663" max="9663" width="17.296875" style="4" customWidth="1"/>
+    <col min="9664" max="9664" width="6.796875" style="4" customWidth="1"/>
+    <col min="9665" max="9665" width="5.296875" style="4" customWidth="1"/>
+    <col min="9666" max="9667" width="6.296875" style="4" customWidth="1"/>
+    <col min="9668" max="9669" width="4.296875" style="4" customWidth="1"/>
+    <col min="9670" max="9670" width="3.8984375" style="4" customWidth="1"/>
     <col min="9671" max="9671" width="3" style="4" customWidth="1"/>
-    <col min="9672" max="9672" width="3.21875" style="4" customWidth="1"/>
+    <col min="9672" max="9672" width="3.19921875" style="4" customWidth="1"/>
     <col min="9673" max="9673" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9674" max="9674" width="6.77734375" style="4" customWidth="1"/>
+    <col min="9674" max="9674" width="6.796875" style="4" customWidth="1"/>
     <col min="9675" max="9677" width="9" style="4"/>
-    <col min="9678" max="9678" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9678" max="9678" width="11.69921875" style="4" customWidth="1"/>
     <col min="9679" max="9679" width="7" style="4" customWidth="1"/>
     <col min="9680" max="9680" width="9" style="4"/>
-    <col min="9681" max="9681" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9681" max="9681" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9682" max="9917" width="9" style="4"/>
-    <col min="9918" max="9918" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9919" max="9919" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9920" max="9920" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9921" max="9921" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9922" max="9923" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9924" max="9925" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9926" max="9926" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9918" max="9918" width="2.796875" style="4" customWidth="1"/>
+    <col min="9919" max="9919" width="17.296875" style="4" customWidth="1"/>
+    <col min="9920" max="9920" width="6.796875" style="4" customWidth="1"/>
+    <col min="9921" max="9921" width="5.296875" style="4" customWidth="1"/>
+    <col min="9922" max="9923" width="6.296875" style="4" customWidth="1"/>
+    <col min="9924" max="9925" width="4.296875" style="4" customWidth="1"/>
+    <col min="9926" max="9926" width="3.8984375" style="4" customWidth="1"/>
     <col min="9927" max="9927" width="3" style="4" customWidth="1"/>
-    <col min="9928" max="9928" width="3.21875" style="4" customWidth="1"/>
+    <col min="9928" max="9928" width="3.19921875" style="4" customWidth="1"/>
     <col min="9929" max="9929" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9930" max="9930" width="6.77734375" style="4" customWidth="1"/>
+    <col min="9930" max="9930" width="6.796875" style="4" customWidth="1"/>
     <col min="9931" max="9933" width="9" style="4"/>
-    <col min="9934" max="9934" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9934" max="9934" width="11.69921875" style="4" customWidth="1"/>
     <col min="9935" max="9935" width="7" style="4" customWidth="1"/>
     <col min="9936" max="9936" width="9" style="4"/>
-    <col min="9937" max="9937" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9937" max="9937" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="9938" max="10173" width="9" style="4"/>
-    <col min="10174" max="10174" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10175" max="10175" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10176" max="10176" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10177" max="10177" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10178" max="10179" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10180" max="10181" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10182" max="10182" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10174" max="10174" width="2.796875" style="4" customWidth="1"/>
+    <col min="10175" max="10175" width="17.296875" style="4" customWidth="1"/>
+    <col min="10176" max="10176" width="6.796875" style="4" customWidth="1"/>
+    <col min="10177" max="10177" width="5.296875" style="4" customWidth="1"/>
+    <col min="10178" max="10179" width="6.296875" style="4" customWidth="1"/>
+    <col min="10180" max="10181" width="4.296875" style="4" customWidth="1"/>
+    <col min="10182" max="10182" width="3.8984375" style="4" customWidth="1"/>
     <col min="10183" max="10183" width="3" style="4" customWidth="1"/>
-    <col min="10184" max="10184" width="3.21875" style="4" customWidth="1"/>
+    <col min="10184" max="10184" width="3.19921875" style="4" customWidth="1"/>
     <col min="10185" max="10185" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10186" max="10186" width="6.77734375" style="4" customWidth="1"/>
+    <col min="10186" max="10186" width="6.796875" style="4" customWidth="1"/>
     <col min="10187" max="10189" width="9" style="4"/>
-    <col min="10190" max="10190" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10190" max="10190" width="11.69921875" style="4" customWidth="1"/>
     <col min="10191" max="10191" width="7" style="4" customWidth="1"/>
     <col min="10192" max="10192" width="9" style="4"/>
-    <col min="10193" max="10193" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10193" max="10193" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="10194" max="10429" width="9" style="4"/>
-    <col min="10430" max="10430" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10431" max="10431" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10432" max="10432" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10433" max="10433" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10434" max="10435" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10436" max="10437" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10438" max="10438" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10430" max="10430" width="2.796875" style="4" customWidth="1"/>
+    <col min="10431" max="10431" width="17.296875" style="4" customWidth="1"/>
+    <col min="10432" max="10432" width="6.796875" style="4" customWidth="1"/>
+    <col min="10433" max="10433" width="5.296875" style="4" customWidth="1"/>
+    <col min="10434" max="10435" width="6.296875" style="4" customWidth="1"/>
+    <col min="10436" max="10437" width="4.296875" style="4" customWidth="1"/>
+    <col min="10438" max="10438" width="3.8984375" style="4" customWidth="1"/>
     <col min="10439" max="10439" width="3" style="4" customWidth="1"/>
-    <col min="10440" max="10440" width="3.21875" style="4" customWidth="1"/>
+    <col min="10440" max="10440" width="3.19921875" style="4" customWidth="1"/>
     <col min="10441" max="10441" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10442" max="10442" width="6.77734375" style="4" customWidth="1"/>
+    <col min="10442" max="10442" width="6.796875" style="4" customWidth="1"/>
     <col min="10443" max="10445" width="9" style="4"/>
-    <col min="10446" max="10446" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10446" max="10446" width="11.69921875" style="4" customWidth="1"/>
     <col min="10447" max="10447" width="7" style="4" customWidth="1"/>
     <col min="10448" max="10448" width="9" style="4"/>
-    <col min="10449" max="10449" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10449" max="10449" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="10450" max="10685" width="9" style="4"/>
-    <col min="10686" max="10686" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10687" max="10687" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10688" max="10688" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10689" max="10689" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10690" max="10691" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10692" max="10693" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10694" max="10694" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10686" max="10686" width="2.796875" style="4" customWidth="1"/>
+    <col min="10687" max="10687" width="17.296875" style="4" customWidth="1"/>
+    <col min="10688" max="10688" width="6.796875" style="4" customWidth="1"/>
+    <col min="10689" max="10689" width="5.296875" style="4" customWidth="1"/>
+    <col min="10690" max="10691" width="6.296875" style="4" customWidth="1"/>
+    <col min="10692" max="10693" width="4.296875" style="4" customWidth="1"/>
+    <col min="10694" max="10694" width="3.8984375" style="4" customWidth="1"/>
     <col min="10695" max="10695" width="3" style="4" customWidth="1"/>
-    <col min="10696" max="10696" width="3.21875" style="4" customWidth="1"/>
+    <col min="10696" max="10696" width="3.19921875" style="4" customWidth="1"/>
     <col min="10697" max="10697" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10698" max="10698" width="6.77734375" style="4" customWidth="1"/>
+    <col min="10698" max="10698" width="6.796875" style="4" customWidth="1"/>
     <col min="10699" max="10701" width="9" style="4"/>
-    <col min="10702" max="10702" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10702" max="10702" width="11.69921875" style="4" customWidth="1"/>
     <col min="10703" max="10703" width="7" style="4" customWidth="1"/>
     <col min="10704" max="10704" width="9" style="4"/>
-    <col min="10705" max="10705" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10705" max="10705" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="10706" max="10941" width="9" style="4"/>
-    <col min="10942" max="10942" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10943" max="10943" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10944" max="10944" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10945" max="10945" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10946" max="10947" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10948" max="10949" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10950" max="10950" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10942" max="10942" width="2.796875" style="4" customWidth="1"/>
+    <col min="10943" max="10943" width="17.296875" style="4" customWidth="1"/>
+    <col min="10944" max="10944" width="6.796875" style="4" customWidth="1"/>
+    <col min="10945" max="10945" width="5.296875" style="4" customWidth="1"/>
+    <col min="10946" max="10947" width="6.296875" style="4" customWidth="1"/>
+    <col min="10948" max="10949" width="4.296875" style="4" customWidth="1"/>
+    <col min="10950" max="10950" width="3.8984375" style="4" customWidth="1"/>
     <col min="10951" max="10951" width="3" style="4" customWidth="1"/>
-    <col min="10952" max="10952" width="3.21875" style="4" customWidth="1"/>
+    <col min="10952" max="10952" width="3.19921875" style="4" customWidth="1"/>
     <col min="10953" max="10953" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10954" max="10954" width="6.77734375" style="4" customWidth="1"/>
+    <col min="10954" max="10954" width="6.796875" style="4" customWidth="1"/>
     <col min="10955" max="10957" width="9" style="4"/>
-    <col min="10958" max="10958" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10958" max="10958" width="11.69921875" style="4" customWidth="1"/>
     <col min="10959" max="10959" width="7" style="4" customWidth="1"/>
     <col min="10960" max="10960" width="9" style="4"/>
-    <col min="10961" max="10961" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="10961" max="10961" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="10962" max="11197" width="9" style="4"/>
-    <col min="11198" max="11198" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11199" max="11199" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11200" max="11200" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11201" max="11201" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11202" max="11203" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11204" max="11205" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11206" max="11206" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11198" max="11198" width="2.796875" style="4" customWidth="1"/>
+    <col min="11199" max="11199" width="17.296875" style="4" customWidth="1"/>
+    <col min="11200" max="11200" width="6.796875" style="4" customWidth="1"/>
+    <col min="11201" max="11201" width="5.296875" style="4" customWidth="1"/>
+    <col min="11202" max="11203" width="6.296875" style="4" customWidth="1"/>
+    <col min="11204" max="11205" width="4.296875" style="4" customWidth="1"/>
+    <col min="11206" max="11206" width="3.8984375" style="4" customWidth="1"/>
     <col min="11207" max="11207" width="3" style="4" customWidth="1"/>
-    <col min="11208" max="11208" width="3.21875" style="4" customWidth="1"/>
+    <col min="11208" max="11208" width="3.19921875" style="4" customWidth="1"/>
     <col min="11209" max="11209" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11210" max="11210" width="6.77734375" style="4" customWidth="1"/>
+    <col min="11210" max="11210" width="6.796875" style="4" customWidth="1"/>
     <col min="11211" max="11213" width="9" style="4"/>
-    <col min="11214" max="11214" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11214" max="11214" width="11.69921875" style="4" customWidth="1"/>
     <col min="11215" max="11215" width="7" style="4" customWidth="1"/>
     <col min="11216" max="11216" width="9" style="4"/>
-    <col min="11217" max="11217" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11217" max="11217" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="11218" max="11453" width="9" style="4"/>
-    <col min="11454" max="11454" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11455" max="11455" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11456" max="11456" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11457" max="11457" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11458" max="11459" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11460" max="11461" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11462" max="11462" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11454" max="11454" width="2.796875" style="4" customWidth="1"/>
+    <col min="11455" max="11455" width="17.296875" style="4" customWidth="1"/>
+    <col min="11456" max="11456" width="6.796875" style="4" customWidth="1"/>
+    <col min="11457" max="11457" width="5.296875" style="4" customWidth="1"/>
+    <col min="11458" max="11459" width="6.296875" style="4" customWidth="1"/>
+    <col min="11460" max="11461" width="4.296875" style="4" customWidth="1"/>
+    <col min="11462" max="11462" width="3.8984375" style="4" customWidth="1"/>
     <col min="11463" max="11463" width="3" style="4" customWidth="1"/>
-    <col min="11464" max="11464" width="3.21875" style="4" customWidth="1"/>
+    <col min="11464" max="11464" width="3.19921875" style="4" customWidth="1"/>
     <col min="11465" max="11465" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11466" max="11466" width="6.77734375" style="4" customWidth="1"/>
+    <col min="11466" max="11466" width="6.796875" style="4" customWidth="1"/>
     <col min="11467" max="11469" width="9" style="4"/>
-    <col min="11470" max="11470" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11470" max="11470" width="11.69921875" style="4" customWidth="1"/>
     <col min="11471" max="11471" width="7" style="4" customWidth="1"/>
     <col min="11472" max="11472" width="9" style="4"/>
-    <col min="11473" max="11473" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11473" max="11473" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="11474" max="11709" width="9" style="4"/>
-    <col min="11710" max="11710" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11711" max="11711" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11712" max="11712" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11713" max="11713" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11714" max="11715" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11716" max="11717" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11718" max="11718" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11710" max="11710" width="2.796875" style="4" customWidth="1"/>
+    <col min="11711" max="11711" width="17.296875" style="4" customWidth="1"/>
+    <col min="11712" max="11712" width="6.796875" style="4" customWidth="1"/>
+    <col min="11713" max="11713" width="5.296875" style="4" customWidth="1"/>
+    <col min="11714" max="11715" width="6.296875" style="4" customWidth="1"/>
+    <col min="11716" max="11717" width="4.296875" style="4" customWidth="1"/>
+    <col min="11718" max="11718" width="3.8984375" style="4" customWidth="1"/>
     <col min="11719" max="11719" width="3" style="4" customWidth="1"/>
-    <col min="11720" max="11720" width="3.21875" style="4" customWidth="1"/>
+    <col min="11720" max="11720" width="3.19921875" style="4" customWidth="1"/>
     <col min="11721" max="11721" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11722" max="11722" width="6.77734375" style="4" customWidth="1"/>
+    <col min="11722" max="11722" width="6.796875" style="4" customWidth="1"/>
     <col min="11723" max="11725" width="9" style="4"/>
-    <col min="11726" max="11726" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11726" max="11726" width="11.69921875" style="4" customWidth="1"/>
     <col min="11727" max="11727" width="7" style="4" customWidth="1"/>
     <col min="11728" max="11728" width="9" style="4"/>
-    <col min="11729" max="11729" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11729" max="11729" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="11730" max="11965" width="9" style="4"/>
-    <col min="11966" max="11966" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11967" max="11967" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11968" max="11968" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11969" max="11969" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11970" max="11971" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11972" max="11973" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11974" max="11974" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11966" max="11966" width="2.796875" style="4" customWidth="1"/>
+    <col min="11967" max="11967" width="17.296875" style="4" customWidth="1"/>
+    <col min="11968" max="11968" width="6.796875" style="4" customWidth="1"/>
+    <col min="11969" max="11969" width="5.296875" style="4" customWidth="1"/>
+    <col min="11970" max="11971" width="6.296875" style="4" customWidth="1"/>
+    <col min="11972" max="11973" width="4.296875" style="4" customWidth="1"/>
+    <col min="11974" max="11974" width="3.8984375" style="4" customWidth="1"/>
     <col min="11975" max="11975" width="3" style="4" customWidth="1"/>
-    <col min="11976" max="11976" width="3.21875" style="4" customWidth="1"/>
+    <col min="11976" max="11976" width="3.19921875" style="4" customWidth="1"/>
     <col min="11977" max="11977" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11978" max="11978" width="6.77734375" style="4" customWidth="1"/>
+    <col min="11978" max="11978" width="6.796875" style="4" customWidth="1"/>
     <col min="11979" max="11981" width="9" style="4"/>
-    <col min="11982" max="11982" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11982" max="11982" width="11.69921875" style="4" customWidth="1"/>
     <col min="11983" max="11983" width="7" style="4" customWidth="1"/>
     <col min="11984" max="11984" width="9" style="4"/>
-    <col min="11985" max="11985" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11985" max="11985" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="11986" max="12221" width="9" style="4"/>
-    <col min="12222" max="12222" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12223" max="12223" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12224" max="12224" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12225" max="12225" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12226" max="12227" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12228" max="12229" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12230" max="12230" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12222" max="12222" width="2.796875" style="4" customWidth="1"/>
+    <col min="12223" max="12223" width="17.296875" style="4" customWidth="1"/>
+    <col min="12224" max="12224" width="6.796875" style="4" customWidth="1"/>
+    <col min="12225" max="12225" width="5.296875" style="4" customWidth="1"/>
+    <col min="12226" max="12227" width="6.296875" style="4" customWidth="1"/>
+    <col min="12228" max="12229" width="4.296875" style="4" customWidth="1"/>
+    <col min="12230" max="12230" width="3.8984375" style="4" customWidth="1"/>
     <col min="12231" max="12231" width="3" style="4" customWidth="1"/>
-    <col min="12232" max="12232" width="3.21875" style="4" customWidth="1"/>
+    <col min="12232" max="12232" width="3.19921875" style="4" customWidth="1"/>
     <col min="12233" max="12233" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12234" max="12234" width="6.77734375" style="4" customWidth="1"/>
+    <col min="12234" max="12234" width="6.796875" style="4" customWidth="1"/>
     <col min="12235" max="12237" width="9" style="4"/>
-    <col min="12238" max="12238" width="11.6640625" style="4" customWidth="1"/>
+    <col min="12238" max="12238" width="11.69921875" style="4" customWidth="1"/>
     <col min="12239" max="12239" width="7" style="4" customWidth="1"/>
     <col min="12240" max="12240" width="9" style="4"/>
-    <col min="12241" max="12241" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="12241" max="12241" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="12242" max="12477" width="9" style="4"/>
-    <col min="12478" max="12478" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12479" max="12479" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12480" max="12480" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12481" max="12481" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12482" max="12483" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12484" max="12485" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12486" max="12486" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12478" max="12478" width="2.796875" style="4" customWidth="1"/>
+    <col min="12479" max="12479" width="17.296875" style="4" customWidth="1"/>
+    <col min="12480" max="12480" width="6.796875" style="4" customWidth="1"/>
+    <col min="12481" max="12481" width="5.296875" style="4" customWidth="1"/>
+    <col min="12482" max="12483" width="6.296875" style="4" customWidth="1"/>
+    <col min="12484" max="12485" width="4.296875" style="4" customWidth="1"/>
+    <col min="12486" max="12486" width="3.8984375" style="4" customWidth="1"/>
     <col min="12487" max="12487" width="3" style="4" customWidth="1"/>
-    <col min="12488" max="12488" width="3.21875" style="4" customWidth="1"/>
+    <col min="12488" max="12488" width="3.19921875" style="4" customWidth="1"/>
     <col min="12489" max="12489" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12490" max="12490" width="6.77734375" style="4" customWidth="1"/>
+    <col min="12490" max="12490" width="6.796875" style="4" customWidth="1"/>
     <col min="12491" max="12493" width="9" style="4"/>
-    <col min="12494" max="12494" width="11.6640625" style="4" customWidth="1"/>
+    <col min="12494" max="12494" width="11.69921875" style="4" customWidth="1"/>
     <col min="12495" max="12495" width="7" style="4" customWidth="1"/>
     <col min="12496" max="12496" width="9" style="4"/>
-    <col min="12497" max="12497" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="12497" max="12497" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="12498" max="12733" width="9" style="4"/>
-    <col min="12734" max="12734" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12735" max="12735" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12736" max="12736" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12737" max="12737" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12738" max="12739" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12740" max="12741" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12742" max="12742" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12734" max="12734" width="2.796875" style="4" customWidth="1"/>
+    <col min="12735" max="12735" width="17.296875" style="4" customWidth="1"/>
+    <col min="12736" max="12736" width="6.796875" style="4" customWidth="1"/>
+    <col min="12737" max="12737" width="5.296875" style="4" customWidth="1"/>
+    <col min="12738" max="12739" width="6.296875" style="4" customWidth="1"/>
+    <col min="12740" max="12741" width="4.296875" style="4" customWidth="1"/>
+    <col min="12742" max="12742" width="3.8984375" style="4" customWidth="1"/>
     <col min="12743" max="12743" width="3" style="4" customWidth="1"/>
-    <col min="12744" max="12744" width="3.21875" style="4" customWidth="1"/>
+    <col min="12744" max="12744" width="3.19921875" style="4" customWidth="1"/>
     <col min="12745" max="12745" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12746" max="12746" width="6.77734375" style="4" customWidth="1"/>
+    <col min="12746" max="12746" width="6.796875" style="4" customWidth="1"/>
     <col min="12747" max="12749" width="9" style="4"/>
-    <col min="12750" max="12750" width="11.6640625" style="4" customWidth="1"/>
+    <col min="12750" max="12750" width="11.69921875" style="4" customWidth="1"/>
     <col min="12751" max="12751" width="7" style="4" customWidth="1"/>
     <col min="12752" max="12752" width="9" style="4"/>
-    <col min="12753" max="12753" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="12753" max="12753" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="12754" max="12989" width="9" style="4"/>
-    <col min="12990" max="12990" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12991" max="12991" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12992" max="12992" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12993" max="12993" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12994" max="12995" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12996" max="12997" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12998" max="12998" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12990" max="12990" width="2.796875" style="4" customWidth="1"/>
+    <col min="12991" max="12991" width="17.296875" style="4" customWidth="1"/>
+    <col min="12992" max="12992" width="6.796875" style="4" customWidth="1"/>
+    <col min="12993" max="12993" width="5.296875" style="4" customWidth="1"/>
+    <col min="12994" max="12995" width="6.296875" style="4" customWidth="1"/>
+    <col min="12996" max="12997" width="4.296875" style="4" customWidth="1"/>
+    <col min="12998" max="12998" width="3.8984375" style="4" customWidth="1"/>
     <col min="12999" max="12999" width="3" style="4" customWidth="1"/>
-    <col min="13000" max="13000" width="3.21875" style="4" customWidth="1"/>
+    <col min="13000" max="13000" width="3.19921875" style="4" customWidth="1"/>
     <col min="13001" max="13001" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13002" max="13002" width="6.77734375" style="4" customWidth="1"/>
+    <col min="13002" max="13002" width="6.796875" style="4" customWidth="1"/>
     <col min="13003" max="13005" width="9" style="4"/>
-    <col min="13006" max="13006" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13006" max="13006" width="11.69921875" style="4" customWidth="1"/>
     <col min="13007" max="13007" width="7" style="4" customWidth="1"/>
     <col min="13008" max="13008" width="9" style="4"/>
-    <col min="13009" max="13009" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13009" max="13009" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="13010" max="13245" width="9" style="4"/>
-    <col min="13246" max="13246" width="2.77734375" style="4" customWidth="1"/>
-    <col min="13247" max="13247" width="17.33203125" style="4" customWidth="1"/>
-    <col min="13248" max="13248" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13249" max="13249" width="5.33203125" style="4" customWidth="1"/>
-    <col min="13250" max="13251" width="6.33203125" style="4" customWidth="1"/>
-    <col min="13252" max="13253" width="4.33203125" style="4" customWidth="1"/>
-    <col min="13254" max="13254" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13246" max="13246" width="2.796875" style="4" customWidth="1"/>
+    <col min="13247" max="13247" width="17.296875" style="4" customWidth="1"/>
+    <col min="13248" max="13248" width="6.796875" style="4" customWidth="1"/>
+    <col min="13249" max="13249" width="5.296875" style="4" customWidth="1"/>
+    <col min="13250" max="13251" width="6.296875" style="4" customWidth="1"/>
+    <col min="13252" max="13253" width="4.296875" style="4" customWidth="1"/>
+    <col min="13254" max="13254" width="3.8984375" style="4" customWidth="1"/>
     <col min="13255" max="13255" width="3" style="4" customWidth="1"/>
-    <col min="13256" max="13256" width="3.21875" style="4" customWidth="1"/>
+    <col min="13256" max="13256" width="3.19921875" style="4" customWidth="1"/>
     <col min="13257" max="13257" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13258" max="13258" width="6.77734375" style="4" customWidth="1"/>
+    <col min="13258" max="13258" width="6.796875" style="4" customWidth="1"/>
     <col min="13259" max="13261" width="9" style="4"/>
-    <col min="13262" max="13262" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13262" max="13262" width="11.69921875" style="4" customWidth="1"/>
     <col min="13263" max="13263" width="7" style="4" customWidth="1"/>
     <col min="13264" max="13264" width="9" style="4"/>
-    <col min="13265" max="13265" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13265" max="13265" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="13266" max="13501" width="9" style="4"/>
-    <col min="13502" max="13502" width="2.77734375" style="4" customWidth="1"/>
-    <col min="13503" max="13503" width="17.33203125" style="4" customWidth="1"/>
-    <col min="13504" max="13504" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13505" max="13505" width="5.33203125" style="4" customWidth="1"/>
-    <col min="13506" max="13507" width="6.33203125" style="4" customWidth="1"/>
-    <col min="13508" max="13509" width="4.33203125" style="4" customWidth="1"/>
-    <col min="13510" max="13510" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13502" max="13502" width="2.796875" style="4" customWidth="1"/>
+    <col min="13503" max="13503" width="17.296875" style="4" customWidth="1"/>
+    <col min="13504" max="13504" width="6.796875" style="4" customWidth="1"/>
+    <col min="13505" max="13505" width="5.296875" style="4" customWidth="1"/>
+    <col min="13506" max="13507" width="6.296875" style="4" customWidth="1"/>
+    <col min="13508" max="13509" width="4.296875" style="4" customWidth="1"/>
+    <col min="13510" max="13510" width="3.8984375" style="4" customWidth="1"/>
     <col min="13511" max="13511" width="3" style="4" customWidth="1"/>
-    <col min="13512" max="13512" width="3.21875" style="4" customWidth="1"/>
+    <col min="13512" max="13512" width="3.19921875" style="4" customWidth="1"/>
     <col min="13513" max="13513" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13514" max="13514" width="6.77734375" style="4" customWidth="1"/>
+    <col min="13514" max="13514" width="6.796875" style="4" customWidth="1"/>
     <col min="13515" max="13517" width="9" style="4"/>
-    <col min="13518" max="13518" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13518" max="13518" width="11.69921875" style="4" customWidth="1"/>
     <col min="13519" max="13519" width="7" style="4" customWidth="1"/>
     <col min="13520" max="13520" width="9" style="4"/>
-    <col min="13521" max="13521" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13521" max="13521" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="13522" max="13757" width="9" style="4"/>
-    <col min="13758" max="13758" width="2.77734375" style="4" customWidth="1"/>
-    <col min="13759" max="13759" width="17.33203125" style="4" customWidth="1"/>
-    <col min="13760" max="13760" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13761" max="13761" width="5.33203125" style="4" customWidth="1"/>
-    <col min="13762" max="13763" width="6.33203125" style="4" customWidth="1"/>
-    <col min="13764" max="13765" width="4.33203125" style="4" customWidth="1"/>
-    <col min="13766" max="13766" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13758" max="13758" width="2.796875" style="4" customWidth="1"/>
+    <col min="13759" max="13759" width="17.296875" style="4" customWidth="1"/>
+    <col min="13760" max="13760" width="6.796875" style="4" customWidth="1"/>
+    <col min="13761" max="13761" width="5.296875" style="4" customWidth="1"/>
+    <col min="13762" max="13763" width="6.296875" style="4" customWidth="1"/>
+    <col min="13764" max="13765" width="4.296875" style="4" customWidth="1"/>
+    <col min="13766" max="13766" width="3.8984375" style="4" customWidth="1"/>
     <col min="13767" max="13767" width="3" style="4" customWidth="1"/>
-    <col min="13768" max="13768" width="3.21875" style="4" customWidth="1"/>
+    <col min="13768" max="13768" width="3.19921875" style="4" customWidth="1"/>
     <col min="13769" max="13769" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13770" max="13770" width="6.77734375" style="4" customWidth="1"/>
+    <col min="13770" max="13770" width="6.796875" style="4" customWidth="1"/>
     <col min="13771" max="13773" width="9" style="4"/>
-    <col min="13774" max="13774" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13774" max="13774" width="11.69921875" style="4" customWidth="1"/>
     <col min="13775" max="13775" width="7" style="4" customWidth="1"/>
     <col min="13776" max="13776" width="9" style="4"/>
-    <col min="13777" max="13777" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13777" max="13777" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="13778" max="14013" width="9" style="4"/>
-    <col min="14014" max="14014" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14015" max="14015" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14016" max="14016" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14017" max="14017" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14018" max="14019" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14020" max="14021" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14022" max="14022" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14014" max="14014" width="2.796875" style="4" customWidth="1"/>
+    <col min="14015" max="14015" width="17.296875" style="4" customWidth="1"/>
+    <col min="14016" max="14016" width="6.796875" style="4" customWidth="1"/>
+    <col min="14017" max="14017" width="5.296875" style="4" customWidth="1"/>
+    <col min="14018" max="14019" width="6.296875" style="4" customWidth="1"/>
+    <col min="14020" max="14021" width="4.296875" style="4" customWidth="1"/>
+    <col min="14022" max="14022" width="3.8984375" style="4" customWidth="1"/>
     <col min="14023" max="14023" width="3" style="4" customWidth="1"/>
-    <col min="14024" max="14024" width="3.21875" style="4" customWidth="1"/>
+    <col min="14024" max="14024" width="3.19921875" style="4" customWidth="1"/>
     <col min="14025" max="14025" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14026" max="14026" width="6.77734375" style="4" customWidth="1"/>
+    <col min="14026" max="14026" width="6.796875" style="4" customWidth="1"/>
     <col min="14027" max="14029" width="9" style="4"/>
-    <col min="14030" max="14030" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14030" max="14030" width="11.69921875" style="4" customWidth="1"/>
     <col min="14031" max="14031" width="7" style="4" customWidth="1"/>
     <col min="14032" max="14032" width="9" style="4"/>
-    <col min="14033" max="14033" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14033" max="14033" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="14034" max="14269" width="9" style="4"/>
-    <col min="14270" max="14270" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14271" max="14271" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14272" max="14272" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14273" max="14273" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14274" max="14275" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14276" max="14277" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14278" max="14278" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14270" max="14270" width="2.796875" style="4" customWidth="1"/>
+    <col min="14271" max="14271" width="17.296875" style="4" customWidth="1"/>
+    <col min="14272" max="14272" width="6.796875" style="4" customWidth="1"/>
+    <col min="14273" max="14273" width="5.296875" style="4" customWidth="1"/>
+    <col min="14274" max="14275" width="6.296875" style="4" customWidth="1"/>
+    <col min="14276" max="14277" width="4.296875" style="4" customWidth="1"/>
+    <col min="14278" max="14278" width="3.8984375" style="4" customWidth="1"/>
     <col min="14279" max="14279" width="3" style="4" customWidth="1"/>
-    <col min="14280" max="14280" width="3.21875" style="4" customWidth="1"/>
+    <col min="14280" max="14280" width="3.19921875" style="4" customWidth="1"/>
     <col min="14281" max="14281" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14282" max="14282" width="6.77734375" style="4" customWidth="1"/>
+    <col min="14282" max="14282" width="6.796875" style="4" customWidth="1"/>
     <col min="14283" max="14285" width="9" style="4"/>
-    <col min="14286" max="14286" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14286" max="14286" width="11.69921875" style="4" customWidth="1"/>
     <col min="14287" max="14287" width="7" style="4" customWidth="1"/>
     <col min="14288" max="14288" width="9" style="4"/>
-    <col min="14289" max="14289" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14289" max="14289" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="14290" max="14525" width="9" style="4"/>
-    <col min="14526" max="14526" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14527" max="14527" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14528" max="14528" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14529" max="14529" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14530" max="14531" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14532" max="14533" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14534" max="14534" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14526" max="14526" width="2.796875" style="4" customWidth="1"/>
+    <col min="14527" max="14527" width="17.296875" style="4" customWidth="1"/>
+    <col min="14528" max="14528" width="6.796875" style="4" customWidth="1"/>
+    <col min="14529" max="14529" width="5.296875" style="4" customWidth="1"/>
+    <col min="14530" max="14531" width="6.296875" style="4" customWidth="1"/>
+    <col min="14532" max="14533" width="4.296875" style="4" customWidth="1"/>
+    <col min="14534" max="14534" width="3.8984375" style="4" customWidth="1"/>
     <col min="14535" max="14535" width="3" style="4" customWidth="1"/>
-    <col min="14536" max="14536" width="3.21875" style="4" customWidth="1"/>
+    <col min="14536" max="14536" width="3.19921875" style="4" customWidth="1"/>
     <col min="14537" max="14537" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14538" max="14538" width="6.77734375" style="4" customWidth="1"/>
+    <col min="14538" max="14538" width="6.796875" style="4" customWidth="1"/>
     <col min="14539" max="14541" width="9" style="4"/>
-    <col min="14542" max="14542" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14542" max="14542" width="11.69921875" style="4" customWidth="1"/>
     <col min="14543" max="14543" width="7" style="4" customWidth="1"/>
     <col min="14544" max="14544" width="9" style="4"/>
-    <col min="14545" max="14545" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14545" max="14545" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="14546" max="14781" width="9" style="4"/>
-    <col min="14782" max="14782" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14783" max="14783" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14784" max="14784" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14785" max="14785" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14786" max="14787" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14788" max="14789" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14790" max="14790" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14782" max="14782" width="2.796875" style="4" customWidth="1"/>
+    <col min="14783" max="14783" width="17.296875" style="4" customWidth="1"/>
+    <col min="14784" max="14784" width="6.796875" style="4" customWidth="1"/>
+    <col min="14785" max="14785" width="5.296875" style="4" customWidth="1"/>
+    <col min="14786" max="14787" width="6.296875" style="4" customWidth="1"/>
+    <col min="14788" max="14789" width="4.296875" style="4" customWidth="1"/>
+    <col min="14790" max="14790" width="3.8984375" style="4" customWidth="1"/>
     <col min="14791" max="14791" width="3" style="4" customWidth="1"/>
-    <col min="14792" max="14792" width="3.21875" style="4" customWidth="1"/>
+    <col min="14792" max="14792" width="3.19921875" style="4" customWidth="1"/>
     <col min="14793" max="14793" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14794" max="14794" width="6.77734375" style="4" customWidth="1"/>
+    <col min="14794" max="14794" width="6.796875" style="4" customWidth="1"/>
     <col min="14795" max="14797" width="9" style="4"/>
-    <col min="14798" max="14798" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14798" max="14798" width="11.69921875" style="4" customWidth="1"/>
     <col min="14799" max="14799" width="7" style="4" customWidth="1"/>
     <col min="14800" max="14800" width="9" style="4"/>
-    <col min="14801" max="14801" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14801" max="14801" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="14802" max="15037" width="9" style="4"/>
-    <col min="15038" max="15038" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15039" max="15039" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15040" max="15040" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15041" max="15041" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15042" max="15043" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15044" max="15045" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15046" max="15046" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15038" max="15038" width="2.796875" style="4" customWidth="1"/>
+    <col min="15039" max="15039" width="17.296875" style="4" customWidth="1"/>
+    <col min="15040" max="15040" width="6.796875" style="4" customWidth="1"/>
+    <col min="15041" max="15041" width="5.296875" style="4" customWidth="1"/>
+    <col min="15042" max="15043" width="6.296875" style="4" customWidth="1"/>
+    <col min="15044" max="15045" width="4.296875" style="4" customWidth="1"/>
+    <col min="15046" max="15046" width="3.8984375" style="4" customWidth="1"/>
     <col min="15047" max="15047" width="3" style="4" customWidth="1"/>
-    <col min="15048" max="15048" width="3.21875" style="4" customWidth="1"/>
+    <col min="15048" max="15048" width="3.19921875" style="4" customWidth="1"/>
     <col min="15049" max="15049" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15050" max="15050" width="6.77734375" style="4" customWidth="1"/>
+    <col min="15050" max="15050" width="6.796875" style="4" customWidth="1"/>
     <col min="15051" max="15053" width="9" style="4"/>
-    <col min="15054" max="15054" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15054" max="15054" width="11.69921875" style="4" customWidth="1"/>
     <col min="15055" max="15055" width="7" style="4" customWidth="1"/>
     <col min="15056" max="15056" width="9" style="4"/>
-    <col min="15057" max="15057" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="15057" max="15057" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="15058" max="15293" width="9" style="4"/>
-    <col min="15294" max="15294" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15295" max="15295" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15296" max="15296" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15297" max="15297" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15298" max="15299" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15300" max="15301" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15302" max="15302" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15294" max="15294" width="2.796875" style="4" customWidth="1"/>
+    <col min="15295" max="15295" width="17.296875" style="4" customWidth="1"/>
+    <col min="15296" max="15296" width="6.796875" style="4" customWidth="1"/>
+    <col min="15297" max="15297" width="5.296875" style="4" customWidth="1"/>
+    <col min="15298" max="15299" width="6.296875" style="4" customWidth="1"/>
+    <col min="15300" max="15301" width="4.296875" style="4" customWidth="1"/>
+    <col min="15302" max="15302" width="3.8984375" style="4" customWidth="1"/>
     <col min="15303" max="15303" width="3" style="4" customWidth="1"/>
-    <col min="15304" max="15304" width="3.21875" style="4" customWidth="1"/>
+    <col min="15304" max="15304" width="3.19921875" style="4" customWidth="1"/>
     <col min="15305" max="15305" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15306" max="15306" width="6.77734375" style="4" customWidth="1"/>
+    <col min="15306" max="15306" width="6.796875" style="4" customWidth="1"/>
     <col min="15307" max="15309" width="9" style="4"/>
-    <col min="15310" max="15310" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15310" max="15310" width="11.69921875" style="4" customWidth="1"/>
     <col min="15311" max="15311" width="7" style="4" customWidth="1"/>
     <col min="15312" max="15312" width="9" style="4"/>
-    <col min="15313" max="15313" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="15313" max="15313" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="15314" max="15549" width="9" style="4"/>
-    <col min="15550" max="15550" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15551" max="15551" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15552" max="15552" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15553" max="15553" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15554" max="15555" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15556" max="15557" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15558" max="15558" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15550" max="15550" width="2.796875" style="4" customWidth="1"/>
+    <col min="15551" max="15551" width="17.296875" style="4" customWidth="1"/>
+    <col min="15552" max="15552" width="6.796875" style="4" customWidth="1"/>
+    <col min="15553" max="15553" width="5.296875" style="4" customWidth="1"/>
+    <col min="15554" max="15555" width="6.296875" style="4" customWidth="1"/>
+    <col min="15556" max="15557" width="4.296875" style="4" customWidth="1"/>
+    <col min="15558" max="15558" width="3.8984375" style="4" customWidth="1"/>
     <col min="15559" max="15559" width="3" style="4" customWidth="1"/>
-    <col min="15560" max="15560" width="3.21875" style="4" customWidth="1"/>
+    <col min="15560" max="15560" width="3.19921875" style="4" customWidth="1"/>
     <col min="15561" max="15561" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15562" max="15562" width="6.77734375" style="4" customWidth="1"/>
+    <col min="15562" max="15562" width="6.796875" style="4" customWidth="1"/>
     <col min="15563" max="15565" width="9" style="4"/>
-    <col min="15566" max="15566" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15566" max="15566" width="11.69921875" style="4" customWidth="1"/>
     <col min="15567" max="15567" width="7" style="4" customWidth="1"/>
     <col min="15568" max="15568" width="9" style="4"/>
-    <col min="15569" max="15569" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="15569" max="15569" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="15570" max="15805" width="9" style="4"/>
-    <col min="15806" max="15806" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15807" max="15807" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15808" max="15808" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15809" max="15809" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15810" max="15811" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15812" max="15813" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15814" max="15814" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15806" max="15806" width="2.796875" style="4" customWidth="1"/>
+    <col min="15807" max="15807" width="17.296875" style="4" customWidth="1"/>
+    <col min="15808" max="15808" width="6.796875" style="4" customWidth="1"/>
+    <col min="15809" max="15809" width="5.296875" style="4" customWidth="1"/>
+    <col min="15810" max="15811" width="6.296875" style="4" customWidth="1"/>
+    <col min="15812" max="15813" width="4.296875" style="4" customWidth="1"/>
+    <col min="15814" max="15814" width="3.8984375" style="4" customWidth="1"/>
     <col min="15815" max="15815" width="3" style="4" customWidth="1"/>
-    <col min="15816" max="15816" width="3.21875" style="4" customWidth="1"/>
+    <col min="15816" max="15816" width="3.19921875" style="4" customWidth="1"/>
     <col min="15817" max="15817" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15818" max="15818" width="6.77734375" style="4" customWidth="1"/>
+    <col min="15818" max="15818" width="6.796875" style="4" customWidth="1"/>
     <col min="15819" max="15821" width="9" style="4"/>
-    <col min="15822" max="15822" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15822" max="15822" width="11.69921875" style="4" customWidth="1"/>
     <col min="15823" max="15823" width="7" style="4" customWidth="1"/>
     <col min="15824" max="15824" width="9" style="4"/>
-    <col min="15825" max="15825" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="15825" max="15825" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="15826" max="16061" width="9" style="4"/>
-    <col min="16062" max="16062" width="2.77734375" style="4" customWidth="1"/>
-    <col min="16063" max="16063" width="17.33203125" style="4" customWidth="1"/>
-    <col min="16064" max="16064" width="6.77734375" style="4" customWidth="1"/>
-    <col min="16065" max="16065" width="5.33203125" style="4" customWidth="1"/>
-    <col min="16066" max="16067" width="6.33203125" style="4" customWidth="1"/>
-    <col min="16068" max="16069" width="4.33203125" style="4" customWidth="1"/>
-    <col min="16070" max="16070" width="3.88671875" style="4" customWidth="1"/>
+    <col min="16062" max="16062" width="2.796875" style="4" customWidth="1"/>
+    <col min="16063" max="16063" width="17.296875" style="4" customWidth="1"/>
+    <col min="16064" max="16064" width="6.796875" style="4" customWidth="1"/>
+    <col min="16065" max="16065" width="5.296875" style="4" customWidth="1"/>
+    <col min="16066" max="16067" width="6.296875" style="4" customWidth="1"/>
+    <col min="16068" max="16069" width="4.296875" style="4" customWidth="1"/>
+    <col min="16070" max="16070" width="3.8984375" style="4" customWidth="1"/>
     <col min="16071" max="16071" width="3" style="4" customWidth="1"/>
-    <col min="16072" max="16072" width="3.21875" style="4" customWidth="1"/>
+    <col min="16072" max="16072" width="3.19921875" style="4" customWidth="1"/>
     <col min="16073" max="16073" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="16074" max="16074" width="6.77734375" style="4" customWidth="1"/>
+    <col min="16074" max="16074" width="6.796875" style="4" customWidth="1"/>
     <col min="16075" max="16077" width="9" style="4"/>
-    <col min="16078" max="16078" width="11.6640625" style="4" customWidth="1"/>
+    <col min="16078" max="16078" width="11.69921875" style="4" customWidth="1"/>
     <col min="16079" max="16079" width="7" style="4" customWidth="1"/>
     <col min="16080" max="16080" width="9" style="4"/>
-    <col min="16081" max="16081" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="16081" max="16081" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
     <col min="16082" max="16381" width="9" style="4"/>
     <col min="16382" max="16384" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="8.4" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="102"/>
+    <row r="1" spans="1:17" ht="8.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="90"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="24.75" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="78" t="s">
+    <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A2" s="71"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="79" t="s">
+      <c r="M2" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="80" t="s">
+      <c r="N2" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="99"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="26.25" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+    <row r="3" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="71"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
       <c r="L3" s="43"/>
       <c r="M3" s="41"/>
       <c r="N3" s="45"/>
-      <c r="O3" s="82"/>
+      <c r="O3" s="72"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="81"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A4" s="71"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
       <c r="L4" s="44"/>
       <c r="M4" s="42"/>
       <c r="N4" s="46"/>
-      <c r="O4" s="82"/>
+      <c r="O4" s="72"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="81"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A5" s="71"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
       <c r="L5" s="36" t="s">
         <v>24</v>
       </c>
@@ -3042,22 +3039,22 @@
       <c r="N5" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="82"/>
+      <c r="O5" s="72"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" ht="25.2" thickBot="1">
-      <c r="A6" s="81"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
+    <row r="6" spans="1:17" ht="25.2" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="71"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
       <c r="L6" s="38" t="s">
         <v>27</v>
       </c>
@@ -3067,669 +3064,669 @@
       <c r="N6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="82"/>
+      <c r="O6" s="72"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" ht="36" customHeight="1" thickTop="1">
-      <c r="A7" s="81"/>
-      <c r="B7" s="52" t="s">
+    <row r="7" spans="1:17" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="71"/>
+      <c r="B7" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="83"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="73"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="84"/>
+    <row r="8" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A8" s="71"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="74"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" ht="27.6">
-      <c r="A9" s="81"/>
-      <c r="B9" s="53" t="s">
+    <row r="9" spans="1:17" ht="27.6" x14ac:dyDescent="0.8">
+      <c r="A9" s="71"/>
+      <c r="B9" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="53" t="s">
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="85"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="81"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="86"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="75"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A10" s="71"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="76"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="81"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="86"/>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A11" s="71"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="76"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="81"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="86"/>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A12" s="71"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="76"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" ht="26.4">
-      <c r="A13" s="81"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="53" t="s">
+    <row r="13" spans="1:17" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A13" s="71"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="85"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="81"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="87"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="75"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A14" s="71"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="77"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="81"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="88"/>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A15" s="71"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="78"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="81"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="86"/>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A16" s="71"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="76"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="81"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="85"/>
-    </row>
-    <row r="18" spans="1:19" ht="26.4">
-      <c r="A18" s="81"/>
-      <c r="B18" s="53" t="s">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A17" s="71"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="75"/>
+    </row>
+    <row r="18" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A18" s="71"/>
+      <c r="B18" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="53" t="s">
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="56"/>
-      <c r="M18" s="56"/>
-      <c r="N18" s="56"/>
-      <c r="O18" s="85"/>
-    </row>
-    <row r="19" spans="1:19">
-      <c r="A19" s="81"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="60" t="s">
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="75"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A19" s="71"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="89"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="79"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="9"/>
     </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="81"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="60" t="s">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A20" s="71"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="85"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="75"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="81"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="61" t="s">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A21" s="71"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="90"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="80"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:19">
-      <c r="A22" s="81"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="85"/>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="81"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="85"/>
-    </row>
-    <row r="24" spans="1:19" ht="26.4">
-      <c r="A24" s="81"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="53" t="s">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A22" s="71"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="75"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A23" s="71"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="75"/>
+    </row>
+    <row r="24" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A24" s="71"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="L24" s="56"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="85"/>
-    </row>
-    <row r="25" spans="1:19">
-      <c r="A25" s="81"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="85"/>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="A26" s="81"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="85"/>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="A27" s="81"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="85"/>
-    </row>
-    <row r="28" spans="1:19" ht="26.4">
-      <c r="A28" s="81"/>
-      <c r="B28" s="53" t="s">
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="75"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A25" s="71"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="75"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A26" s="71"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="96"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="96"/>
+      <c r="O26" s="75"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A27" s="71"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="96"/>
+      <c r="O27" s="75"/>
+    </row>
+    <row r="28" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A28" s="71"/>
+      <c r="B28" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="85"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="96"/>
+      <c r="O28" s="75"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="S28" s="13"/>
     </row>
-    <row r="29" spans="1:19">
-      <c r="A29" s="81"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="82"/>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A29" s="71"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="96"/>
+      <c r="O29" s="72"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="81"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="82"/>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A30" s="71"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="96"/>
+      <c r="O30" s="72"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:19" ht="26.4">
-      <c r="A31" s="81"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="53" t="s">
+    <row r="31" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A31" s="71"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="L31" s="56"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="91"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="81"/>
       <c r="P31" s="16"/>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="81"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="91"/>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A32" s="71"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="81"/>
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" spans="1:27">
-      <c r="A33" s="81"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="91"/>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A33" s="71"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="96"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="81"/>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" spans="1:27">
-      <c r="A34" s="81"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="91"/>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A34" s="71"/>
+      <c r="B34" s="100"/>
+      <c r="C34" s="100"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="81"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" spans="1:27">
-      <c r="A35" s="81"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="82"/>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A35" s="71"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="96"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="96"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="72"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
     </row>
-    <row r="36" spans="1:27">
-      <c r="A36" s="81"/>
-      <c r="B36" s="73"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="82"/>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A36" s="71"/>
+      <c r="B36" s="95"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="95"/>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="96"/>
+      <c r="O36" s="72"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
-    <row r="37" spans="1:27">
-      <c r="A37" s="81"/>
-      <c r="B37" s="74"/>
-      <c r="C37" s="49"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="72"/>
-      <c r="L37" s="72"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="82"/>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A37" s="71"/>
+      <c r="B37" s="95"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="95"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="95"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="96"/>
+      <c r="O37" s="72"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
     </row>
-    <row r="38" spans="1:27">
-      <c r="A38" s="81"/>
-      <c r="B38" s="74"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="72"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="85"/>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A38" s="71"/>
+      <c r="B38" s="96"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="96"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="96"/>
+      <c r="N38" s="96"/>
+      <c r="O38" s="75"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="32.4" customHeight="1" thickBot="1">
-      <c r="A39" s="92" t="s">
+    <row r="39" spans="1:27" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A39" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="93"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="95"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="85"/>
       <c r="K39" s="96"/>
       <c r="L39" s="96"/>
       <c r="M39" s="96"/>
-      <c r="N39" s="97"/>
-      <c r="O39" s="98"/>
+      <c r="N39" s="96"/>
+      <c r="O39" s="86"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11"/>
     </row>
-    <row r="40" spans="1:27" ht="30" customHeight="1">
+    <row r="40" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B40" s="17"/>
       <c r="J40" s="20"/>
       <c r="K40" s="14"/>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.7">
       <c r="B41" s="18"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.7">
       <c r="B42" s="18"/>
       <c r="J42" s="6"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43" spans="1:27" ht="33" customHeight="1">
+    <row r="43" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B43" s="18"/>
       <c r="J43" s="6"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="1:27" ht="33.75" customHeight="1">
+    <row r="44" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B44" s="21"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
@@ -3740,7 +3737,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:27" ht="46.5" customHeight="1">
+    <row r="45" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B45" s="1"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
@@ -3751,7 +3748,7 @@
       <c r="I45" s="20"/>
       <c r="J45" s="14"/>
     </row>
-    <row r="46" spans="1:27" ht="27.75" customHeight="1">
+    <row r="46" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B46" s="22"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -3764,7 +3761,7 @@
       <c r="T46" s="24"/>
       <c r="U46" s="24"/>
     </row>
-    <row r="47" spans="1:27" ht="27.75" customHeight="1">
+    <row r="47" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B47" s="12"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -3784,7 +3781,7 @@
       <c r="Z47" s="24"/>
       <c r="AA47" s="24"/>
     </row>
-    <row r="48" spans="1:27" ht="21.75" customHeight="1">
+    <row r="48" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B48" s="12"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -3804,15 +3801,15 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="2:27">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B49" s="12"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
+      <c r="C49" s="99"/>
+      <c r="D49" s="99"/>
+      <c r="E49" s="99"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="99"/>
+      <c r="I49" s="99"/>
       <c r="J49" s="23"/>
       <c r="S49" s="12"/>
       <c r="T49" s="8"/>
@@ -3824,7 +3821,7 @@
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
     </row>
-    <row r="50" spans="2:27">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B50" s="22"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -3843,15 +3840,15 @@
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
     </row>
-    <row r="51" spans="2:27">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B51" s="26"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="98"/>
+      <c r="E51" s="98"/>
+      <c r="F51" s="98"/>
+      <c r="G51" s="98"/>
+      <c r="H51" s="98"/>
+      <c r="I51" s="98"/>
       <c r="S51" s="12"/>
       <c r="T51" s="27"/>
       <c r="U51" s="27"/>
@@ -3862,7 +3859,7 @@
       <c r="Z51" s="27"/>
       <c r="AA51" s="27"/>
     </row>
-    <row r="52" spans="2:27">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B52" s="22"/>
       <c r="C52" s="12"/>
       <c r="D52" s="14"/>
@@ -3881,7 +3878,7 @@
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
     </row>
-    <row r="53" spans="2:27">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.7">
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
@@ -3899,7 +3896,7 @@
       <c r="Z53" s="27"/>
       <c r="AA53" s="27"/>
     </row>
-    <row r="54" spans="2:27">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.7">
       <c r="C54" s="23"/>
       <c r="D54" s="23"/>
       <c r="E54" s="23"/>
@@ -3917,14 +3914,14 @@
       <c r="Z54" s="27"/>
       <c r="AA54" s="27"/>
     </row>
-    <row r="55" spans="2:27">
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="47"/>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.7">
+      <c r="C55" s="98"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
       <c r="S55" s="12"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
@@ -3935,7 +3932,7 @@
       <c r="Z55" s="27"/>
       <c r="AA55" s="27"/>
     </row>
-    <row r="56" spans="2:27">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S56" s="22"/>
       <c r="T56" s="28"/>
       <c r="U56" s="27"/>
@@ -3946,7 +3943,7 @@
       <c r="Z56" s="14"/>
       <c r="AA56" s="14"/>
     </row>
-    <row r="57" spans="2:27">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S57" s="26"/>
       <c r="T57" s="27"/>
       <c r="U57" s="27"/>
@@ -3957,7 +3954,7 @@
       <c r="Z57" s="27"/>
       <c r="AA57" s="23"/>
     </row>
-    <row r="58" spans="2:27">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S58" s="26"/>
       <c r="T58" s="12"/>
       <c r="U58" s="14"/>
@@ -3968,7 +3965,7 @@
       <c r="Z58" s="27"/>
       <c r="AA58" s="23"/>
     </row>
-    <row r="59" spans="2:27">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S59" s="22"/>
       <c r="T59" s="25"/>
       <c r="U59" s="25"/>
@@ -3979,7 +3976,7 @@
       <c r="Z59" s="14"/>
       <c r="AA59" s="14"/>
     </row>
-    <row r="60" spans="2:27" ht="20.25" customHeight="1">
+    <row r="60" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="T60" s="25"/>
       <c r="U60" s="25"/>
       <c r="V60" s="25"/>
@@ -3989,7 +3986,7 @@
       <c r="Z60" s="25"/>
       <c r="AA60" s="25"/>
     </row>
-    <row r="61" spans="2:27" ht="20.25" customHeight="1">
+    <row r="61" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="T61" s="27"/>
       <c r="U61" s="27"/>
       <c r="V61" s="25"/>
@@ -3999,7 +3996,7 @@
       <c r="Z61" s="25"/>
       <c r="AA61" s="25"/>
     </row>
-    <row r="62" spans="2:27">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.7">
       <c r="V62" s="27"/>
       <c r="W62" s="27"/>
       <c r="X62" s="27"/>
@@ -4007,15 +4004,44 @@
       <c r="Z62" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="33">
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
     <mergeCell ref="C55:I55"/>
     <mergeCell ref="C49:I49"/>
     <mergeCell ref="C51:I51"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B7:N7"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0"/>
-  <pageSetup paperSize="9" scale="84" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="81" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -4027,1192 +4053,1192 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AA62"/>
-  <sheetFormatPr defaultRowHeight="24.6"/>
+  <sheetFormatPr defaultRowHeight="24.6" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="2.296875" style="4" customWidth="1"/>
     <col min="2" max="2" width="4" style="4" customWidth="1"/>
-    <col min="3" max="4" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5" max="6" width="8.33203125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="4" customWidth="1"/>
+    <col min="3" max="4" width="6.796875" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.296875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="6.296875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="6.796875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="4.69921875" style="4" customWidth="1"/>
     <col min="10" max="10" width="5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="4" customWidth="1"/>
-    <col min="12" max="14" width="15.77734375" style="4" customWidth="1"/>
-    <col min="15" max="15" width="2.33203125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="8.88671875" style="4"/>
-    <col min="17" max="17" width="11.6640625" style="4" customWidth="1"/>
-    <col min="18" max="18" width="2.33203125" style="4" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="189" width="8.88671875" style="4"/>
-    <col min="190" max="190" width="2.77734375" style="4" customWidth="1"/>
-    <col min="191" max="191" width="17.33203125" style="4" customWidth="1"/>
-    <col min="192" max="192" width="6.77734375" style="4" customWidth="1"/>
-    <col min="193" max="193" width="5.33203125" style="4" customWidth="1"/>
-    <col min="194" max="195" width="6.33203125" style="4" customWidth="1"/>
-    <col min="196" max="197" width="4.33203125" style="4" customWidth="1"/>
-    <col min="198" max="198" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="12.296875" style="4" customWidth="1"/>
+    <col min="12" max="14" width="15.796875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="2.296875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="8.8984375" style="4"/>
+    <col min="17" max="17" width="11.69921875" style="4" customWidth="1"/>
+    <col min="18" max="18" width="2.296875" style="4" customWidth="1"/>
+    <col min="19" max="19" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="20" max="189" width="8.8984375" style="4"/>
+    <col min="190" max="190" width="2.796875" style="4" customWidth="1"/>
+    <col min="191" max="191" width="17.296875" style="4" customWidth="1"/>
+    <col min="192" max="192" width="6.796875" style="4" customWidth="1"/>
+    <col min="193" max="193" width="5.296875" style="4" customWidth="1"/>
+    <col min="194" max="195" width="6.296875" style="4" customWidth="1"/>
+    <col min="196" max="197" width="4.296875" style="4" customWidth="1"/>
+    <col min="198" max="198" width="3.8984375" style="4" customWidth="1"/>
     <col min="199" max="199" width="3" style="4" customWidth="1"/>
-    <col min="200" max="200" width="3.21875" style="4" customWidth="1"/>
+    <col min="200" max="200" width="3.19921875" style="4" customWidth="1"/>
     <col min="201" max="201" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="202" max="202" width="6.77734375" style="4" customWidth="1"/>
-    <col min="203" max="205" width="8.88671875" style="4"/>
-    <col min="206" max="206" width="11.6640625" style="4" customWidth="1"/>
+    <col min="202" max="202" width="6.796875" style="4" customWidth="1"/>
+    <col min="203" max="205" width="8.8984375" style="4"/>
+    <col min="206" max="206" width="11.69921875" style="4" customWidth="1"/>
     <col min="207" max="207" width="7" style="4" customWidth="1"/>
-    <col min="208" max="208" width="8.88671875" style="4"/>
-    <col min="209" max="209" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="210" max="445" width="8.88671875" style="4"/>
-    <col min="446" max="446" width="2.77734375" style="4" customWidth="1"/>
-    <col min="447" max="447" width="17.33203125" style="4" customWidth="1"/>
-    <col min="448" max="448" width="6.77734375" style="4" customWidth="1"/>
-    <col min="449" max="449" width="5.33203125" style="4" customWidth="1"/>
-    <col min="450" max="451" width="6.33203125" style="4" customWidth="1"/>
-    <col min="452" max="453" width="4.33203125" style="4" customWidth="1"/>
-    <col min="454" max="454" width="3.88671875" style="4" customWidth="1"/>
+    <col min="208" max="208" width="8.8984375" style="4"/>
+    <col min="209" max="209" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="210" max="445" width="8.8984375" style="4"/>
+    <col min="446" max="446" width="2.796875" style="4" customWidth="1"/>
+    <col min="447" max="447" width="17.296875" style="4" customWidth="1"/>
+    <col min="448" max="448" width="6.796875" style="4" customWidth="1"/>
+    <col min="449" max="449" width="5.296875" style="4" customWidth="1"/>
+    <col min="450" max="451" width="6.296875" style="4" customWidth="1"/>
+    <col min="452" max="453" width="4.296875" style="4" customWidth="1"/>
+    <col min="454" max="454" width="3.8984375" style="4" customWidth="1"/>
     <col min="455" max="455" width="3" style="4" customWidth="1"/>
-    <col min="456" max="456" width="3.21875" style="4" customWidth="1"/>
+    <col min="456" max="456" width="3.19921875" style="4" customWidth="1"/>
     <col min="457" max="457" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="458" max="458" width="6.77734375" style="4" customWidth="1"/>
-    <col min="459" max="461" width="8.88671875" style="4"/>
-    <col min="462" max="462" width="11.6640625" style="4" customWidth="1"/>
+    <col min="458" max="458" width="6.796875" style="4" customWidth="1"/>
+    <col min="459" max="461" width="8.8984375" style="4"/>
+    <col min="462" max="462" width="11.69921875" style="4" customWidth="1"/>
     <col min="463" max="463" width="7" style="4" customWidth="1"/>
-    <col min="464" max="464" width="8.88671875" style="4"/>
-    <col min="465" max="465" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="466" max="701" width="8.88671875" style="4"/>
-    <col min="702" max="702" width="2.77734375" style="4" customWidth="1"/>
-    <col min="703" max="703" width="17.33203125" style="4" customWidth="1"/>
-    <col min="704" max="704" width="6.77734375" style="4" customWidth="1"/>
-    <col min="705" max="705" width="5.33203125" style="4" customWidth="1"/>
-    <col min="706" max="707" width="6.33203125" style="4" customWidth="1"/>
-    <col min="708" max="709" width="4.33203125" style="4" customWidth="1"/>
-    <col min="710" max="710" width="3.88671875" style="4" customWidth="1"/>
+    <col min="464" max="464" width="8.8984375" style="4"/>
+    <col min="465" max="465" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="466" max="701" width="8.8984375" style="4"/>
+    <col min="702" max="702" width="2.796875" style="4" customWidth="1"/>
+    <col min="703" max="703" width="17.296875" style="4" customWidth="1"/>
+    <col min="704" max="704" width="6.796875" style="4" customWidth="1"/>
+    <col min="705" max="705" width="5.296875" style="4" customWidth="1"/>
+    <col min="706" max="707" width="6.296875" style="4" customWidth="1"/>
+    <col min="708" max="709" width="4.296875" style="4" customWidth="1"/>
+    <col min="710" max="710" width="3.8984375" style="4" customWidth="1"/>
     <col min="711" max="711" width="3" style="4" customWidth="1"/>
-    <col min="712" max="712" width="3.21875" style="4" customWidth="1"/>
+    <col min="712" max="712" width="3.19921875" style="4" customWidth="1"/>
     <col min="713" max="713" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="714" max="714" width="6.77734375" style="4" customWidth="1"/>
-    <col min="715" max="717" width="8.88671875" style="4"/>
-    <col min="718" max="718" width="11.6640625" style="4" customWidth="1"/>
+    <col min="714" max="714" width="6.796875" style="4" customWidth="1"/>
+    <col min="715" max="717" width="8.8984375" style="4"/>
+    <col min="718" max="718" width="11.69921875" style="4" customWidth="1"/>
     <col min="719" max="719" width="7" style="4" customWidth="1"/>
-    <col min="720" max="720" width="8.88671875" style="4"/>
-    <col min="721" max="721" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="722" max="957" width="8.88671875" style="4"/>
-    <col min="958" max="958" width="2.77734375" style="4" customWidth="1"/>
-    <col min="959" max="959" width="17.33203125" style="4" customWidth="1"/>
-    <col min="960" max="960" width="6.77734375" style="4" customWidth="1"/>
-    <col min="961" max="961" width="5.33203125" style="4" customWidth="1"/>
-    <col min="962" max="963" width="6.33203125" style="4" customWidth="1"/>
-    <col min="964" max="965" width="4.33203125" style="4" customWidth="1"/>
-    <col min="966" max="966" width="3.88671875" style="4" customWidth="1"/>
+    <col min="720" max="720" width="8.8984375" style="4"/>
+    <col min="721" max="721" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="722" max="957" width="8.8984375" style="4"/>
+    <col min="958" max="958" width="2.796875" style="4" customWidth="1"/>
+    <col min="959" max="959" width="17.296875" style="4" customWidth="1"/>
+    <col min="960" max="960" width="6.796875" style="4" customWidth="1"/>
+    <col min="961" max="961" width="5.296875" style="4" customWidth="1"/>
+    <col min="962" max="963" width="6.296875" style="4" customWidth="1"/>
+    <col min="964" max="965" width="4.296875" style="4" customWidth="1"/>
+    <col min="966" max="966" width="3.8984375" style="4" customWidth="1"/>
     <col min="967" max="967" width="3" style="4" customWidth="1"/>
-    <col min="968" max="968" width="3.21875" style="4" customWidth="1"/>
+    <col min="968" max="968" width="3.19921875" style="4" customWidth="1"/>
     <col min="969" max="969" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="970" max="970" width="6.77734375" style="4" customWidth="1"/>
-    <col min="971" max="973" width="8.88671875" style="4"/>
-    <col min="974" max="974" width="11.6640625" style="4" customWidth="1"/>
+    <col min="970" max="970" width="6.796875" style="4" customWidth="1"/>
+    <col min="971" max="973" width="8.8984375" style="4"/>
+    <col min="974" max="974" width="11.69921875" style="4" customWidth="1"/>
     <col min="975" max="975" width="7" style="4" customWidth="1"/>
-    <col min="976" max="976" width="8.88671875" style="4"/>
-    <col min="977" max="977" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="978" max="1213" width="8.88671875" style="4"/>
-    <col min="1214" max="1214" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1215" max="1215" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1216" max="1216" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1217" max="1217" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1218" max="1219" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1220" max="1221" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1222" max="1222" width="3.88671875" style="4" customWidth="1"/>
+    <col min="976" max="976" width="8.8984375" style="4"/>
+    <col min="977" max="977" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="978" max="1213" width="8.8984375" style="4"/>
+    <col min="1214" max="1214" width="2.796875" style="4" customWidth="1"/>
+    <col min="1215" max="1215" width="17.296875" style="4" customWidth="1"/>
+    <col min="1216" max="1216" width="6.796875" style="4" customWidth="1"/>
+    <col min="1217" max="1217" width="5.296875" style="4" customWidth="1"/>
+    <col min="1218" max="1219" width="6.296875" style="4" customWidth="1"/>
+    <col min="1220" max="1221" width="4.296875" style="4" customWidth="1"/>
+    <col min="1222" max="1222" width="3.8984375" style="4" customWidth="1"/>
     <col min="1223" max="1223" width="3" style="4" customWidth="1"/>
-    <col min="1224" max="1224" width="3.21875" style="4" customWidth="1"/>
+    <col min="1224" max="1224" width="3.19921875" style="4" customWidth="1"/>
     <col min="1225" max="1225" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1226" max="1226" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1227" max="1229" width="8.88671875" style="4"/>
-    <col min="1230" max="1230" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1226" max="1226" width="6.796875" style="4" customWidth="1"/>
+    <col min="1227" max="1229" width="8.8984375" style="4"/>
+    <col min="1230" max="1230" width="11.69921875" style="4" customWidth="1"/>
     <col min="1231" max="1231" width="7" style="4" customWidth="1"/>
-    <col min="1232" max="1232" width="8.88671875" style="4"/>
-    <col min="1233" max="1233" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="1234" max="1469" width="8.88671875" style="4"/>
-    <col min="1470" max="1470" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1471" max="1471" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1472" max="1472" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1473" max="1473" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1474" max="1475" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1476" max="1477" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1478" max="1478" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1232" max="1232" width="8.8984375" style="4"/>
+    <col min="1233" max="1233" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1234" max="1469" width="8.8984375" style="4"/>
+    <col min="1470" max="1470" width="2.796875" style="4" customWidth="1"/>
+    <col min="1471" max="1471" width="17.296875" style="4" customWidth="1"/>
+    <col min="1472" max="1472" width="6.796875" style="4" customWidth="1"/>
+    <col min="1473" max="1473" width="5.296875" style="4" customWidth="1"/>
+    <col min="1474" max="1475" width="6.296875" style="4" customWidth="1"/>
+    <col min="1476" max="1477" width="4.296875" style="4" customWidth="1"/>
+    <col min="1478" max="1478" width="3.8984375" style="4" customWidth="1"/>
     <col min="1479" max="1479" width="3" style="4" customWidth="1"/>
-    <col min="1480" max="1480" width="3.21875" style="4" customWidth="1"/>
+    <col min="1480" max="1480" width="3.19921875" style="4" customWidth="1"/>
     <col min="1481" max="1481" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1482" max="1482" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1483" max="1485" width="8.88671875" style="4"/>
-    <col min="1486" max="1486" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1482" max="1482" width="6.796875" style="4" customWidth="1"/>
+    <col min="1483" max="1485" width="8.8984375" style="4"/>
+    <col min="1486" max="1486" width="11.69921875" style="4" customWidth="1"/>
     <col min="1487" max="1487" width="7" style="4" customWidth="1"/>
-    <col min="1488" max="1488" width="8.88671875" style="4"/>
-    <col min="1489" max="1489" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="1490" max="1725" width="8.88671875" style="4"/>
-    <col min="1726" max="1726" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1727" max="1727" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1728" max="1728" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1729" max="1729" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1730" max="1731" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1732" max="1733" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1734" max="1734" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1488" max="1488" width="8.8984375" style="4"/>
+    <col min="1489" max="1489" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1490" max="1725" width="8.8984375" style="4"/>
+    <col min="1726" max="1726" width="2.796875" style="4" customWidth="1"/>
+    <col min="1727" max="1727" width="17.296875" style="4" customWidth="1"/>
+    <col min="1728" max="1728" width="6.796875" style="4" customWidth="1"/>
+    <col min="1729" max="1729" width="5.296875" style="4" customWidth="1"/>
+    <col min="1730" max="1731" width="6.296875" style="4" customWidth="1"/>
+    <col min="1732" max="1733" width="4.296875" style="4" customWidth="1"/>
+    <col min="1734" max="1734" width="3.8984375" style="4" customWidth="1"/>
     <col min="1735" max="1735" width="3" style="4" customWidth="1"/>
-    <col min="1736" max="1736" width="3.21875" style="4" customWidth="1"/>
+    <col min="1736" max="1736" width="3.19921875" style="4" customWidth="1"/>
     <col min="1737" max="1737" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1738" max="1738" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1739" max="1741" width="8.88671875" style="4"/>
-    <col min="1742" max="1742" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1738" max="1738" width="6.796875" style="4" customWidth="1"/>
+    <col min="1739" max="1741" width="8.8984375" style="4"/>
+    <col min="1742" max="1742" width="11.69921875" style="4" customWidth="1"/>
     <col min="1743" max="1743" width="7" style="4" customWidth="1"/>
-    <col min="1744" max="1744" width="8.88671875" style="4"/>
-    <col min="1745" max="1745" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="1746" max="1981" width="8.88671875" style="4"/>
-    <col min="1982" max="1982" width="2.77734375" style="4" customWidth="1"/>
-    <col min="1983" max="1983" width="17.33203125" style="4" customWidth="1"/>
-    <col min="1984" max="1984" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1985" max="1985" width="5.33203125" style="4" customWidth="1"/>
-    <col min="1986" max="1987" width="6.33203125" style="4" customWidth="1"/>
-    <col min="1988" max="1989" width="4.33203125" style="4" customWidth="1"/>
-    <col min="1990" max="1990" width="3.88671875" style="4" customWidth="1"/>
+    <col min="1744" max="1744" width="8.8984375" style="4"/>
+    <col min="1745" max="1745" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="1746" max="1981" width="8.8984375" style="4"/>
+    <col min="1982" max="1982" width="2.796875" style="4" customWidth="1"/>
+    <col min="1983" max="1983" width="17.296875" style="4" customWidth="1"/>
+    <col min="1984" max="1984" width="6.796875" style="4" customWidth="1"/>
+    <col min="1985" max="1985" width="5.296875" style="4" customWidth="1"/>
+    <col min="1986" max="1987" width="6.296875" style="4" customWidth="1"/>
+    <col min="1988" max="1989" width="4.296875" style="4" customWidth="1"/>
+    <col min="1990" max="1990" width="3.8984375" style="4" customWidth="1"/>
     <col min="1991" max="1991" width="3" style="4" customWidth="1"/>
-    <col min="1992" max="1992" width="3.21875" style="4" customWidth="1"/>
+    <col min="1992" max="1992" width="3.19921875" style="4" customWidth="1"/>
     <col min="1993" max="1993" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1994" max="1994" width="6.77734375" style="4" customWidth="1"/>
-    <col min="1995" max="1997" width="8.88671875" style="4"/>
-    <col min="1998" max="1998" width="11.6640625" style="4" customWidth="1"/>
+    <col min="1994" max="1994" width="6.796875" style="4" customWidth="1"/>
+    <col min="1995" max="1997" width="8.8984375" style="4"/>
+    <col min="1998" max="1998" width="11.69921875" style="4" customWidth="1"/>
     <col min="1999" max="1999" width="7" style="4" customWidth="1"/>
-    <col min="2000" max="2000" width="8.88671875" style="4"/>
-    <col min="2001" max="2001" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2002" max="2237" width="8.88671875" style="4"/>
-    <col min="2238" max="2238" width="2.77734375" style="4" customWidth="1"/>
-    <col min="2239" max="2239" width="17.33203125" style="4" customWidth="1"/>
-    <col min="2240" max="2240" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2241" max="2241" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2242" max="2243" width="6.33203125" style="4" customWidth="1"/>
-    <col min="2244" max="2245" width="4.33203125" style="4" customWidth="1"/>
-    <col min="2246" max="2246" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2000" max="2000" width="8.8984375" style="4"/>
+    <col min="2001" max="2001" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2002" max="2237" width="8.8984375" style="4"/>
+    <col min="2238" max="2238" width="2.796875" style="4" customWidth="1"/>
+    <col min="2239" max="2239" width="17.296875" style="4" customWidth="1"/>
+    <col min="2240" max="2240" width="6.796875" style="4" customWidth="1"/>
+    <col min="2241" max="2241" width="5.296875" style="4" customWidth="1"/>
+    <col min="2242" max="2243" width="6.296875" style="4" customWidth="1"/>
+    <col min="2244" max="2245" width="4.296875" style="4" customWidth="1"/>
+    <col min="2246" max="2246" width="3.8984375" style="4" customWidth="1"/>
     <col min="2247" max="2247" width="3" style="4" customWidth="1"/>
-    <col min="2248" max="2248" width="3.21875" style="4" customWidth="1"/>
+    <col min="2248" max="2248" width="3.19921875" style="4" customWidth="1"/>
     <col min="2249" max="2249" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2250" max="2250" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2251" max="2253" width="8.88671875" style="4"/>
-    <col min="2254" max="2254" width="11.6640625" style="4" customWidth="1"/>
+    <col min="2250" max="2250" width="6.796875" style="4" customWidth="1"/>
+    <col min="2251" max="2253" width="8.8984375" style="4"/>
+    <col min="2254" max="2254" width="11.69921875" style="4" customWidth="1"/>
     <col min="2255" max="2255" width="7" style="4" customWidth="1"/>
-    <col min="2256" max="2256" width="8.88671875" style="4"/>
-    <col min="2257" max="2257" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2258" max="2493" width="8.88671875" style="4"/>
-    <col min="2494" max="2494" width="2.77734375" style="4" customWidth="1"/>
-    <col min="2495" max="2495" width="17.33203125" style="4" customWidth="1"/>
-    <col min="2496" max="2496" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2497" max="2497" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2498" max="2499" width="6.33203125" style="4" customWidth="1"/>
-    <col min="2500" max="2501" width="4.33203125" style="4" customWidth="1"/>
-    <col min="2502" max="2502" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2256" max="2256" width="8.8984375" style="4"/>
+    <col min="2257" max="2257" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2258" max="2493" width="8.8984375" style="4"/>
+    <col min="2494" max="2494" width="2.796875" style="4" customWidth="1"/>
+    <col min="2495" max="2495" width="17.296875" style="4" customWidth="1"/>
+    <col min="2496" max="2496" width="6.796875" style="4" customWidth="1"/>
+    <col min="2497" max="2497" width="5.296875" style="4" customWidth="1"/>
+    <col min="2498" max="2499" width="6.296875" style="4" customWidth="1"/>
+    <col min="2500" max="2501" width="4.296875" style="4" customWidth="1"/>
+    <col min="2502" max="2502" width="3.8984375" style="4" customWidth="1"/>
     <col min="2503" max="2503" width="3" style="4" customWidth="1"/>
-    <col min="2504" max="2504" width="3.21875" style="4" customWidth="1"/>
+    <col min="2504" max="2504" width="3.19921875" style="4" customWidth="1"/>
     <col min="2505" max="2505" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2506" max="2506" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2507" max="2509" width="8.88671875" style="4"/>
-    <col min="2510" max="2510" width="11.6640625" style="4" customWidth="1"/>
+    <col min="2506" max="2506" width="6.796875" style="4" customWidth="1"/>
+    <col min="2507" max="2509" width="8.8984375" style="4"/>
+    <col min="2510" max="2510" width="11.69921875" style="4" customWidth="1"/>
     <col min="2511" max="2511" width="7" style="4" customWidth="1"/>
-    <col min="2512" max="2512" width="8.88671875" style="4"/>
-    <col min="2513" max="2513" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2514" max="2749" width="8.88671875" style="4"/>
-    <col min="2750" max="2750" width="2.77734375" style="4" customWidth="1"/>
-    <col min="2751" max="2751" width="17.33203125" style="4" customWidth="1"/>
-    <col min="2752" max="2752" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2753" max="2753" width="5.33203125" style="4" customWidth="1"/>
-    <col min="2754" max="2755" width="6.33203125" style="4" customWidth="1"/>
-    <col min="2756" max="2757" width="4.33203125" style="4" customWidth="1"/>
-    <col min="2758" max="2758" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2512" max="2512" width="8.8984375" style="4"/>
+    <col min="2513" max="2513" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2514" max="2749" width="8.8984375" style="4"/>
+    <col min="2750" max="2750" width="2.796875" style="4" customWidth="1"/>
+    <col min="2751" max="2751" width="17.296875" style="4" customWidth="1"/>
+    <col min="2752" max="2752" width="6.796875" style="4" customWidth="1"/>
+    <col min="2753" max="2753" width="5.296875" style="4" customWidth="1"/>
+    <col min="2754" max="2755" width="6.296875" style="4" customWidth="1"/>
+    <col min="2756" max="2757" width="4.296875" style="4" customWidth="1"/>
+    <col min="2758" max="2758" width="3.8984375" style="4" customWidth="1"/>
     <col min="2759" max="2759" width="3" style="4" customWidth="1"/>
-    <col min="2760" max="2760" width="3.21875" style="4" customWidth="1"/>
+    <col min="2760" max="2760" width="3.19921875" style="4" customWidth="1"/>
     <col min="2761" max="2761" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2762" max="2762" width="6.77734375" style="4" customWidth="1"/>
-    <col min="2763" max="2765" width="8.88671875" style="4"/>
-    <col min="2766" max="2766" width="11.6640625" style="4" customWidth="1"/>
+    <col min="2762" max="2762" width="6.796875" style="4" customWidth="1"/>
+    <col min="2763" max="2765" width="8.8984375" style="4"/>
+    <col min="2766" max="2766" width="11.69921875" style="4" customWidth="1"/>
     <col min="2767" max="2767" width="7" style="4" customWidth="1"/>
-    <col min="2768" max="2768" width="8.88671875" style="4"/>
-    <col min="2769" max="2769" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2770" max="3005" width="8.88671875" style="4"/>
-    <col min="3006" max="3006" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3007" max="3007" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3008" max="3008" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3009" max="3009" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3010" max="3011" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3012" max="3013" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3014" max="3014" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2768" max="2768" width="8.8984375" style="4"/>
+    <col min="2769" max="2769" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2770" max="3005" width="8.8984375" style="4"/>
+    <col min="3006" max="3006" width="2.796875" style="4" customWidth="1"/>
+    <col min="3007" max="3007" width="17.296875" style="4" customWidth="1"/>
+    <col min="3008" max="3008" width="6.796875" style="4" customWidth="1"/>
+    <col min="3009" max="3009" width="5.296875" style="4" customWidth="1"/>
+    <col min="3010" max="3011" width="6.296875" style="4" customWidth="1"/>
+    <col min="3012" max="3013" width="4.296875" style="4" customWidth="1"/>
+    <col min="3014" max="3014" width="3.8984375" style="4" customWidth="1"/>
     <col min="3015" max="3015" width="3" style="4" customWidth="1"/>
-    <col min="3016" max="3016" width="3.21875" style="4" customWidth="1"/>
+    <col min="3016" max="3016" width="3.19921875" style="4" customWidth="1"/>
     <col min="3017" max="3017" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3018" max="3018" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3019" max="3021" width="8.88671875" style="4"/>
-    <col min="3022" max="3022" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3018" max="3018" width="6.796875" style="4" customWidth="1"/>
+    <col min="3019" max="3021" width="8.8984375" style="4"/>
+    <col min="3022" max="3022" width="11.69921875" style="4" customWidth="1"/>
     <col min="3023" max="3023" width="7" style="4" customWidth="1"/>
-    <col min="3024" max="3024" width="8.88671875" style="4"/>
-    <col min="3025" max="3025" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3026" max="3261" width="8.88671875" style="4"/>
-    <col min="3262" max="3262" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3263" max="3263" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3264" max="3264" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3265" max="3265" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3266" max="3267" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3268" max="3269" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3270" max="3270" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3024" max="3024" width="8.8984375" style="4"/>
+    <col min="3025" max="3025" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3026" max="3261" width="8.8984375" style="4"/>
+    <col min="3262" max="3262" width="2.796875" style="4" customWidth="1"/>
+    <col min="3263" max="3263" width="17.296875" style="4" customWidth="1"/>
+    <col min="3264" max="3264" width="6.796875" style="4" customWidth="1"/>
+    <col min="3265" max="3265" width="5.296875" style="4" customWidth="1"/>
+    <col min="3266" max="3267" width="6.296875" style="4" customWidth="1"/>
+    <col min="3268" max="3269" width="4.296875" style="4" customWidth="1"/>
+    <col min="3270" max="3270" width="3.8984375" style="4" customWidth="1"/>
     <col min="3271" max="3271" width="3" style="4" customWidth="1"/>
-    <col min="3272" max="3272" width="3.21875" style="4" customWidth="1"/>
+    <col min="3272" max="3272" width="3.19921875" style="4" customWidth="1"/>
     <col min="3273" max="3273" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3274" max="3274" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3275" max="3277" width="8.88671875" style="4"/>
-    <col min="3278" max="3278" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3274" max="3274" width="6.796875" style="4" customWidth="1"/>
+    <col min="3275" max="3277" width="8.8984375" style="4"/>
+    <col min="3278" max="3278" width="11.69921875" style="4" customWidth="1"/>
     <col min="3279" max="3279" width="7" style="4" customWidth="1"/>
-    <col min="3280" max="3280" width="8.88671875" style="4"/>
-    <col min="3281" max="3281" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3282" max="3517" width="8.88671875" style="4"/>
-    <col min="3518" max="3518" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3519" max="3519" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3520" max="3520" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3521" max="3521" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3522" max="3523" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3524" max="3525" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3526" max="3526" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3280" max="3280" width="8.8984375" style="4"/>
+    <col min="3281" max="3281" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3282" max="3517" width="8.8984375" style="4"/>
+    <col min="3518" max="3518" width="2.796875" style="4" customWidth="1"/>
+    <col min="3519" max="3519" width="17.296875" style="4" customWidth="1"/>
+    <col min="3520" max="3520" width="6.796875" style="4" customWidth="1"/>
+    <col min="3521" max="3521" width="5.296875" style="4" customWidth="1"/>
+    <col min="3522" max="3523" width="6.296875" style="4" customWidth="1"/>
+    <col min="3524" max="3525" width="4.296875" style="4" customWidth="1"/>
+    <col min="3526" max="3526" width="3.8984375" style="4" customWidth="1"/>
     <col min="3527" max="3527" width="3" style="4" customWidth="1"/>
-    <col min="3528" max="3528" width="3.21875" style="4" customWidth="1"/>
+    <col min="3528" max="3528" width="3.19921875" style="4" customWidth="1"/>
     <col min="3529" max="3529" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3530" max="3530" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3531" max="3533" width="8.88671875" style="4"/>
-    <col min="3534" max="3534" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3530" max="3530" width="6.796875" style="4" customWidth="1"/>
+    <col min="3531" max="3533" width="8.8984375" style="4"/>
+    <col min="3534" max="3534" width="11.69921875" style="4" customWidth="1"/>
     <col min="3535" max="3535" width="7" style="4" customWidth="1"/>
-    <col min="3536" max="3536" width="8.88671875" style="4"/>
-    <col min="3537" max="3537" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3538" max="3773" width="8.88671875" style="4"/>
-    <col min="3774" max="3774" width="2.77734375" style="4" customWidth="1"/>
-    <col min="3775" max="3775" width="17.33203125" style="4" customWidth="1"/>
-    <col min="3776" max="3776" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3777" max="3777" width="5.33203125" style="4" customWidth="1"/>
-    <col min="3778" max="3779" width="6.33203125" style="4" customWidth="1"/>
-    <col min="3780" max="3781" width="4.33203125" style="4" customWidth="1"/>
-    <col min="3782" max="3782" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3536" max="3536" width="8.8984375" style="4"/>
+    <col min="3537" max="3537" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3538" max="3773" width="8.8984375" style="4"/>
+    <col min="3774" max="3774" width="2.796875" style="4" customWidth="1"/>
+    <col min="3775" max="3775" width="17.296875" style="4" customWidth="1"/>
+    <col min="3776" max="3776" width="6.796875" style="4" customWidth="1"/>
+    <col min="3777" max="3777" width="5.296875" style="4" customWidth="1"/>
+    <col min="3778" max="3779" width="6.296875" style="4" customWidth="1"/>
+    <col min="3780" max="3781" width="4.296875" style="4" customWidth="1"/>
+    <col min="3782" max="3782" width="3.8984375" style="4" customWidth="1"/>
     <col min="3783" max="3783" width="3" style="4" customWidth="1"/>
-    <col min="3784" max="3784" width="3.21875" style="4" customWidth="1"/>
+    <col min="3784" max="3784" width="3.19921875" style="4" customWidth="1"/>
     <col min="3785" max="3785" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3786" max="3786" width="6.77734375" style="4" customWidth="1"/>
-    <col min="3787" max="3789" width="8.88671875" style="4"/>
-    <col min="3790" max="3790" width="11.6640625" style="4" customWidth="1"/>
+    <col min="3786" max="3786" width="6.796875" style="4" customWidth="1"/>
+    <col min="3787" max="3789" width="8.8984375" style="4"/>
+    <col min="3790" max="3790" width="11.69921875" style="4" customWidth="1"/>
     <col min="3791" max="3791" width="7" style="4" customWidth="1"/>
-    <col min="3792" max="3792" width="8.88671875" style="4"/>
-    <col min="3793" max="3793" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="3794" max="4029" width="8.88671875" style="4"/>
-    <col min="4030" max="4030" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4031" max="4031" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4032" max="4032" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4033" max="4033" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4034" max="4035" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4036" max="4037" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4038" max="4038" width="3.88671875" style="4" customWidth="1"/>
+    <col min="3792" max="3792" width="8.8984375" style="4"/>
+    <col min="3793" max="3793" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3794" max="4029" width="8.8984375" style="4"/>
+    <col min="4030" max="4030" width="2.796875" style="4" customWidth="1"/>
+    <col min="4031" max="4031" width="17.296875" style="4" customWidth="1"/>
+    <col min="4032" max="4032" width="6.796875" style="4" customWidth="1"/>
+    <col min="4033" max="4033" width="5.296875" style="4" customWidth="1"/>
+    <col min="4034" max="4035" width="6.296875" style="4" customWidth="1"/>
+    <col min="4036" max="4037" width="4.296875" style="4" customWidth="1"/>
+    <col min="4038" max="4038" width="3.8984375" style="4" customWidth="1"/>
     <col min="4039" max="4039" width="3" style="4" customWidth="1"/>
-    <col min="4040" max="4040" width="3.21875" style="4" customWidth="1"/>
+    <col min="4040" max="4040" width="3.19921875" style="4" customWidth="1"/>
     <col min="4041" max="4041" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4042" max="4042" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4043" max="4045" width="8.88671875" style="4"/>
-    <col min="4046" max="4046" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4042" max="4042" width="6.796875" style="4" customWidth="1"/>
+    <col min="4043" max="4045" width="8.8984375" style="4"/>
+    <col min="4046" max="4046" width="11.69921875" style="4" customWidth="1"/>
     <col min="4047" max="4047" width="7" style="4" customWidth="1"/>
-    <col min="4048" max="4048" width="8.88671875" style="4"/>
-    <col min="4049" max="4049" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4050" max="4285" width="8.88671875" style="4"/>
-    <col min="4286" max="4286" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4287" max="4287" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4288" max="4288" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4289" max="4289" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4290" max="4291" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4292" max="4293" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4294" max="4294" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4048" max="4048" width="8.8984375" style="4"/>
+    <col min="4049" max="4049" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4050" max="4285" width="8.8984375" style="4"/>
+    <col min="4286" max="4286" width="2.796875" style="4" customWidth="1"/>
+    <col min="4287" max="4287" width="17.296875" style="4" customWidth="1"/>
+    <col min="4288" max="4288" width="6.796875" style="4" customWidth="1"/>
+    <col min="4289" max="4289" width="5.296875" style="4" customWidth="1"/>
+    <col min="4290" max="4291" width="6.296875" style="4" customWidth="1"/>
+    <col min="4292" max="4293" width="4.296875" style="4" customWidth="1"/>
+    <col min="4294" max="4294" width="3.8984375" style="4" customWidth="1"/>
     <col min="4295" max="4295" width="3" style="4" customWidth="1"/>
-    <col min="4296" max="4296" width="3.21875" style="4" customWidth="1"/>
+    <col min="4296" max="4296" width="3.19921875" style="4" customWidth="1"/>
     <col min="4297" max="4297" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4298" max="4298" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4299" max="4301" width="8.88671875" style="4"/>
-    <col min="4302" max="4302" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4298" max="4298" width="6.796875" style="4" customWidth="1"/>
+    <col min="4299" max="4301" width="8.8984375" style="4"/>
+    <col min="4302" max="4302" width="11.69921875" style="4" customWidth="1"/>
     <col min="4303" max="4303" width="7" style="4" customWidth="1"/>
-    <col min="4304" max="4304" width="8.88671875" style="4"/>
-    <col min="4305" max="4305" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4306" max="4541" width="8.88671875" style="4"/>
-    <col min="4542" max="4542" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4543" max="4543" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4544" max="4544" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4545" max="4545" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4546" max="4547" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4548" max="4549" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4550" max="4550" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4304" max="4304" width="8.8984375" style="4"/>
+    <col min="4305" max="4305" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4306" max="4541" width="8.8984375" style="4"/>
+    <col min="4542" max="4542" width="2.796875" style="4" customWidth="1"/>
+    <col min="4543" max="4543" width="17.296875" style="4" customWidth="1"/>
+    <col min="4544" max="4544" width="6.796875" style="4" customWidth="1"/>
+    <col min="4545" max="4545" width="5.296875" style="4" customWidth="1"/>
+    <col min="4546" max="4547" width="6.296875" style="4" customWidth="1"/>
+    <col min="4548" max="4549" width="4.296875" style="4" customWidth="1"/>
+    <col min="4550" max="4550" width="3.8984375" style="4" customWidth="1"/>
     <col min="4551" max="4551" width="3" style="4" customWidth="1"/>
-    <col min="4552" max="4552" width="3.21875" style="4" customWidth="1"/>
+    <col min="4552" max="4552" width="3.19921875" style="4" customWidth="1"/>
     <col min="4553" max="4553" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4554" max="4554" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4555" max="4557" width="8.88671875" style="4"/>
-    <col min="4558" max="4558" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4554" max="4554" width="6.796875" style="4" customWidth="1"/>
+    <col min="4555" max="4557" width="8.8984375" style="4"/>
+    <col min="4558" max="4558" width="11.69921875" style="4" customWidth="1"/>
     <col min="4559" max="4559" width="7" style="4" customWidth="1"/>
-    <col min="4560" max="4560" width="8.88671875" style="4"/>
-    <col min="4561" max="4561" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4562" max="4797" width="8.88671875" style="4"/>
-    <col min="4798" max="4798" width="2.77734375" style="4" customWidth="1"/>
-    <col min="4799" max="4799" width="17.33203125" style="4" customWidth="1"/>
-    <col min="4800" max="4800" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4801" max="4801" width="5.33203125" style="4" customWidth="1"/>
-    <col min="4802" max="4803" width="6.33203125" style="4" customWidth="1"/>
-    <col min="4804" max="4805" width="4.33203125" style="4" customWidth="1"/>
-    <col min="4806" max="4806" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4560" max="4560" width="8.8984375" style="4"/>
+    <col min="4561" max="4561" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4562" max="4797" width="8.8984375" style="4"/>
+    <col min="4798" max="4798" width="2.796875" style="4" customWidth="1"/>
+    <col min="4799" max="4799" width="17.296875" style="4" customWidth="1"/>
+    <col min="4800" max="4800" width="6.796875" style="4" customWidth="1"/>
+    <col min="4801" max="4801" width="5.296875" style="4" customWidth="1"/>
+    <col min="4802" max="4803" width="6.296875" style="4" customWidth="1"/>
+    <col min="4804" max="4805" width="4.296875" style="4" customWidth="1"/>
+    <col min="4806" max="4806" width="3.8984375" style="4" customWidth="1"/>
     <col min="4807" max="4807" width="3" style="4" customWidth="1"/>
-    <col min="4808" max="4808" width="3.21875" style="4" customWidth="1"/>
+    <col min="4808" max="4808" width="3.19921875" style="4" customWidth="1"/>
     <col min="4809" max="4809" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4810" max="4810" width="6.77734375" style="4" customWidth="1"/>
-    <col min="4811" max="4813" width="8.88671875" style="4"/>
-    <col min="4814" max="4814" width="11.6640625" style="4" customWidth="1"/>
+    <col min="4810" max="4810" width="6.796875" style="4" customWidth="1"/>
+    <col min="4811" max="4813" width="8.8984375" style="4"/>
+    <col min="4814" max="4814" width="11.69921875" style="4" customWidth="1"/>
     <col min="4815" max="4815" width="7" style="4" customWidth="1"/>
-    <col min="4816" max="4816" width="8.88671875" style="4"/>
-    <col min="4817" max="4817" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4818" max="5053" width="8.88671875" style="4"/>
-    <col min="5054" max="5054" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5055" max="5055" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5056" max="5056" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5057" max="5057" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5058" max="5059" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5060" max="5061" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5062" max="5062" width="3.88671875" style="4" customWidth="1"/>
+    <col min="4816" max="4816" width="8.8984375" style="4"/>
+    <col min="4817" max="4817" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4818" max="5053" width="8.8984375" style="4"/>
+    <col min="5054" max="5054" width="2.796875" style="4" customWidth="1"/>
+    <col min="5055" max="5055" width="17.296875" style="4" customWidth="1"/>
+    <col min="5056" max="5056" width="6.796875" style="4" customWidth="1"/>
+    <col min="5057" max="5057" width="5.296875" style="4" customWidth="1"/>
+    <col min="5058" max="5059" width="6.296875" style="4" customWidth="1"/>
+    <col min="5060" max="5061" width="4.296875" style="4" customWidth="1"/>
+    <col min="5062" max="5062" width="3.8984375" style="4" customWidth="1"/>
     <col min="5063" max="5063" width="3" style="4" customWidth="1"/>
-    <col min="5064" max="5064" width="3.21875" style="4" customWidth="1"/>
+    <col min="5064" max="5064" width="3.19921875" style="4" customWidth="1"/>
     <col min="5065" max="5065" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5066" max="5066" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5067" max="5069" width="8.88671875" style="4"/>
-    <col min="5070" max="5070" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5066" max="5066" width="6.796875" style="4" customWidth="1"/>
+    <col min="5067" max="5069" width="8.8984375" style="4"/>
+    <col min="5070" max="5070" width="11.69921875" style="4" customWidth="1"/>
     <col min="5071" max="5071" width="7" style="4" customWidth="1"/>
-    <col min="5072" max="5072" width="8.88671875" style="4"/>
-    <col min="5073" max="5073" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5074" max="5309" width="8.88671875" style="4"/>
-    <col min="5310" max="5310" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5311" max="5311" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5312" max="5312" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5313" max="5313" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5314" max="5315" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5316" max="5317" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5318" max="5318" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5072" max="5072" width="8.8984375" style="4"/>
+    <col min="5073" max="5073" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5074" max="5309" width="8.8984375" style="4"/>
+    <col min="5310" max="5310" width="2.796875" style="4" customWidth="1"/>
+    <col min="5311" max="5311" width="17.296875" style="4" customWidth="1"/>
+    <col min="5312" max="5312" width="6.796875" style="4" customWidth="1"/>
+    <col min="5313" max="5313" width="5.296875" style="4" customWidth="1"/>
+    <col min="5314" max="5315" width="6.296875" style="4" customWidth="1"/>
+    <col min="5316" max="5317" width="4.296875" style="4" customWidth="1"/>
+    <col min="5318" max="5318" width="3.8984375" style="4" customWidth="1"/>
     <col min="5319" max="5319" width="3" style="4" customWidth="1"/>
-    <col min="5320" max="5320" width="3.21875" style="4" customWidth="1"/>
+    <col min="5320" max="5320" width="3.19921875" style="4" customWidth="1"/>
     <col min="5321" max="5321" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5322" max="5322" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5323" max="5325" width="8.88671875" style="4"/>
-    <col min="5326" max="5326" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5322" max="5322" width="6.796875" style="4" customWidth="1"/>
+    <col min="5323" max="5325" width="8.8984375" style="4"/>
+    <col min="5326" max="5326" width="11.69921875" style="4" customWidth="1"/>
     <col min="5327" max="5327" width="7" style="4" customWidth="1"/>
-    <col min="5328" max="5328" width="8.88671875" style="4"/>
-    <col min="5329" max="5329" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5330" max="5565" width="8.88671875" style="4"/>
-    <col min="5566" max="5566" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5567" max="5567" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5568" max="5568" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5569" max="5569" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5570" max="5571" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5572" max="5573" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5574" max="5574" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5328" max="5328" width="8.8984375" style="4"/>
+    <col min="5329" max="5329" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5330" max="5565" width="8.8984375" style="4"/>
+    <col min="5566" max="5566" width="2.796875" style="4" customWidth="1"/>
+    <col min="5567" max="5567" width="17.296875" style="4" customWidth="1"/>
+    <col min="5568" max="5568" width="6.796875" style="4" customWidth="1"/>
+    <col min="5569" max="5569" width="5.296875" style="4" customWidth="1"/>
+    <col min="5570" max="5571" width="6.296875" style="4" customWidth="1"/>
+    <col min="5572" max="5573" width="4.296875" style="4" customWidth="1"/>
+    <col min="5574" max="5574" width="3.8984375" style="4" customWidth="1"/>
     <col min="5575" max="5575" width="3" style="4" customWidth="1"/>
-    <col min="5576" max="5576" width="3.21875" style="4" customWidth="1"/>
+    <col min="5576" max="5576" width="3.19921875" style="4" customWidth="1"/>
     <col min="5577" max="5577" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5578" max="5578" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5579" max="5581" width="8.88671875" style="4"/>
-    <col min="5582" max="5582" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5578" max="5578" width="6.796875" style="4" customWidth="1"/>
+    <col min="5579" max="5581" width="8.8984375" style="4"/>
+    <col min="5582" max="5582" width="11.69921875" style="4" customWidth="1"/>
     <col min="5583" max="5583" width="7" style="4" customWidth="1"/>
-    <col min="5584" max="5584" width="8.88671875" style="4"/>
-    <col min="5585" max="5585" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5586" max="5821" width="8.88671875" style="4"/>
-    <col min="5822" max="5822" width="2.77734375" style="4" customWidth="1"/>
-    <col min="5823" max="5823" width="17.33203125" style="4" customWidth="1"/>
-    <col min="5824" max="5824" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5825" max="5825" width="5.33203125" style="4" customWidth="1"/>
-    <col min="5826" max="5827" width="6.33203125" style="4" customWidth="1"/>
-    <col min="5828" max="5829" width="4.33203125" style="4" customWidth="1"/>
-    <col min="5830" max="5830" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5584" max="5584" width="8.8984375" style="4"/>
+    <col min="5585" max="5585" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5586" max="5821" width="8.8984375" style="4"/>
+    <col min="5822" max="5822" width="2.796875" style="4" customWidth="1"/>
+    <col min="5823" max="5823" width="17.296875" style="4" customWidth="1"/>
+    <col min="5824" max="5824" width="6.796875" style="4" customWidth="1"/>
+    <col min="5825" max="5825" width="5.296875" style="4" customWidth="1"/>
+    <col min="5826" max="5827" width="6.296875" style="4" customWidth="1"/>
+    <col min="5828" max="5829" width="4.296875" style="4" customWidth="1"/>
+    <col min="5830" max="5830" width="3.8984375" style="4" customWidth="1"/>
     <col min="5831" max="5831" width="3" style="4" customWidth="1"/>
-    <col min="5832" max="5832" width="3.21875" style="4" customWidth="1"/>
+    <col min="5832" max="5832" width="3.19921875" style="4" customWidth="1"/>
     <col min="5833" max="5833" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5834" max="5834" width="6.77734375" style="4" customWidth="1"/>
-    <col min="5835" max="5837" width="8.88671875" style="4"/>
-    <col min="5838" max="5838" width="11.6640625" style="4" customWidth="1"/>
+    <col min="5834" max="5834" width="6.796875" style="4" customWidth="1"/>
+    <col min="5835" max="5837" width="8.8984375" style="4"/>
+    <col min="5838" max="5838" width="11.69921875" style="4" customWidth="1"/>
     <col min="5839" max="5839" width="7" style="4" customWidth="1"/>
-    <col min="5840" max="5840" width="8.88671875" style="4"/>
-    <col min="5841" max="5841" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5842" max="6077" width="8.88671875" style="4"/>
-    <col min="6078" max="6078" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6079" max="6079" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6080" max="6080" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6081" max="6081" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6082" max="6083" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6084" max="6085" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6086" max="6086" width="3.88671875" style="4" customWidth="1"/>
+    <col min="5840" max="5840" width="8.8984375" style="4"/>
+    <col min="5841" max="5841" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5842" max="6077" width="8.8984375" style="4"/>
+    <col min="6078" max="6078" width="2.796875" style="4" customWidth="1"/>
+    <col min="6079" max="6079" width="17.296875" style="4" customWidth="1"/>
+    <col min="6080" max="6080" width="6.796875" style="4" customWidth="1"/>
+    <col min="6081" max="6081" width="5.296875" style="4" customWidth="1"/>
+    <col min="6082" max="6083" width="6.296875" style="4" customWidth="1"/>
+    <col min="6084" max="6085" width="4.296875" style="4" customWidth="1"/>
+    <col min="6086" max="6086" width="3.8984375" style="4" customWidth="1"/>
     <col min="6087" max="6087" width="3" style="4" customWidth="1"/>
-    <col min="6088" max="6088" width="3.21875" style="4" customWidth="1"/>
+    <col min="6088" max="6088" width="3.19921875" style="4" customWidth="1"/>
     <col min="6089" max="6089" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6090" max="6090" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6091" max="6093" width="8.88671875" style="4"/>
-    <col min="6094" max="6094" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6090" max="6090" width="6.796875" style="4" customWidth="1"/>
+    <col min="6091" max="6093" width="8.8984375" style="4"/>
+    <col min="6094" max="6094" width="11.69921875" style="4" customWidth="1"/>
     <col min="6095" max="6095" width="7" style="4" customWidth="1"/>
-    <col min="6096" max="6096" width="8.88671875" style="4"/>
-    <col min="6097" max="6097" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6098" max="6333" width="8.88671875" style="4"/>
-    <col min="6334" max="6334" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6335" max="6335" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6336" max="6336" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6337" max="6337" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6338" max="6339" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6340" max="6341" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6342" max="6342" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6096" max="6096" width="8.8984375" style="4"/>
+    <col min="6097" max="6097" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6098" max="6333" width="8.8984375" style="4"/>
+    <col min="6334" max="6334" width="2.796875" style="4" customWidth="1"/>
+    <col min="6335" max="6335" width="17.296875" style="4" customWidth="1"/>
+    <col min="6336" max="6336" width="6.796875" style="4" customWidth="1"/>
+    <col min="6337" max="6337" width="5.296875" style="4" customWidth="1"/>
+    <col min="6338" max="6339" width="6.296875" style="4" customWidth="1"/>
+    <col min="6340" max="6341" width="4.296875" style="4" customWidth="1"/>
+    <col min="6342" max="6342" width="3.8984375" style="4" customWidth="1"/>
     <col min="6343" max="6343" width="3" style="4" customWidth="1"/>
-    <col min="6344" max="6344" width="3.21875" style="4" customWidth="1"/>
+    <col min="6344" max="6344" width="3.19921875" style="4" customWidth="1"/>
     <col min="6345" max="6345" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6346" max="6346" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6347" max="6349" width="8.88671875" style="4"/>
-    <col min="6350" max="6350" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6346" max="6346" width="6.796875" style="4" customWidth="1"/>
+    <col min="6347" max="6349" width="8.8984375" style="4"/>
+    <col min="6350" max="6350" width="11.69921875" style="4" customWidth="1"/>
     <col min="6351" max="6351" width="7" style="4" customWidth="1"/>
-    <col min="6352" max="6352" width="8.88671875" style="4"/>
-    <col min="6353" max="6353" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6354" max="6589" width="8.88671875" style="4"/>
-    <col min="6590" max="6590" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6591" max="6591" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6592" max="6592" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6593" max="6593" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6594" max="6595" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6596" max="6597" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6598" max="6598" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6352" max="6352" width="8.8984375" style="4"/>
+    <col min="6353" max="6353" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6354" max="6589" width="8.8984375" style="4"/>
+    <col min="6590" max="6590" width="2.796875" style="4" customWidth="1"/>
+    <col min="6591" max="6591" width="17.296875" style="4" customWidth="1"/>
+    <col min="6592" max="6592" width="6.796875" style="4" customWidth="1"/>
+    <col min="6593" max="6593" width="5.296875" style="4" customWidth="1"/>
+    <col min="6594" max="6595" width="6.296875" style="4" customWidth="1"/>
+    <col min="6596" max="6597" width="4.296875" style="4" customWidth="1"/>
+    <col min="6598" max="6598" width="3.8984375" style="4" customWidth="1"/>
     <col min="6599" max="6599" width="3" style="4" customWidth="1"/>
-    <col min="6600" max="6600" width="3.21875" style="4" customWidth="1"/>
+    <col min="6600" max="6600" width="3.19921875" style="4" customWidth="1"/>
     <col min="6601" max="6601" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6602" max="6602" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6603" max="6605" width="8.88671875" style="4"/>
-    <col min="6606" max="6606" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6602" max="6602" width="6.796875" style="4" customWidth="1"/>
+    <col min="6603" max="6605" width="8.8984375" style="4"/>
+    <col min="6606" max="6606" width="11.69921875" style="4" customWidth="1"/>
     <col min="6607" max="6607" width="7" style="4" customWidth="1"/>
-    <col min="6608" max="6608" width="8.88671875" style="4"/>
-    <col min="6609" max="6609" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6610" max="6845" width="8.88671875" style="4"/>
-    <col min="6846" max="6846" width="2.77734375" style="4" customWidth="1"/>
-    <col min="6847" max="6847" width="17.33203125" style="4" customWidth="1"/>
-    <col min="6848" max="6848" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6849" max="6849" width="5.33203125" style="4" customWidth="1"/>
-    <col min="6850" max="6851" width="6.33203125" style="4" customWidth="1"/>
-    <col min="6852" max="6853" width="4.33203125" style="4" customWidth="1"/>
-    <col min="6854" max="6854" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6608" max="6608" width="8.8984375" style="4"/>
+    <col min="6609" max="6609" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6610" max="6845" width="8.8984375" style="4"/>
+    <col min="6846" max="6846" width="2.796875" style="4" customWidth="1"/>
+    <col min="6847" max="6847" width="17.296875" style="4" customWidth="1"/>
+    <col min="6848" max="6848" width="6.796875" style="4" customWidth="1"/>
+    <col min="6849" max="6849" width="5.296875" style="4" customWidth="1"/>
+    <col min="6850" max="6851" width="6.296875" style="4" customWidth="1"/>
+    <col min="6852" max="6853" width="4.296875" style="4" customWidth="1"/>
+    <col min="6854" max="6854" width="3.8984375" style="4" customWidth="1"/>
     <col min="6855" max="6855" width="3" style="4" customWidth="1"/>
-    <col min="6856" max="6856" width="3.21875" style="4" customWidth="1"/>
+    <col min="6856" max="6856" width="3.19921875" style="4" customWidth="1"/>
     <col min="6857" max="6857" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6858" max="6858" width="6.77734375" style="4" customWidth="1"/>
-    <col min="6859" max="6861" width="8.88671875" style="4"/>
-    <col min="6862" max="6862" width="11.6640625" style="4" customWidth="1"/>
+    <col min="6858" max="6858" width="6.796875" style="4" customWidth="1"/>
+    <col min="6859" max="6861" width="8.8984375" style="4"/>
+    <col min="6862" max="6862" width="11.69921875" style="4" customWidth="1"/>
     <col min="6863" max="6863" width="7" style="4" customWidth="1"/>
-    <col min="6864" max="6864" width="8.88671875" style="4"/>
-    <col min="6865" max="6865" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6866" max="7101" width="8.88671875" style="4"/>
-    <col min="7102" max="7102" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7103" max="7103" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7104" max="7104" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7105" max="7105" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7106" max="7107" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7108" max="7109" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7110" max="7110" width="3.88671875" style="4" customWidth="1"/>
+    <col min="6864" max="6864" width="8.8984375" style="4"/>
+    <col min="6865" max="6865" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6866" max="7101" width="8.8984375" style="4"/>
+    <col min="7102" max="7102" width="2.796875" style="4" customWidth="1"/>
+    <col min="7103" max="7103" width="17.296875" style="4" customWidth="1"/>
+    <col min="7104" max="7104" width="6.796875" style="4" customWidth="1"/>
+    <col min="7105" max="7105" width="5.296875" style="4" customWidth="1"/>
+    <col min="7106" max="7107" width="6.296875" style="4" customWidth="1"/>
+    <col min="7108" max="7109" width="4.296875" style="4" customWidth="1"/>
+    <col min="7110" max="7110" width="3.8984375" style="4" customWidth="1"/>
     <col min="7111" max="7111" width="3" style="4" customWidth="1"/>
-    <col min="7112" max="7112" width="3.21875" style="4" customWidth="1"/>
+    <col min="7112" max="7112" width="3.19921875" style="4" customWidth="1"/>
     <col min="7113" max="7113" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7114" max="7114" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7115" max="7117" width="8.88671875" style="4"/>
-    <col min="7118" max="7118" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7114" max="7114" width="6.796875" style="4" customWidth="1"/>
+    <col min="7115" max="7117" width="8.8984375" style="4"/>
+    <col min="7118" max="7118" width="11.69921875" style="4" customWidth="1"/>
     <col min="7119" max="7119" width="7" style="4" customWidth="1"/>
-    <col min="7120" max="7120" width="8.88671875" style="4"/>
-    <col min="7121" max="7121" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7122" max="7357" width="8.88671875" style="4"/>
-    <col min="7358" max="7358" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7359" max="7359" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7360" max="7360" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7361" max="7361" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7362" max="7363" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7364" max="7365" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7366" max="7366" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7120" max="7120" width="8.8984375" style="4"/>
+    <col min="7121" max="7121" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7122" max="7357" width="8.8984375" style="4"/>
+    <col min="7358" max="7358" width="2.796875" style="4" customWidth="1"/>
+    <col min="7359" max="7359" width="17.296875" style="4" customWidth="1"/>
+    <col min="7360" max="7360" width="6.796875" style="4" customWidth="1"/>
+    <col min="7361" max="7361" width="5.296875" style="4" customWidth="1"/>
+    <col min="7362" max="7363" width="6.296875" style="4" customWidth="1"/>
+    <col min="7364" max="7365" width="4.296875" style="4" customWidth="1"/>
+    <col min="7366" max="7366" width="3.8984375" style="4" customWidth="1"/>
     <col min="7367" max="7367" width="3" style="4" customWidth="1"/>
-    <col min="7368" max="7368" width="3.21875" style="4" customWidth="1"/>
+    <col min="7368" max="7368" width="3.19921875" style="4" customWidth="1"/>
     <col min="7369" max="7369" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7370" max="7370" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7371" max="7373" width="8.88671875" style="4"/>
-    <col min="7374" max="7374" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7370" max="7370" width="6.796875" style="4" customWidth="1"/>
+    <col min="7371" max="7373" width="8.8984375" style="4"/>
+    <col min="7374" max="7374" width="11.69921875" style="4" customWidth="1"/>
     <col min="7375" max="7375" width="7" style="4" customWidth="1"/>
-    <col min="7376" max="7376" width="8.88671875" style="4"/>
-    <col min="7377" max="7377" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7378" max="7613" width="8.88671875" style="4"/>
-    <col min="7614" max="7614" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7615" max="7615" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7616" max="7616" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7617" max="7617" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7618" max="7619" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7620" max="7621" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7622" max="7622" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7376" max="7376" width="8.8984375" style="4"/>
+    <col min="7377" max="7377" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7378" max="7613" width="8.8984375" style="4"/>
+    <col min="7614" max="7614" width="2.796875" style="4" customWidth="1"/>
+    <col min="7615" max="7615" width="17.296875" style="4" customWidth="1"/>
+    <col min="7616" max="7616" width="6.796875" style="4" customWidth="1"/>
+    <col min="7617" max="7617" width="5.296875" style="4" customWidth="1"/>
+    <col min="7618" max="7619" width="6.296875" style="4" customWidth="1"/>
+    <col min="7620" max="7621" width="4.296875" style="4" customWidth="1"/>
+    <col min="7622" max="7622" width="3.8984375" style="4" customWidth="1"/>
     <col min="7623" max="7623" width="3" style="4" customWidth="1"/>
-    <col min="7624" max="7624" width="3.21875" style="4" customWidth="1"/>
+    <col min="7624" max="7624" width="3.19921875" style="4" customWidth="1"/>
     <col min="7625" max="7625" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7626" max="7626" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7627" max="7629" width="8.88671875" style="4"/>
-    <col min="7630" max="7630" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7626" max="7626" width="6.796875" style="4" customWidth="1"/>
+    <col min="7627" max="7629" width="8.8984375" style="4"/>
+    <col min="7630" max="7630" width="11.69921875" style="4" customWidth="1"/>
     <col min="7631" max="7631" width="7" style="4" customWidth="1"/>
-    <col min="7632" max="7632" width="8.88671875" style="4"/>
-    <col min="7633" max="7633" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7634" max="7869" width="8.88671875" style="4"/>
-    <col min="7870" max="7870" width="2.77734375" style="4" customWidth="1"/>
-    <col min="7871" max="7871" width="17.33203125" style="4" customWidth="1"/>
-    <col min="7872" max="7872" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7873" max="7873" width="5.33203125" style="4" customWidth="1"/>
-    <col min="7874" max="7875" width="6.33203125" style="4" customWidth="1"/>
-    <col min="7876" max="7877" width="4.33203125" style="4" customWidth="1"/>
-    <col min="7878" max="7878" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7632" max="7632" width="8.8984375" style="4"/>
+    <col min="7633" max="7633" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7634" max="7869" width="8.8984375" style="4"/>
+    <col min="7870" max="7870" width="2.796875" style="4" customWidth="1"/>
+    <col min="7871" max="7871" width="17.296875" style="4" customWidth="1"/>
+    <col min="7872" max="7872" width="6.796875" style="4" customWidth="1"/>
+    <col min="7873" max="7873" width="5.296875" style="4" customWidth="1"/>
+    <col min="7874" max="7875" width="6.296875" style="4" customWidth="1"/>
+    <col min="7876" max="7877" width="4.296875" style="4" customWidth="1"/>
+    <col min="7878" max="7878" width="3.8984375" style="4" customWidth="1"/>
     <col min="7879" max="7879" width="3" style="4" customWidth="1"/>
-    <col min="7880" max="7880" width="3.21875" style="4" customWidth="1"/>
+    <col min="7880" max="7880" width="3.19921875" style="4" customWidth="1"/>
     <col min="7881" max="7881" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7882" max="7882" width="6.77734375" style="4" customWidth="1"/>
-    <col min="7883" max="7885" width="8.88671875" style="4"/>
-    <col min="7886" max="7886" width="11.6640625" style="4" customWidth="1"/>
+    <col min="7882" max="7882" width="6.796875" style="4" customWidth="1"/>
+    <col min="7883" max="7885" width="8.8984375" style="4"/>
+    <col min="7886" max="7886" width="11.69921875" style="4" customWidth="1"/>
     <col min="7887" max="7887" width="7" style="4" customWidth="1"/>
-    <col min="7888" max="7888" width="8.88671875" style="4"/>
-    <col min="7889" max="7889" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="7890" max="8125" width="8.88671875" style="4"/>
-    <col min="8126" max="8126" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8127" max="8127" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8128" max="8128" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8129" max="8129" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8130" max="8131" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8132" max="8133" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8134" max="8134" width="3.88671875" style="4" customWidth="1"/>
+    <col min="7888" max="7888" width="8.8984375" style="4"/>
+    <col min="7889" max="7889" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7890" max="8125" width="8.8984375" style="4"/>
+    <col min="8126" max="8126" width="2.796875" style="4" customWidth="1"/>
+    <col min="8127" max="8127" width="17.296875" style="4" customWidth="1"/>
+    <col min="8128" max="8128" width="6.796875" style="4" customWidth="1"/>
+    <col min="8129" max="8129" width="5.296875" style="4" customWidth="1"/>
+    <col min="8130" max="8131" width="6.296875" style="4" customWidth="1"/>
+    <col min="8132" max="8133" width="4.296875" style="4" customWidth="1"/>
+    <col min="8134" max="8134" width="3.8984375" style="4" customWidth="1"/>
     <col min="8135" max="8135" width="3" style="4" customWidth="1"/>
-    <col min="8136" max="8136" width="3.21875" style="4" customWidth="1"/>
+    <col min="8136" max="8136" width="3.19921875" style="4" customWidth="1"/>
     <col min="8137" max="8137" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8138" max="8138" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8139" max="8141" width="8.88671875" style="4"/>
-    <col min="8142" max="8142" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8138" max="8138" width="6.796875" style="4" customWidth="1"/>
+    <col min="8139" max="8141" width="8.8984375" style="4"/>
+    <col min="8142" max="8142" width="11.69921875" style="4" customWidth="1"/>
     <col min="8143" max="8143" width="7" style="4" customWidth="1"/>
-    <col min="8144" max="8144" width="8.88671875" style="4"/>
-    <col min="8145" max="8145" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8146" max="8381" width="8.88671875" style="4"/>
-    <col min="8382" max="8382" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8383" max="8383" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8384" max="8384" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8385" max="8385" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8386" max="8387" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8388" max="8389" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8390" max="8390" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8144" max="8144" width="8.8984375" style="4"/>
+    <col min="8145" max="8145" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8146" max="8381" width="8.8984375" style="4"/>
+    <col min="8382" max="8382" width="2.796875" style="4" customWidth="1"/>
+    <col min="8383" max="8383" width="17.296875" style="4" customWidth="1"/>
+    <col min="8384" max="8384" width="6.796875" style="4" customWidth="1"/>
+    <col min="8385" max="8385" width="5.296875" style="4" customWidth="1"/>
+    <col min="8386" max="8387" width="6.296875" style="4" customWidth="1"/>
+    <col min="8388" max="8389" width="4.296875" style="4" customWidth="1"/>
+    <col min="8390" max="8390" width="3.8984375" style="4" customWidth="1"/>
     <col min="8391" max="8391" width="3" style="4" customWidth="1"/>
-    <col min="8392" max="8392" width="3.21875" style="4" customWidth="1"/>
+    <col min="8392" max="8392" width="3.19921875" style="4" customWidth="1"/>
     <col min="8393" max="8393" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8394" max="8394" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8395" max="8397" width="8.88671875" style="4"/>
-    <col min="8398" max="8398" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8394" max="8394" width="6.796875" style="4" customWidth="1"/>
+    <col min="8395" max="8397" width="8.8984375" style="4"/>
+    <col min="8398" max="8398" width="11.69921875" style="4" customWidth="1"/>
     <col min="8399" max="8399" width="7" style="4" customWidth="1"/>
-    <col min="8400" max="8400" width="8.88671875" style="4"/>
-    <col min="8401" max="8401" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8402" max="8637" width="8.88671875" style="4"/>
-    <col min="8638" max="8638" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8639" max="8639" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8640" max="8640" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8641" max="8641" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8642" max="8643" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8644" max="8645" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8646" max="8646" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8400" max="8400" width="8.8984375" style="4"/>
+    <col min="8401" max="8401" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8402" max="8637" width="8.8984375" style="4"/>
+    <col min="8638" max="8638" width="2.796875" style="4" customWidth="1"/>
+    <col min="8639" max="8639" width="17.296875" style="4" customWidth="1"/>
+    <col min="8640" max="8640" width="6.796875" style="4" customWidth="1"/>
+    <col min="8641" max="8641" width="5.296875" style="4" customWidth="1"/>
+    <col min="8642" max="8643" width="6.296875" style="4" customWidth="1"/>
+    <col min="8644" max="8645" width="4.296875" style="4" customWidth="1"/>
+    <col min="8646" max="8646" width="3.8984375" style="4" customWidth="1"/>
     <col min="8647" max="8647" width="3" style="4" customWidth="1"/>
-    <col min="8648" max="8648" width="3.21875" style="4" customWidth="1"/>
+    <col min="8648" max="8648" width="3.19921875" style="4" customWidth="1"/>
     <col min="8649" max="8649" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8650" max="8650" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8651" max="8653" width="8.88671875" style="4"/>
-    <col min="8654" max="8654" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8650" max="8650" width="6.796875" style="4" customWidth="1"/>
+    <col min="8651" max="8653" width="8.8984375" style="4"/>
+    <col min="8654" max="8654" width="11.69921875" style="4" customWidth="1"/>
     <col min="8655" max="8655" width="7" style="4" customWidth="1"/>
-    <col min="8656" max="8656" width="8.88671875" style="4"/>
-    <col min="8657" max="8657" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8658" max="8893" width="8.88671875" style="4"/>
-    <col min="8894" max="8894" width="2.77734375" style="4" customWidth="1"/>
-    <col min="8895" max="8895" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8896" max="8896" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8897" max="8897" width="5.33203125" style="4" customWidth="1"/>
-    <col min="8898" max="8899" width="6.33203125" style="4" customWidth="1"/>
-    <col min="8900" max="8901" width="4.33203125" style="4" customWidth="1"/>
-    <col min="8902" max="8902" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8656" max="8656" width="8.8984375" style="4"/>
+    <col min="8657" max="8657" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8658" max="8893" width="8.8984375" style="4"/>
+    <col min="8894" max="8894" width="2.796875" style="4" customWidth="1"/>
+    <col min="8895" max="8895" width="17.296875" style="4" customWidth="1"/>
+    <col min="8896" max="8896" width="6.796875" style="4" customWidth="1"/>
+    <col min="8897" max="8897" width="5.296875" style="4" customWidth="1"/>
+    <col min="8898" max="8899" width="6.296875" style="4" customWidth="1"/>
+    <col min="8900" max="8901" width="4.296875" style="4" customWidth="1"/>
+    <col min="8902" max="8902" width="3.8984375" style="4" customWidth="1"/>
     <col min="8903" max="8903" width="3" style="4" customWidth="1"/>
-    <col min="8904" max="8904" width="3.21875" style="4" customWidth="1"/>
+    <col min="8904" max="8904" width="3.19921875" style="4" customWidth="1"/>
     <col min="8905" max="8905" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8906" max="8906" width="6.77734375" style="4" customWidth="1"/>
-    <col min="8907" max="8909" width="8.88671875" style="4"/>
-    <col min="8910" max="8910" width="11.6640625" style="4" customWidth="1"/>
+    <col min="8906" max="8906" width="6.796875" style="4" customWidth="1"/>
+    <col min="8907" max="8909" width="8.8984375" style="4"/>
+    <col min="8910" max="8910" width="11.69921875" style="4" customWidth="1"/>
     <col min="8911" max="8911" width="7" style="4" customWidth="1"/>
-    <col min="8912" max="8912" width="8.88671875" style="4"/>
-    <col min="8913" max="8913" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8914" max="9149" width="8.88671875" style="4"/>
-    <col min="9150" max="9150" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9151" max="9151" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9152" max="9152" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9153" max="9153" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9154" max="9155" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9156" max="9157" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9158" max="9158" width="3.88671875" style="4" customWidth="1"/>
+    <col min="8912" max="8912" width="8.8984375" style="4"/>
+    <col min="8913" max="8913" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8914" max="9149" width="8.8984375" style="4"/>
+    <col min="9150" max="9150" width="2.796875" style="4" customWidth="1"/>
+    <col min="9151" max="9151" width="17.296875" style="4" customWidth="1"/>
+    <col min="9152" max="9152" width="6.796875" style="4" customWidth="1"/>
+    <col min="9153" max="9153" width="5.296875" style="4" customWidth="1"/>
+    <col min="9154" max="9155" width="6.296875" style="4" customWidth="1"/>
+    <col min="9156" max="9157" width="4.296875" style="4" customWidth="1"/>
+    <col min="9158" max="9158" width="3.8984375" style="4" customWidth="1"/>
     <col min="9159" max="9159" width="3" style="4" customWidth="1"/>
-    <col min="9160" max="9160" width="3.21875" style="4" customWidth="1"/>
+    <col min="9160" max="9160" width="3.19921875" style="4" customWidth="1"/>
     <col min="9161" max="9161" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9162" max="9162" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9163" max="9165" width="8.88671875" style="4"/>
-    <col min="9166" max="9166" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9162" max="9162" width="6.796875" style="4" customWidth="1"/>
+    <col min="9163" max="9165" width="8.8984375" style="4"/>
+    <col min="9166" max="9166" width="11.69921875" style="4" customWidth="1"/>
     <col min="9167" max="9167" width="7" style="4" customWidth="1"/>
-    <col min="9168" max="9168" width="8.88671875" style="4"/>
-    <col min="9169" max="9169" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9170" max="9405" width="8.88671875" style="4"/>
-    <col min="9406" max="9406" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9407" max="9407" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9408" max="9408" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9409" max="9409" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9410" max="9411" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9412" max="9413" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9414" max="9414" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9168" max="9168" width="8.8984375" style="4"/>
+    <col min="9169" max="9169" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9170" max="9405" width="8.8984375" style="4"/>
+    <col min="9406" max="9406" width="2.796875" style="4" customWidth="1"/>
+    <col min="9407" max="9407" width="17.296875" style="4" customWidth="1"/>
+    <col min="9408" max="9408" width="6.796875" style="4" customWidth="1"/>
+    <col min="9409" max="9409" width="5.296875" style="4" customWidth="1"/>
+    <col min="9410" max="9411" width="6.296875" style="4" customWidth="1"/>
+    <col min="9412" max="9413" width="4.296875" style="4" customWidth="1"/>
+    <col min="9414" max="9414" width="3.8984375" style="4" customWidth="1"/>
     <col min="9415" max="9415" width="3" style="4" customWidth="1"/>
-    <col min="9416" max="9416" width="3.21875" style="4" customWidth="1"/>
+    <col min="9416" max="9416" width="3.19921875" style="4" customWidth="1"/>
     <col min="9417" max="9417" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9418" max="9418" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9419" max="9421" width="8.88671875" style="4"/>
-    <col min="9422" max="9422" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9418" max="9418" width="6.796875" style="4" customWidth="1"/>
+    <col min="9419" max="9421" width="8.8984375" style="4"/>
+    <col min="9422" max="9422" width="11.69921875" style="4" customWidth="1"/>
     <col min="9423" max="9423" width="7" style="4" customWidth="1"/>
-    <col min="9424" max="9424" width="8.88671875" style="4"/>
-    <col min="9425" max="9425" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9426" max="9661" width="8.88671875" style="4"/>
-    <col min="9662" max="9662" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9663" max="9663" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9664" max="9664" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9665" max="9665" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9666" max="9667" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9668" max="9669" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9670" max="9670" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9424" max="9424" width="8.8984375" style="4"/>
+    <col min="9425" max="9425" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9426" max="9661" width="8.8984375" style="4"/>
+    <col min="9662" max="9662" width="2.796875" style="4" customWidth="1"/>
+    <col min="9663" max="9663" width="17.296875" style="4" customWidth="1"/>
+    <col min="9664" max="9664" width="6.796875" style="4" customWidth="1"/>
+    <col min="9665" max="9665" width="5.296875" style="4" customWidth="1"/>
+    <col min="9666" max="9667" width="6.296875" style="4" customWidth="1"/>
+    <col min="9668" max="9669" width="4.296875" style="4" customWidth="1"/>
+    <col min="9670" max="9670" width="3.8984375" style="4" customWidth="1"/>
     <col min="9671" max="9671" width="3" style="4" customWidth="1"/>
-    <col min="9672" max="9672" width="3.21875" style="4" customWidth="1"/>
+    <col min="9672" max="9672" width="3.19921875" style="4" customWidth="1"/>
     <col min="9673" max="9673" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9674" max="9674" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9675" max="9677" width="8.88671875" style="4"/>
-    <col min="9678" max="9678" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9674" max="9674" width="6.796875" style="4" customWidth="1"/>
+    <col min="9675" max="9677" width="8.8984375" style="4"/>
+    <col min="9678" max="9678" width="11.69921875" style="4" customWidth="1"/>
     <col min="9679" max="9679" width="7" style="4" customWidth="1"/>
-    <col min="9680" max="9680" width="8.88671875" style="4"/>
-    <col min="9681" max="9681" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9682" max="9917" width="8.88671875" style="4"/>
-    <col min="9918" max="9918" width="2.77734375" style="4" customWidth="1"/>
-    <col min="9919" max="9919" width="17.33203125" style="4" customWidth="1"/>
-    <col min="9920" max="9920" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9921" max="9921" width="5.33203125" style="4" customWidth="1"/>
-    <col min="9922" max="9923" width="6.33203125" style="4" customWidth="1"/>
-    <col min="9924" max="9925" width="4.33203125" style="4" customWidth="1"/>
-    <col min="9926" max="9926" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9680" max="9680" width="8.8984375" style="4"/>
+    <col min="9681" max="9681" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9682" max="9917" width="8.8984375" style="4"/>
+    <col min="9918" max="9918" width="2.796875" style="4" customWidth="1"/>
+    <col min="9919" max="9919" width="17.296875" style="4" customWidth="1"/>
+    <col min="9920" max="9920" width="6.796875" style="4" customWidth="1"/>
+    <col min="9921" max="9921" width="5.296875" style="4" customWidth="1"/>
+    <col min="9922" max="9923" width="6.296875" style="4" customWidth="1"/>
+    <col min="9924" max="9925" width="4.296875" style="4" customWidth="1"/>
+    <col min="9926" max="9926" width="3.8984375" style="4" customWidth="1"/>
     <col min="9927" max="9927" width="3" style="4" customWidth="1"/>
-    <col min="9928" max="9928" width="3.21875" style="4" customWidth="1"/>
+    <col min="9928" max="9928" width="3.19921875" style="4" customWidth="1"/>
     <col min="9929" max="9929" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9930" max="9930" width="6.77734375" style="4" customWidth="1"/>
-    <col min="9931" max="9933" width="8.88671875" style="4"/>
-    <col min="9934" max="9934" width="11.6640625" style="4" customWidth="1"/>
+    <col min="9930" max="9930" width="6.796875" style="4" customWidth="1"/>
+    <col min="9931" max="9933" width="8.8984375" style="4"/>
+    <col min="9934" max="9934" width="11.69921875" style="4" customWidth="1"/>
     <col min="9935" max="9935" width="7" style="4" customWidth="1"/>
-    <col min="9936" max="9936" width="8.88671875" style="4"/>
-    <col min="9937" max="9937" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9938" max="10173" width="8.88671875" style="4"/>
-    <col min="10174" max="10174" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10175" max="10175" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10176" max="10176" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10177" max="10177" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10178" max="10179" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10180" max="10181" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10182" max="10182" width="3.88671875" style="4" customWidth="1"/>
+    <col min="9936" max="9936" width="8.8984375" style="4"/>
+    <col min="9937" max="9937" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9938" max="10173" width="8.8984375" style="4"/>
+    <col min="10174" max="10174" width="2.796875" style="4" customWidth="1"/>
+    <col min="10175" max="10175" width="17.296875" style="4" customWidth="1"/>
+    <col min="10176" max="10176" width="6.796875" style="4" customWidth="1"/>
+    <col min="10177" max="10177" width="5.296875" style="4" customWidth="1"/>
+    <col min="10178" max="10179" width="6.296875" style="4" customWidth="1"/>
+    <col min="10180" max="10181" width="4.296875" style="4" customWidth="1"/>
+    <col min="10182" max="10182" width="3.8984375" style="4" customWidth="1"/>
     <col min="10183" max="10183" width="3" style="4" customWidth="1"/>
-    <col min="10184" max="10184" width="3.21875" style="4" customWidth="1"/>
+    <col min="10184" max="10184" width="3.19921875" style="4" customWidth="1"/>
     <col min="10185" max="10185" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10186" max="10186" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10187" max="10189" width="8.88671875" style="4"/>
-    <col min="10190" max="10190" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10186" max="10186" width="6.796875" style="4" customWidth="1"/>
+    <col min="10187" max="10189" width="8.8984375" style="4"/>
+    <col min="10190" max="10190" width="11.69921875" style="4" customWidth="1"/>
     <col min="10191" max="10191" width="7" style="4" customWidth="1"/>
-    <col min="10192" max="10192" width="8.88671875" style="4"/>
-    <col min="10193" max="10193" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10194" max="10429" width="8.88671875" style="4"/>
-    <col min="10430" max="10430" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10431" max="10431" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10432" max="10432" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10433" max="10433" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10434" max="10435" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10436" max="10437" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10438" max="10438" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10192" max="10192" width="8.8984375" style="4"/>
+    <col min="10193" max="10193" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10194" max="10429" width="8.8984375" style="4"/>
+    <col min="10430" max="10430" width="2.796875" style="4" customWidth="1"/>
+    <col min="10431" max="10431" width="17.296875" style="4" customWidth="1"/>
+    <col min="10432" max="10432" width="6.796875" style="4" customWidth="1"/>
+    <col min="10433" max="10433" width="5.296875" style="4" customWidth="1"/>
+    <col min="10434" max="10435" width="6.296875" style="4" customWidth="1"/>
+    <col min="10436" max="10437" width="4.296875" style="4" customWidth="1"/>
+    <col min="10438" max="10438" width="3.8984375" style="4" customWidth="1"/>
     <col min="10439" max="10439" width="3" style="4" customWidth="1"/>
-    <col min="10440" max="10440" width="3.21875" style="4" customWidth="1"/>
+    <col min="10440" max="10440" width="3.19921875" style="4" customWidth="1"/>
     <col min="10441" max="10441" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10442" max="10442" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10443" max="10445" width="8.88671875" style="4"/>
-    <col min="10446" max="10446" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10442" max="10442" width="6.796875" style="4" customWidth="1"/>
+    <col min="10443" max="10445" width="8.8984375" style="4"/>
+    <col min="10446" max="10446" width="11.69921875" style="4" customWidth="1"/>
     <col min="10447" max="10447" width="7" style="4" customWidth="1"/>
-    <col min="10448" max="10448" width="8.88671875" style="4"/>
-    <col min="10449" max="10449" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10450" max="10685" width="8.88671875" style="4"/>
-    <col min="10686" max="10686" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10687" max="10687" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10688" max="10688" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10689" max="10689" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10690" max="10691" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10692" max="10693" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10694" max="10694" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10448" max="10448" width="8.8984375" style="4"/>
+    <col min="10449" max="10449" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10450" max="10685" width="8.8984375" style="4"/>
+    <col min="10686" max="10686" width="2.796875" style="4" customWidth="1"/>
+    <col min="10687" max="10687" width="17.296875" style="4" customWidth="1"/>
+    <col min="10688" max="10688" width="6.796875" style="4" customWidth="1"/>
+    <col min="10689" max="10689" width="5.296875" style="4" customWidth="1"/>
+    <col min="10690" max="10691" width="6.296875" style="4" customWidth="1"/>
+    <col min="10692" max="10693" width="4.296875" style="4" customWidth="1"/>
+    <col min="10694" max="10694" width="3.8984375" style="4" customWidth="1"/>
     <col min="10695" max="10695" width="3" style="4" customWidth="1"/>
-    <col min="10696" max="10696" width="3.21875" style="4" customWidth="1"/>
+    <col min="10696" max="10696" width="3.19921875" style="4" customWidth="1"/>
     <col min="10697" max="10697" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10698" max="10698" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10699" max="10701" width="8.88671875" style="4"/>
-    <col min="10702" max="10702" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10698" max="10698" width="6.796875" style="4" customWidth="1"/>
+    <col min="10699" max="10701" width="8.8984375" style="4"/>
+    <col min="10702" max="10702" width="11.69921875" style="4" customWidth="1"/>
     <col min="10703" max="10703" width="7" style="4" customWidth="1"/>
-    <col min="10704" max="10704" width="8.88671875" style="4"/>
-    <col min="10705" max="10705" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10706" max="10941" width="8.88671875" style="4"/>
-    <col min="10942" max="10942" width="2.77734375" style="4" customWidth="1"/>
-    <col min="10943" max="10943" width="17.33203125" style="4" customWidth="1"/>
-    <col min="10944" max="10944" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10945" max="10945" width="5.33203125" style="4" customWidth="1"/>
-    <col min="10946" max="10947" width="6.33203125" style="4" customWidth="1"/>
-    <col min="10948" max="10949" width="4.33203125" style="4" customWidth="1"/>
-    <col min="10950" max="10950" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10704" max="10704" width="8.8984375" style="4"/>
+    <col min="10705" max="10705" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10706" max="10941" width="8.8984375" style="4"/>
+    <col min="10942" max="10942" width="2.796875" style="4" customWidth="1"/>
+    <col min="10943" max="10943" width="17.296875" style="4" customWidth="1"/>
+    <col min="10944" max="10944" width="6.796875" style="4" customWidth="1"/>
+    <col min="10945" max="10945" width="5.296875" style="4" customWidth="1"/>
+    <col min="10946" max="10947" width="6.296875" style="4" customWidth="1"/>
+    <col min="10948" max="10949" width="4.296875" style="4" customWidth="1"/>
+    <col min="10950" max="10950" width="3.8984375" style="4" customWidth="1"/>
     <col min="10951" max="10951" width="3" style="4" customWidth="1"/>
-    <col min="10952" max="10952" width="3.21875" style="4" customWidth="1"/>
+    <col min="10952" max="10952" width="3.19921875" style="4" customWidth="1"/>
     <col min="10953" max="10953" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10954" max="10954" width="6.77734375" style="4" customWidth="1"/>
-    <col min="10955" max="10957" width="8.88671875" style="4"/>
-    <col min="10958" max="10958" width="11.6640625" style="4" customWidth="1"/>
+    <col min="10954" max="10954" width="6.796875" style="4" customWidth="1"/>
+    <col min="10955" max="10957" width="8.8984375" style="4"/>
+    <col min="10958" max="10958" width="11.69921875" style="4" customWidth="1"/>
     <col min="10959" max="10959" width="7" style="4" customWidth="1"/>
-    <col min="10960" max="10960" width="8.88671875" style="4"/>
-    <col min="10961" max="10961" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10962" max="11197" width="8.88671875" style="4"/>
-    <col min="11198" max="11198" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11199" max="11199" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11200" max="11200" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11201" max="11201" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11202" max="11203" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11204" max="11205" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11206" max="11206" width="3.88671875" style="4" customWidth="1"/>
+    <col min="10960" max="10960" width="8.8984375" style="4"/>
+    <col min="10961" max="10961" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10962" max="11197" width="8.8984375" style="4"/>
+    <col min="11198" max="11198" width="2.796875" style="4" customWidth="1"/>
+    <col min="11199" max="11199" width="17.296875" style="4" customWidth="1"/>
+    <col min="11200" max="11200" width="6.796875" style="4" customWidth="1"/>
+    <col min="11201" max="11201" width="5.296875" style="4" customWidth="1"/>
+    <col min="11202" max="11203" width="6.296875" style="4" customWidth="1"/>
+    <col min="11204" max="11205" width="4.296875" style="4" customWidth="1"/>
+    <col min="11206" max="11206" width="3.8984375" style="4" customWidth="1"/>
     <col min="11207" max="11207" width="3" style="4" customWidth="1"/>
-    <col min="11208" max="11208" width="3.21875" style="4" customWidth="1"/>
+    <col min="11208" max="11208" width="3.19921875" style="4" customWidth="1"/>
     <col min="11209" max="11209" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11210" max="11210" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11211" max="11213" width="8.88671875" style="4"/>
-    <col min="11214" max="11214" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11210" max="11210" width="6.796875" style="4" customWidth="1"/>
+    <col min="11211" max="11213" width="8.8984375" style="4"/>
+    <col min="11214" max="11214" width="11.69921875" style="4" customWidth="1"/>
     <col min="11215" max="11215" width="7" style="4" customWidth="1"/>
-    <col min="11216" max="11216" width="8.88671875" style="4"/>
-    <col min="11217" max="11217" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11218" max="11453" width="8.88671875" style="4"/>
-    <col min="11454" max="11454" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11455" max="11455" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11456" max="11456" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11457" max="11457" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11458" max="11459" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11460" max="11461" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11462" max="11462" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11216" max="11216" width="8.8984375" style="4"/>
+    <col min="11217" max="11217" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11218" max="11453" width="8.8984375" style="4"/>
+    <col min="11454" max="11454" width="2.796875" style="4" customWidth="1"/>
+    <col min="11455" max="11455" width="17.296875" style="4" customWidth="1"/>
+    <col min="11456" max="11456" width="6.796875" style="4" customWidth="1"/>
+    <col min="11457" max="11457" width="5.296875" style="4" customWidth="1"/>
+    <col min="11458" max="11459" width="6.296875" style="4" customWidth="1"/>
+    <col min="11460" max="11461" width="4.296875" style="4" customWidth="1"/>
+    <col min="11462" max="11462" width="3.8984375" style="4" customWidth="1"/>
     <col min="11463" max="11463" width="3" style="4" customWidth="1"/>
-    <col min="11464" max="11464" width="3.21875" style="4" customWidth="1"/>
+    <col min="11464" max="11464" width="3.19921875" style="4" customWidth="1"/>
     <col min="11465" max="11465" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11466" max="11466" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11467" max="11469" width="8.88671875" style="4"/>
-    <col min="11470" max="11470" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11466" max="11466" width="6.796875" style="4" customWidth="1"/>
+    <col min="11467" max="11469" width="8.8984375" style="4"/>
+    <col min="11470" max="11470" width="11.69921875" style="4" customWidth="1"/>
     <col min="11471" max="11471" width="7" style="4" customWidth="1"/>
-    <col min="11472" max="11472" width="8.88671875" style="4"/>
-    <col min="11473" max="11473" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11474" max="11709" width="8.88671875" style="4"/>
-    <col min="11710" max="11710" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11711" max="11711" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11712" max="11712" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11713" max="11713" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11714" max="11715" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11716" max="11717" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11718" max="11718" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11472" max="11472" width="8.8984375" style="4"/>
+    <col min="11473" max="11473" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11474" max="11709" width="8.8984375" style="4"/>
+    <col min="11710" max="11710" width="2.796875" style="4" customWidth="1"/>
+    <col min="11711" max="11711" width="17.296875" style="4" customWidth="1"/>
+    <col min="11712" max="11712" width="6.796875" style="4" customWidth="1"/>
+    <col min="11713" max="11713" width="5.296875" style="4" customWidth="1"/>
+    <col min="11714" max="11715" width="6.296875" style="4" customWidth="1"/>
+    <col min="11716" max="11717" width="4.296875" style="4" customWidth="1"/>
+    <col min="11718" max="11718" width="3.8984375" style="4" customWidth="1"/>
     <col min="11719" max="11719" width="3" style="4" customWidth="1"/>
-    <col min="11720" max="11720" width="3.21875" style="4" customWidth="1"/>
+    <col min="11720" max="11720" width="3.19921875" style="4" customWidth="1"/>
     <col min="11721" max="11721" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11722" max="11722" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11723" max="11725" width="8.88671875" style="4"/>
-    <col min="11726" max="11726" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11722" max="11722" width="6.796875" style="4" customWidth="1"/>
+    <col min="11723" max="11725" width="8.8984375" style="4"/>
+    <col min="11726" max="11726" width="11.69921875" style="4" customWidth="1"/>
     <col min="11727" max="11727" width="7" style="4" customWidth="1"/>
-    <col min="11728" max="11728" width="8.88671875" style="4"/>
-    <col min="11729" max="11729" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11730" max="11965" width="8.88671875" style="4"/>
-    <col min="11966" max="11966" width="2.77734375" style="4" customWidth="1"/>
-    <col min="11967" max="11967" width="17.33203125" style="4" customWidth="1"/>
-    <col min="11968" max="11968" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11969" max="11969" width="5.33203125" style="4" customWidth="1"/>
-    <col min="11970" max="11971" width="6.33203125" style="4" customWidth="1"/>
-    <col min="11972" max="11973" width="4.33203125" style="4" customWidth="1"/>
-    <col min="11974" max="11974" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11728" max="11728" width="8.8984375" style="4"/>
+    <col min="11729" max="11729" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11730" max="11965" width="8.8984375" style="4"/>
+    <col min="11966" max="11966" width="2.796875" style="4" customWidth="1"/>
+    <col min="11967" max="11967" width="17.296875" style="4" customWidth="1"/>
+    <col min="11968" max="11968" width="6.796875" style="4" customWidth="1"/>
+    <col min="11969" max="11969" width="5.296875" style="4" customWidth="1"/>
+    <col min="11970" max="11971" width="6.296875" style="4" customWidth="1"/>
+    <col min="11972" max="11973" width="4.296875" style="4" customWidth="1"/>
+    <col min="11974" max="11974" width="3.8984375" style="4" customWidth="1"/>
     <col min="11975" max="11975" width="3" style="4" customWidth="1"/>
-    <col min="11976" max="11976" width="3.21875" style="4" customWidth="1"/>
+    <col min="11976" max="11976" width="3.19921875" style="4" customWidth="1"/>
     <col min="11977" max="11977" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11978" max="11978" width="6.77734375" style="4" customWidth="1"/>
-    <col min="11979" max="11981" width="8.88671875" style="4"/>
-    <col min="11982" max="11982" width="11.6640625" style="4" customWidth="1"/>
+    <col min="11978" max="11978" width="6.796875" style="4" customWidth="1"/>
+    <col min="11979" max="11981" width="8.8984375" style="4"/>
+    <col min="11982" max="11982" width="11.69921875" style="4" customWidth="1"/>
     <col min="11983" max="11983" width="7" style="4" customWidth="1"/>
-    <col min="11984" max="11984" width="8.88671875" style="4"/>
-    <col min="11985" max="11985" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11986" max="12221" width="8.88671875" style="4"/>
-    <col min="12222" max="12222" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12223" max="12223" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12224" max="12224" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12225" max="12225" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12226" max="12227" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12228" max="12229" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12230" max="12230" width="3.88671875" style="4" customWidth="1"/>
+    <col min="11984" max="11984" width="8.8984375" style="4"/>
+    <col min="11985" max="11985" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11986" max="12221" width="8.8984375" style="4"/>
+    <col min="12222" max="12222" width="2.796875" style="4" customWidth="1"/>
+    <col min="12223" max="12223" width="17.296875" style="4" customWidth="1"/>
+    <col min="12224" max="12224" width="6.796875" style="4" customWidth="1"/>
+    <col min="12225" max="12225" width="5.296875" style="4" customWidth="1"/>
+    <col min="12226" max="12227" width="6.296875" style="4" customWidth="1"/>
+    <col min="12228" max="12229" width="4.296875" style="4" customWidth="1"/>
+    <col min="12230" max="12230" width="3.8984375" style="4" customWidth="1"/>
     <col min="12231" max="12231" width="3" style="4" customWidth="1"/>
-    <col min="12232" max="12232" width="3.21875" style="4" customWidth="1"/>
+    <col min="12232" max="12232" width="3.19921875" style="4" customWidth="1"/>
     <col min="12233" max="12233" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12234" max="12234" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12235" max="12237" width="8.88671875" style="4"/>
-    <col min="12238" max="12238" width="11.6640625" style="4" customWidth="1"/>
+    <col min="12234" max="12234" width="6.796875" style="4" customWidth="1"/>
+    <col min="12235" max="12237" width="8.8984375" style="4"/>
+    <col min="12238" max="12238" width="11.69921875" style="4" customWidth="1"/>
     <col min="12239" max="12239" width="7" style="4" customWidth="1"/>
-    <col min="12240" max="12240" width="8.88671875" style="4"/>
-    <col min="12241" max="12241" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="12242" max="12477" width="8.88671875" style="4"/>
-    <col min="12478" max="12478" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12479" max="12479" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12480" max="12480" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12481" max="12481" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12482" max="12483" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12484" max="12485" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12486" max="12486" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12240" max="12240" width="8.8984375" style="4"/>
+    <col min="12241" max="12241" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12242" max="12477" width="8.8984375" style="4"/>
+    <col min="12478" max="12478" width="2.796875" style="4" customWidth="1"/>
+    <col min="12479" max="12479" width="17.296875" style="4" customWidth="1"/>
+    <col min="12480" max="12480" width="6.796875" style="4" customWidth="1"/>
+    <col min="12481" max="12481" width="5.296875" style="4" customWidth="1"/>
+    <col min="12482" max="12483" width="6.296875" style="4" customWidth="1"/>
+    <col min="12484" max="12485" width="4.296875" style="4" customWidth="1"/>
+    <col min="12486" max="12486" width="3.8984375" style="4" customWidth="1"/>
     <col min="12487" max="12487" width="3" style="4" customWidth="1"/>
-    <col min="12488" max="12488" width="3.21875" style="4" customWidth="1"/>
+    <col min="12488" max="12488" width="3.19921875" style="4" customWidth="1"/>
     <col min="12489" max="12489" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12490" max="12490" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12491" max="12493" width="8.88671875" style="4"/>
-    <col min="12494" max="12494" width="11.6640625" style="4" customWidth="1"/>
+    <col min="12490" max="12490" width="6.796875" style="4" customWidth="1"/>
+    <col min="12491" max="12493" width="8.8984375" style="4"/>
+    <col min="12494" max="12494" width="11.69921875" style="4" customWidth="1"/>
     <col min="12495" max="12495" width="7" style="4" customWidth="1"/>
-    <col min="12496" max="12496" width="8.88671875" style="4"/>
-    <col min="12497" max="12497" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="12498" max="12733" width="8.88671875" style="4"/>
-    <col min="12734" max="12734" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12735" max="12735" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12736" max="12736" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12737" max="12737" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12738" max="12739" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12740" max="12741" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12742" max="12742" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12496" max="12496" width="8.8984375" style="4"/>
+    <col min="12497" max="12497" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12498" max="12733" width="8.8984375" style="4"/>
+    <col min="12734" max="12734" width="2.796875" style="4" customWidth="1"/>
+    <col min="12735" max="12735" width="17.296875" style="4" customWidth="1"/>
+    <col min="12736" max="12736" width="6.796875" style="4" customWidth="1"/>
+    <col min="12737" max="12737" width="5.296875" style="4" customWidth="1"/>
+    <col min="12738" max="12739" width="6.296875" style="4" customWidth="1"/>
+    <col min="12740" max="12741" width="4.296875" style="4" customWidth="1"/>
+    <col min="12742" max="12742" width="3.8984375" style="4" customWidth="1"/>
     <col min="12743" max="12743" width="3" style="4" customWidth="1"/>
-    <col min="12744" max="12744" width="3.21875" style="4" customWidth="1"/>
+    <col min="12744" max="12744" width="3.19921875" style="4" customWidth="1"/>
     <col min="12745" max="12745" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12746" max="12746" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12747" max="12749" width="8.88671875" style="4"/>
-    <col min="12750" max="12750" width="11.6640625" style="4" customWidth="1"/>
+    <col min="12746" max="12746" width="6.796875" style="4" customWidth="1"/>
+    <col min="12747" max="12749" width="8.8984375" style="4"/>
+    <col min="12750" max="12750" width="11.69921875" style="4" customWidth="1"/>
     <col min="12751" max="12751" width="7" style="4" customWidth="1"/>
-    <col min="12752" max="12752" width="8.88671875" style="4"/>
-    <col min="12753" max="12753" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="12754" max="12989" width="8.88671875" style="4"/>
-    <col min="12990" max="12990" width="2.77734375" style="4" customWidth="1"/>
-    <col min="12991" max="12991" width="17.33203125" style="4" customWidth="1"/>
-    <col min="12992" max="12992" width="6.77734375" style="4" customWidth="1"/>
-    <col min="12993" max="12993" width="5.33203125" style="4" customWidth="1"/>
-    <col min="12994" max="12995" width="6.33203125" style="4" customWidth="1"/>
-    <col min="12996" max="12997" width="4.33203125" style="4" customWidth="1"/>
-    <col min="12998" max="12998" width="3.88671875" style="4" customWidth="1"/>
+    <col min="12752" max="12752" width="8.8984375" style="4"/>
+    <col min="12753" max="12753" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12754" max="12989" width="8.8984375" style="4"/>
+    <col min="12990" max="12990" width="2.796875" style="4" customWidth="1"/>
+    <col min="12991" max="12991" width="17.296875" style="4" customWidth="1"/>
+    <col min="12992" max="12992" width="6.796875" style="4" customWidth="1"/>
+    <col min="12993" max="12993" width="5.296875" style="4" customWidth="1"/>
+    <col min="12994" max="12995" width="6.296875" style="4" customWidth="1"/>
+    <col min="12996" max="12997" width="4.296875" style="4" customWidth="1"/>
+    <col min="12998" max="12998" width="3.8984375" style="4" customWidth="1"/>
     <col min="12999" max="12999" width="3" style="4" customWidth="1"/>
-    <col min="13000" max="13000" width="3.21875" style="4" customWidth="1"/>
+    <col min="13000" max="13000" width="3.19921875" style="4" customWidth="1"/>
     <col min="13001" max="13001" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13002" max="13002" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13003" max="13005" width="8.88671875" style="4"/>
-    <col min="13006" max="13006" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13002" max="13002" width="6.796875" style="4" customWidth="1"/>
+    <col min="13003" max="13005" width="8.8984375" style="4"/>
+    <col min="13006" max="13006" width="11.69921875" style="4" customWidth="1"/>
     <col min="13007" max="13007" width="7" style="4" customWidth="1"/>
-    <col min="13008" max="13008" width="8.88671875" style="4"/>
-    <col min="13009" max="13009" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13010" max="13245" width="8.88671875" style="4"/>
-    <col min="13246" max="13246" width="2.77734375" style="4" customWidth="1"/>
-    <col min="13247" max="13247" width="17.33203125" style="4" customWidth="1"/>
-    <col min="13248" max="13248" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13249" max="13249" width="5.33203125" style="4" customWidth="1"/>
-    <col min="13250" max="13251" width="6.33203125" style="4" customWidth="1"/>
-    <col min="13252" max="13253" width="4.33203125" style="4" customWidth="1"/>
-    <col min="13254" max="13254" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13008" max="13008" width="8.8984375" style="4"/>
+    <col min="13009" max="13009" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13010" max="13245" width="8.8984375" style="4"/>
+    <col min="13246" max="13246" width="2.796875" style="4" customWidth="1"/>
+    <col min="13247" max="13247" width="17.296875" style="4" customWidth="1"/>
+    <col min="13248" max="13248" width="6.796875" style="4" customWidth="1"/>
+    <col min="13249" max="13249" width="5.296875" style="4" customWidth="1"/>
+    <col min="13250" max="13251" width="6.296875" style="4" customWidth="1"/>
+    <col min="13252" max="13253" width="4.296875" style="4" customWidth="1"/>
+    <col min="13254" max="13254" width="3.8984375" style="4" customWidth="1"/>
     <col min="13255" max="13255" width="3" style="4" customWidth="1"/>
-    <col min="13256" max="13256" width="3.21875" style="4" customWidth="1"/>
+    <col min="13256" max="13256" width="3.19921875" style="4" customWidth="1"/>
     <col min="13257" max="13257" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13258" max="13258" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13259" max="13261" width="8.88671875" style="4"/>
-    <col min="13262" max="13262" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13258" max="13258" width="6.796875" style="4" customWidth="1"/>
+    <col min="13259" max="13261" width="8.8984375" style="4"/>
+    <col min="13262" max="13262" width="11.69921875" style="4" customWidth="1"/>
     <col min="13263" max="13263" width="7" style="4" customWidth="1"/>
-    <col min="13264" max="13264" width="8.88671875" style="4"/>
-    <col min="13265" max="13265" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13266" max="13501" width="8.88671875" style="4"/>
-    <col min="13502" max="13502" width="2.77734375" style="4" customWidth="1"/>
-    <col min="13503" max="13503" width="17.33203125" style="4" customWidth="1"/>
-    <col min="13504" max="13504" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13505" max="13505" width="5.33203125" style="4" customWidth="1"/>
-    <col min="13506" max="13507" width="6.33203125" style="4" customWidth="1"/>
-    <col min="13508" max="13509" width="4.33203125" style="4" customWidth="1"/>
-    <col min="13510" max="13510" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13264" max="13264" width="8.8984375" style="4"/>
+    <col min="13265" max="13265" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13266" max="13501" width="8.8984375" style="4"/>
+    <col min="13502" max="13502" width="2.796875" style="4" customWidth="1"/>
+    <col min="13503" max="13503" width="17.296875" style="4" customWidth="1"/>
+    <col min="13504" max="13504" width="6.796875" style="4" customWidth="1"/>
+    <col min="13505" max="13505" width="5.296875" style="4" customWidth="1"/>
+    <col min="13506" max="13507" width="6.296875" style="4" customWidth="1"/>
+    <col min="13508" max="13509" width="4.296875" style="4" customWidth="1"/>
+    <col min="13510" max="13510" width="3.8984375" style="4" customWidth="1"/>
     <col min="13511" max="13511" width="3" style="4" customWidth="1"/>
-    <col min="13512" max="13512" width="3.21875" style="4" customWidth="1"/>
+    <col min="13512" max="13512" width="3.19921875" style="4" customWidth="1"/>
     <col min="13513" max="13513" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13514" max="13514" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13515" max="13517" width="8.88671875" style="4"/>
-    <col min="13518" max="13518" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13514" max="13514" width="6.796875" style="4" customWidth="1"/>
+    <col min="13515" max="13517" width="8.8984375" style="4"/>
+    <col min="13518" max="13518" width="11.69921875" style="4" customWidth="1"/>
     <col min="13519" max="13519" width="7" style="4" customWidth="1"/>
-    <col min="13520" max="13520" width="8.88671875" style="4"/>
-    <col min="13521" max="13521" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13522" max="13757" width="8.88671875" style="4"/>
-    <col min="13758" max="13758" width="2.77734375" style="4" customWidth="1"/>
-    <col min="13759" max="13759" width="17.33203125" style="4" customWidth="1"/>
-    <col min="13760" max="13760" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13761" max="13761" width="5.33203125" style="4" customWidth="1"/>
-    <col min="13762" max="13763" width="6.33203125" style="4" customWidth="1"/>
-    <col min="13764" max="13765" width="4.33203125" style="4" customWidth="1"/>
-    <col min="13766" max="13766" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13520" max="13520" width="8.8984375" style="4"/>
+    <col min="13521" max="13521" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13522" max="13757" width="8.8984375" style="4"/>
+    <col min="13758" max="13758" width="2.796875" style="4" customWidth="1"/>
+    <col min="13759" max="13759" width="17.296875" style="4" customWidth="1"/>
+    <col min="13760" max="13760" width="6.796875" style="4" customWidth="1"/>
+    <col min="13761" max="13761" width="5.296875" style="4" customWidth="1"/>
+    <col min="13762" max="13763" width="6.296875" style="4" customWidth="1"/>
+    <col min="13764" max="13765" width="4.296875" style="4" customWidth="1"/>
+    <col min="13766" max="13766" width="3.8984375" style="4" customWidth="1"/>
     <col min="13767" max="13767" width="3" style="4" customWidth="1"/>
-    <col min="13768" max="13768" width="3.21875" style="4" customWidth="1"/>
+    <col min="13768" max="13768" width="3.19921875" style="4" customWidth="1"/>
     <col min="13769" max="13769" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13770" max="13770" width="6.77734375" style="4" customWidth="1"/>
-    <col min="13771" max="13773" width="8.88671875" style="4"/>
-    <col min="13774" max="13774" width="11.6640625" style="4" customWidth="1"/>
+    <col min="13770" max="13770" width="6.796875" style="4" customWidth="1"/>
+    <col min="13771" max="13773" width="8.8984375" style="4"/>
+    <col min="13774" max="13774" width="11.69921875" style="4" customWidth="1"/>
     <col min="13775" max="13775" width="7" style="4" customWidth="1"/>
-    <col min="13776" max="13776" width="8.88671875" style="4"/>
-    <col min="13777" max="13777" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="13778" max="14013" width="8.88671875" style="4"/>
-    <col min="14014" max="14014" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14015" max="14015" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14016" max="14016" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14017" max="14017" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14018" max="14019" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14020" max="14021" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14022" max="14022" width="3.88671875" style="4" customWidth="1"/>
+    <col min="13776" max="13776" width="8.8984375" style="4"/>
+    <col min="13777" max="13777" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="13778" max="14013" width="8.8984375" style="4"/>
+    <col min="14014" max="14014" width="2.796875" style="4" customWidth="1"/>
+    <col min="14015" max="14015" width="17.296875" style="4" customWidth="1"/>
+    <col min="14016" max="14016" width="6.796875" style="4" customWidth="1"/>
+    <col min="14017" max="14017" width="5.296875" style="4" customWidth="1"/>
+    <col min="14018" max="14019" width="6.296875" style="4" customWidth="1"/>
+    <col min="14020" max="14021" width="4.296875" style="4" customWidth="1"/>
+    <col min="14022" max="14022" width="3.8984375" style="4" customWidth="1"/>
     <col min="14023" max="14023" width="3" style="4" customWidth="1"/>
-    <col min="14024" max="14024" width="3.21875" style="4" customWidth="1"/>
+    <col min="14024" max="14024" width="3.19921875" style="4" customWidth="1"/>
     <col min="14025" max="14025" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14026" max="14026" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14027" max="14029" width="8.88671875" style="4"/>
-    <col min="14030" max="14030" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14026" max="14026" width="6.796875" style="4" customWidth="1"/>
+    <col min="14027" max="14029" width="8.8984375" style="4"/>
+    <col min="14030" max="14030" width="11.69921875" style="4" customWidth="1"/>
     <col min="14031" max="14031" width="7" style="4" customWidth="1"/>
-    <col min="14032" max="14032" width="8.88671875" style="4"/>
-    <col min="14033" max="14033" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14034" max="14269" width="8.88671875" style="4"/>
-    <col min="14270" max="14270" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14271" max="14271" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14272" max="14272" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14273" max="14273" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14274" max="14275" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14276" max="14277" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14278" max="14278" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14032" max="14032" width="8.8984375" style="4"/>
+    <col min="14033" max="14033" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14034" max="14269" width="8.8984375" style="4"/>
+    <col min="14270" max="14270" width="2.796875" style="4" customWidth="1"/>
+    <col min="14271" max="14271" width="17.296875" style="4" customWidth="1"/>
+    <col min="14272" max="14272" width="6.796875" style="4" customWidth="1"/>
+    <col min="14273" max="14273" width="5.296875" style="4" customWidth="1"/>
+    <col min="14274" max="14275" width="6.296875" style="4" customWidth="1"/>
+    <col min="14276" max="14277" width="4.296875" style="4" customWidth="1"/>
+    <col min="14278" max="14278" width="3.8984375" style="4" customWidth="1"/>
     <col min="14279" max="14279" width="3" style="4" customWidth="1"/>
-    <col min="14280" max="14280" width="3.21875" style="4" customWidth="1"/>
+    <col min="14280" max="14280" width="3.19921875" style="4" customWidth="1"/>
     <col min="14281" max="14281" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14282" max="14282" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14283" max="14285" width="8.88671875" style="4"/>
-    <col min="14286" max="14286" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14282" max="14282" width="6.796875" style="4" customWidth="1"/>
+    <col min="14283" max="14285" width="8.8984375" style="4"/>
+    <col min="14286" max="14286" width="11.69921875" style="4" customWidth="1"/>
     <col min="14287" max="14287" width="7" style="4" customWidth="1"/>
-    <col min="14288" max="14288" width="8.88671875" style="4"/>
-    <col min="14289" max="14289" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14290" max="14525" width="8.88671875" style="4"/>
-    <col min="14526" max="14526" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14527" max="14527" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14528" max="14528" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14529" max="14529" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14530" max="14531" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14532" max="14533" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14534" max="14534" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14288" max="14288" width="8.8984375" style="4"/>
+    <col min="14289" max="14289" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14290" max="14525" width="8.8984375" style="4"/>
+    <col min="14526" max="14526" width="2.796875" style="4" customWidth="1"/>
+    <col min="14527" max="14527" width="17.296875" style="4" customWidth="1"/>
+    <col min="14528" max="14528" width="6.796875" style="4" customWidth="1"/>
+    <col min="14529" max="14529" width="5.296875" style="4" customWidth="1"/>
+    <col min="14530" max="14531" width="6.296875" style="4" customWidth="1"/>
+    <col min="14532" max="14533" width="4.296875" style="4" customWidth="1"/>
+    <col min="14534" max="14534" width="3.8984375" style="4" customWidth="1"/>
     <col min="14535" max="14535" width="3" style="4" customWidth="1"/>
-    <col min="14536" max="14536" width="3.21875" style="4" customWidth="1"/>
+    <col min="14536" max="14536" width="3.19921875" style="4" customWidth="1"/>
     <col min="14537" max="14537" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14538" max="14538" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14539" max="14541" width="8.88671875" style="4"/>
-    <col min="14542" max="14542" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14538" max="14538" width="6.796875" style="4" customWidth="1"/>
+    <col min="14539" max="14541" width="8.8984375" style="4"/>
+    <col min="14542" max="14542" width="11.69921875" style="4" customWidth="1"/>
     <col min="14543" max="14543" width="7" style="4" customWidth="1"/>
-    <col min="14544" max="14544" width="8.88671875" style="4"/>
-    <col min="14545" max="14545" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14546" max="14781" width="8.88671875" style="4"/>
-    <col min="14782" max="14782" width="2.77734375" style="4" customWidth="1"/>
-    <col min="14783" max="14783" width="17.33203125" style="4" customWidth="1"/>
-    <col min="14784" max="14784" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14785" max="14785" width="5.33203125" style="4" customWidth="1"/>
-    <col min="14786" max="14787" width="6.33203125" style="4" customWidth="1"/>
-    <col min="14788" max="14789" width="4.33203125" style="4" customWidth="1"/>
-    <col min="14790" max="14790" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14544" max="14544" width="8.8984375" style="4"/>
+    <col min="14545" max="14545" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14546" max="14781" width="8.8984375" style="4"/>
+    <col min="14782" max="14782" width="2.796875" style="4" customWidth="1"/>
+    <col min="14783" max="14783" width="17.296875" style="4" customWidth="1"/>
+    <col min="14784" max="14784" width="6.796875" style="4" customWidth="1"/>
+    <col min="14785" max="14785" width="5.296875" style="4" customWidth="1"/>
+    <col min="14786" max="14787" width="6.296875" style="4" customWidth="1"/>
+    <col min="14788" max="14789" width="4.296875" style="4" customWidth="1"/>
+    <col min="14790" max="14790" width="3.8984375" style="4" customWidth="1"/>
     <col min="14791" max="14791" width="3" style="4" customWidth="1"/>
-    <col min="14792" max="14792" width="3.21875" style="4" customWidth="1"/>
+    <col min="14792" max="14792" width="3.19921875" style="4" customWidth="1"/>
     <col min="14793" max="14793" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14794" max="14794" width="6.77734375" style="4" customWidth="1"/>
-    <col min="14795" max="14797" width="8.88671875" style="4"/>
-    <col min="14798" max="14798" width="11.6640625" style="4" customWidth="1"/>
+    <col min="14794" max="14794" width="6.796875" style="4" customWidth="1"/>
+    <col min="14795" max="14797" width="8.8984375" style="4"/>
+    <col min="14798" max="14798" width="11.69921875" style="4" customWidth="1"/>
     <col min="14799" max="14799" width="7" style="4" customWidth="1"/>
-    <col min="14800" max="14800" width="8.88671875" style="4"/>
-    <col min="14801" max="14801" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14802" max="15037" width="8.88671875" style="4"/>
-    <col min="15038" max="15038" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15039" max="15039" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15040" max="15040" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15041" max="15041" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15042" max="15043" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15044" max="15045" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15046" max="15046" width="3.88671875" style="4" customWidth="1"/>
+    <col min="14800" max="14800" width="8.8984375" style="4"/>
+    <col min="14801" max="14801" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="14802" max="15037" width="8.8984375" style="4"/>
+    <col min="15038" max="15038" width="2.796875" style="4" customWidth="1"/>
+    <col min="15039" max="15039" width="17.296875" style="4" customWidth="1"/>
+    <col min="15040" max="15040" width="6.796875" style="4" customWidth="1"/>
+    <col min="15041" max="15041" width="5.296875" style="4" customWidth="1"/>
+    <col min="15042" max="15043" width="6.296875" style="4" customWidth="1"/>
+    <col min="15044" max="15045" width="4.296875" style="4" customWidth="1"/>
+    <col min="15046" max="15046" width="3.8984375" style="4" customWidth="1"/>
     <col min="15047" max="15047" width="3" style="4" customWidth="1"/>
-    <col min="15048" max="15048" width="3.21875" style="4" customWidth="1"/>
+    <col min="15048" max="15048" width="3.19921875" style="4" customWidth="1"/>
     <col min="15049" max="15049" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15050" max="15050" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15051" max="15053" width="8.88671875" style="4"/>
-    <col min="15054" max="15054" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15050" max="15050" width="6.796875" style="4" customWidth="1"/>
+    <col min="15051" max="15053" width="8.8984375" style="4"/>
+    <col min="15054" max="15054" width="11.69921875" style="4" customWidth="1"/>
     <col min="15055" max="15055" width="7" style="4" customWidth="1"/>
-    <col min="15056" max="15056" width="8.88671875" style="4"/>
-    <col min="15057" max="15057" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15058" max="15293" width="8.88671875" style="4"/>
-    <col min="15294" max="15294" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15295" max="15295" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15296" max="15296" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15297" max="15297" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15298" max="15299" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15300" max="15301" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15302" max="15302" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15056" max="15056" width="8.8984375" style="4"/>
+    <col min="15057" max="15057" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15058" max="15293" width="8.8984375" style="4"/>
+    <col min="15294" max="15294" width="2.796875" style="4" customWidth="1"/>
+    <col min="15295" max="15295" width="17.296875" style="4" customWidth="1"/>
+    <col min="15296" max="15296" width="6.796875" style="4" customWidth="1"/>
+    <col min="15297" max="15297" width="5.296875" style="4" customWidth="1"/>
+    <col min="15298" max="15299" width="6.296875" style="4" customWidth="1"/>
+    <col min="15300" max="15301" width="4.296875" style="4" customWidth="1"/>
+    <col min="15302" max="15302" width="3.8984375" style="4" customWidth="1"/>
     <col min="15303" max="15303" width="3" style="4" customWidth="1"/>
-    <col min="15304" max="15304" width="3.21875" style="4" customWidth="1"/>
+    <col min="15304" max="15304" width="3.19921875" style="4" customWidth="1"/>
     <col min="15305" max="15305" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15306" max="15306" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15307" max="15309" width="8.88671875" style="4"/>
-    <col min="15310" max="15310" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15306" max="15306" width="6.796875" style="4" customWidth="1"/>
+    <col min="15307" max="15309" width="8.8984375" style="4"/>
+    <col min="15310" max="15310" width="11.69921875" style="4" customWidth="1"/>
     <col min="15311" max="15311" width="7" style="4" customWidth="1"/>
-    <col min="15312" max="15312" width="8.88671875" style="4"/>
-    <col min="15313" max="15313" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15314" max="15549" width="8.88671875" style="4"/>
-    <col min="15550" max="15550" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15551" max="15551" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15552" max="15552" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15553" max="15553" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15554" max="15555" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15556" max="15557" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15558" max="15558" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15312" max="15312" width="8.8984375" style="4"/>
+    <col min="15313" max="15313" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15314" max="15549" width="8.8984375" style="4"/>
+    <col min="15550" max="15550" width="2.796875" style="4" customWidth="1"/>
+    <col min="15551" max="15551" width="17.296875" style="4" customWidth="1"/>
+    <col min="15552" max="15552" width="6.796875" style="4" customWidth="1"/>
+    <col min="15553" max="15553" width="5.296875" style="4" customWidth="1"/>
+    <col min="15554" max="15555" width="6.296875" style="4" customWidth="1"/>
+    <col min="15556" max="15557" width="4.296875" style="4" customWidth="1"/>
+    <col min="15558" max="15558" width="3.8984375" style="4" customWidth="1"/>
     <col min="15559" max="15559" width="3" style="4" customWidth="1"/>
-    <col min="15560" max="15560" width="3.21875" style="4" customWidth="1"/>
+    <col min="15560" max="15560" width="3.19921875" style="4" customWidth="1"/>
     <col min="15561" max="15561" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15562" max="15562" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15563" max="15565" width="8.88671875" style="4"/>
-    <col min="15566" max="15566" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15562" max="15562" width="6.796875" style="4" customWidth="1"/>
+    <col min="15563" max="15565" width="8.8984375" style="4"/>
+    <col min="15566" max="15566" width="11.69921875" style="4" customWidth="1"/>
     <col min="15567" max="15567" width="7" style="4" customWidth="1"/>
-    <col min="15568" max="15568" width="8.88671875" style="4"/>
-    <col min="15569" max="15569" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15570" max="15805" width="8.88671875" style="4"/>
-    <col min="15806" max="15806" width="2.77734375" style="4" customWidth="1"/>
-    <col min="15807" max="15807" width="17.33203125" style="4" customWidth="1"/>
-    <col min="15808" max="15808" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15809" max="15809" width="5.33203125" style="4" customWidth="1"/>
-    <col min="15810" max="15811" width="6.33203125" style="4" customWidth="1"/>
-    <col min="15812" max="15813" width="4.33203125" style="4" customWidth="1"/>
-    <col min="15814" max="15814" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15568" max="15568" width="8.8984375" style="4"/>
+    <col min="15569" max="15569" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15570" max="15805" width="8.8984375" style="4"/>
+    <col min="15806" max="15806" width="2.796875" style="4" customWidth="1"/>
+    <col min="15807" max="15807" width="17.296875" style="4" customWidth="1"/>
+    <col min="15808" max="15808" width="6.796875" style="4" customWidth="1"/>
+    <col min="15809" max="15809" width="5.296875" style="4" customWidth="1"/>
+    <col min="15810" max="15811" width="6.296875" style="4" customWidth="1"/>
+    <col min="15812" max="15813" width="4.296875" style="4" customWidth="1"/>
+    <col min="15814" max="15814" width="3.8984375" style="4" customWidth="1"/>
     <col min="15815" max="15815" width="3" style="4" customWidth="1"/>
-    <col min="15816" max="15816" width="3.21875" style="4" customWidth="1"/>
+    <col min="15816" max="15816" width="3.19921875" style="4" customWidth="1"/>
     <col min="15817" max="15817" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15818" max="15818" width="6.77734375" style="4" customWidth="1"/>
-    <col min="15819" max="15821" width="8.88671875" style="4"/>
-    <col min="15822" max="15822" width="11.6640625" style="4" customWidth="1"/>
+    <col min="15818" max="15818" width="6.796875" style="4" customWidth="1"/>
+    <col min="15819" max="15821" width="8.8984375" style="4"/>
+    <col min="15822" max="15822" width="11.69921875" style="4" customWidth="1"/>
     <col min="15823" max="15823" width="7" style="4" customWidth="1"/>
-    <col min="15824" max="15824" width="8.88671875" style="4"/>
-    <col min="15825" max="15825" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="15826" max="16061" width="8.88671875" style="4"/>
-    <col min="16062" max="16062" width="2.77734375" style="4" customWidth="1"/>
-    <col min="16063" max="16063" width="17.33203125" style="4" customWidth="1"/>
-    <col min="16064" max="16064" width="6.77734375" style="4" customWidth="1"/>
-    <col min="16065" max="16065" width="5.33203125" style="4" customWidth="1"/>
-    <col min="16066" max="16067" width="6.33203125" style="4" customWidth="1"/>
-    <col min="16068" max="16069" width="4.33203125" style="4" customWidth="1"/>
-    <col min="16070" max="16070" width="3.88671875" style="4" customWidth="1"/>
+    <col min="15824" max="15824" width="8.8984375" style="4"/>
+    <col min="15825" max="15825" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="15826" max="16061" width="8.8984375" style="4"/>
+    <col min="16062" max="16062" width="2.796875" style="4" customWidth="1"/>
+    <col min="16063" max="16063" width="17.296875" style="4" customWidth="1"/>
+    <col min="16064" max="16064" width="6.796875" style="4" customWidth="1"/>
+    <col min="16065" max="16065" width="5.296875" style="4" customWidth="1"/>
+    <col min="16066" max="16067" width="6.296875" style="4" customWidth="1"/>
+    <col min="16068" max="16069" width="4.296875" style="4" customWidth="1"/>
+    <col min="16070" max="16070" width="3.8984375" style="4" customWidth="1"/>
     <col min="16071" max="16071" width="3" style="4" customWidth="1"/>
-    <col min="16072" max="16072" width="3.21875" style="4" customWidth="1"/>
+    <col min="16072" max="16072" width="3.19921875" style="4" customWidth="1"/>
     <col min="16073" max="16073" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="16074" max="16074" width="6.77734375" style="4" customWidth="1"/>
-    <col min="16075" max="16077" width="8.88671875" style="4"/>
-    <col min="16078" max="16078" width="11.6640625" style="4" customWidth="1"/>
+    <col min="16074" max="16074" width="6.796875" style="4" customWidth="1"/>
+    <col min="16075" max="16077" width="8.8984375" style="4"/>
+    <col min="16078" max="16078" width="11.69921875" style="4" customWidth="1"/>
     <col min="16079" max="16079" width="7" style="4" customWidth="1"/>
-    <col min="16080" max="16080" width="8.88671875" style="4"/>
-    <col min="16081" max="16081" width="10.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="16082" max="16381" width="8.88671875" style="4"/>
+    <col min="16080" max="16080" width="8.8984375" style="4"/>
+    <col min="16081" max="16081" width="10.8984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="16082" max="16381" width="8.8984375" style="4"/>
     <col min="16382" max="16384" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="8.4" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A1" s="75"/>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="102"/>
+    <row r="1" spans="1:17" ht="8.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A1" s="65"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="90"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="24.75" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="78" t="s">
+    <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A2" s="71"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="79" t="s">
+      <c r="M2" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="80" t="s">
+      <c r="N2" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="99"/>
+      <c r="O2" s="87"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="26.25" customHeight="1">
-      <c r="A3" s="81"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
+    <row r="3" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="71"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
       <c r="L3" s="43"/>
       <c r="M3" s="41"/>
       <c r="N3" s="45"/>
-      <c r="O3" s="82"/>
+      <c r="O3" s="72"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:17">
-      <c r="A4" s="81"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A4" s="71"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
       <c r="L4" s="44"/>
       <c r="M4" s="42"/>
       <c r="N4" s="46"/>
-      <c r="O4" s="82"/>
+      <c r="O4" s="72"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
-      <c r="A5" s="81"/>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A5" s="71"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
       <c r="L5" s="36" t="s">
         <v>24</v>
       </c>
@@ -5222,22 +5248,22 @@
       <c r="N5" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="82"/>
+      <c r="O5" s="72"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:17" ht="25.2" thickBot="1">
-      <c r="A6" s="81"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
+    <row r="6" spans="1:17" ht="25.2" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A6" s="71"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
       <c r="L6" s="38" t="s">
         <v>27</v>
       </c>
@@ -5247,669 +5273,669 @@
       <c r="N6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="82"/>
+      <c r="O6" s="72"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:17" ht="36" customHeight="1" thickTop="1">
-      <c r="A7" s="81"/>
-      <c r="B7" s="52" t="s">
+    <row r="7" spans="1:17" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.8">
+      <c r="A7" s="71"/>
+      <c r="B7" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="52"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-      <c r="J7" s="52"/>
-      <c r="K7" s="52"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="83"/>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
+      <c r="H7" s="97"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="97"/>
+      <c r="N7" s="97"/>
+      <c r="O7" s="73"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17" ht="14.4" customHeight="1">
-      <c r="A8" s="81"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="84"/>
+    <row r="8" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A8" s="71"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="74"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
-    <row r="9" spans="1:17" ht="27.6">
-      <c r="A9" s="81"/>
-      <c r="B9" s="53" t="s">
+    <row r="9" spans="1:17" ht="27.6" x14ac:dyDescent="0.8">
+      <c r="A9" s="71"/>
+      <c r="B9" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="53" t="s">
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="50"/>
+      <c r="G9" s="50"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53"/>
-      <c r="N9" s="53"/>
-      <c r="O9" s="85"/>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10" s="81"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="86"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="75"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A10" s="71"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="76"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
-    <row r="11" spans="1:17">
-      <c r="A11" s="81"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="86"/>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A11" s="71"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="76"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
-    <row r="12" spans="1:17">
-      <c r="A12" s="81"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
-      <c r="J12" s="49"/>
-      <c r="K12" s="50"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="86"/>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A12" s="71"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
+      <c r="N12" s="96"/>
+      <c r="O12" s="76"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" ht="26.4">
-      <c r="A13" s="81"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="53" t="s">
+    <row r="13" spans="1:17" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A13" s="71"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="L13" s="56"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="85"/>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14" s="81"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="57"/>
-      <c r="M14" s="57"/>
-      <c r="N14" s="57"/>
-      <c r="O14" s="87"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="75"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A14" s="71"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="96"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
+      <c r="N14" s="96"/>
+      <c r="O14" s="77"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
-    <row r="15" spans="1:17">
-      <c r="A15" s="81"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="50"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="49"/>
-      <c r="O15" s="88"/>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A15" s="71"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="78"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
-    <row r="16" spans="1:17">
-      <c r="A16" s="81"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="59"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="86"/>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.7">
+      <c r="A16" s="71"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
+      <c r="N16" s="96"/>
+      <c r="O16" s="76"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="81"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49"/>
-      <c r="L17" s="49"/>
-      <c r="M17" s="49"/>
-      <c r="N17" s="49"/>
-      <c r="O17" s="85"/>
-    </row>
-    <row r="18" spans="1:19" ht="26.4">
-      <c r="A18" s="81"/>
-      <c r="B18" s="53" t="s">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A17" s="71"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="75"/>
+    </row>
+    <row r="18" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A18" s="71"/>
+      <c r="B18" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="56"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="53" t="s">
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="56"/>
-      <c r="M18" s="56"/>
-      <c r="N18" s="56"/>
-      <c r="O18" s="85"/>
-    </row>
-    <row r="19" spans="1:19">
-      <c r="A19" s="81"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="60" t="s">
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="75"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A19" s="71"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="89"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="79"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="9"/>
     </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="81"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="60" t="s">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A20" s="71"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="49"/>
-      <c r="O20" s="85"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="47"/>
+      <c r="O20" s="75"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="81"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="50"/>
-      <c r="J21" s="49"/>
-      <c r="K21" s="61" t="s">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A21" s="71"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="62"/>
-      <c r="O21" s="90"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="80"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
-    <row r="22" spans="1:19">
-      <c r="A22" s="81"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="49"/>
-      <c r="M22" s="49"/>
-      <c r="N22" s="49"/>
-      <c r="O22" s="85"/>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="81"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="64"/>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="85"/>
-    </row>
-    <row r="24" spans="1:19" ht="26.4">
-      <c r="A24" s="81"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="53" t="s">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A22" s="71"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
+      <c r="N22" s="47"/>
+      <c r="O22" s="75"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A23" s="71"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="57"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
+      <c r="N23" s="47"/>
+      <c r="O23" s="75"/>
+    </row>
+    <row r="24" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A24" s="71"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="47"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="L24" s="56"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="85"/>
-    </row>
-    <row r="25" spans="1:19">
-      <c r="A25" s="81"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="85"/>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="A26" s="81"/>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="66"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="85"/>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="A27" s="81"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="85"/>
-    </row>
-    <row r="28" spans="1:19" ht="26.4">
-      <c r="A28" s="81"/>
-      <c r="B28" s="53" t="s">
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="75"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A25" s="71"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="59"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="75"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A26" s="71"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="47"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="61"/>
+      <c r="O26" s="75"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A27" s="71"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="60"/>
+      <c r="N27" s="61"/>
+      <c r="O27" s="75"/>
+    </row>
+    <row r="28" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A28" s="71"/>
+      <c r="B28" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="69"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="85"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="62"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="61"/>
+      <c r="O28" s="75"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="S28" s="13"/>
     </row>
-    <row r="29" spans="1:19">
-      <c r="A29" s="81"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="82"/>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A29" s="71"/>
+      <c r="B29" s="96"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="96"/>
+      <c r="I29" s="96"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="47"/>
+      <c r="O29" s="72"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="81"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="82"/>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A30" s="71"/>
+      <c r="B30" s="96"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="96"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="96"/>
+      <c r="I30" s="96"/>
+      <c r="J30" s="47"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="64"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="47"/>
+      <c r="O30" s="72"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:19" ht="26.4">
-      <c r="A31" s="81"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="49"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="53" t="s">
+    <row r="31" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A31" s="71"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="47"/>
+      <c r="K31" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="56"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="91"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="52"/>
+      <c r="O31" s="81"/>
       <c r="P31" s="16"/>
       <c r="Q31" s="16"/>
     </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="81"/>
-      <c r="B32" s="49"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="91"/>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A32" s="71"/>
+      <c r="B32" s="96"/>
+      <c r="C32" s="96"/>
+      <c r="D32" s="96"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="96"/>
+      <c r="G32" s="96"/>
+      <c r="H32" s="96"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="96"/>
+      <c r="O32" s="81"/>
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
     </row>
-    <row r="33" spans="1:27">
-      <c r="A33" s="81"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="49"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="49"/>
-      <c r="K33" s="63"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="91"/>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A33" s="71"/>
+      <c r="B33" s="96"/>
+      <c r="C33" s="96"/>
+      <c r="D33" s="96"/>
+      <c r="E33" s="96"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="96"/>
+      <c r="H33" s="96"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="96"/>
+      <c r="O33" s="81"/>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
     </row>
-    <row r="34" spans="1:27">
-      <c r="A34" s="81"/>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="49"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="91"/>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A34" s="71"/>
+      <c r="B34" s="96"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="96"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="96"/>
+      <c r="G34" s="96"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="47"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="81"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
     </row>
-    <row r="35" spans="1:27">
-      <c r="A35" s="81"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="49"/>
-      <c r="D35" s="49"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="82"/>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A35" s="71"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="96"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="96"/>
+      <c r="J35" s="47"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="91"/>
+      <c r="O35" s="72"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
     </row>
-    <row r="36" spans="1:27">
-      <c r="A36" s="81"/>
-      <c r="B36" s="73"/>
-      <c r="C36" s="49"/>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="82"/>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A36" s="71"/>
+      <c r="B36" s="96"/>
+      <c r="C36" s="96"/>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="96"/>
+      <c r="H36" s="96"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="47"/>
+      <c r="K36" s="92"/>
+      <c r="L36" s="92"/>
+      <c r="M36" s="92"/>
+      <c r="N36" s="92"/>
+      <c r="O36" s="72"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
-    <row r="37" spans="1:27">
-      <c r="A37" s="81"/>
-      <c r="B37" s="74"/>
-      <c r="C37" s="49"/>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="72"/>
-      <c r="L37" s="72"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="72"/>
-      <c r="O37" s="82"/>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A37" s="71"/>
+      <c r="B37" s="96"/>
+      <c r="C37" s="96"/>
+      <c r="D37" s="96"/>
+      <c r="E37" s="96"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="47"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
+      <c r="M37" s="56"/>
+      <c r="N37" s="92"/>
+      <c r="O37" s="72"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
     </row>
-    <row r="38" spans="1:27">
-      <c r="A38" s="81"/>
-      <c r="B38" s="74"/>
-      <c r="C38" s="49"/>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="72"/>
-      <c r="L38" s="72"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="85"/>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.7">
+      <c r="A38" s="71"/>
+      <c r="B38" s="96"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="47"/>
+      <c r="K38" s="92"/>
+      <c r="L38" s="92"/>
+      <c r="M38" s="56"/>
+      <c r="N38" s="92"/>
+      <c r="O38" s="75"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:27" ht="32.4" customHeight="1" thickBot="1">
-      <c r="A39" s="92" t="s">
+    <row r="39" spans="1:27" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A39" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="93"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="94"/>
-      <c r="J39" s="95"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="96"/>
-      <c r="N39" s="97"/>
-      <c r="O39" s="98"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="84"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="85"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="93"/>
+      <c r="N39" s="94"/>
+      <c r="O39" s="86"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11"/>
     </row>
-    <row r="40" spans="1:27" ht="30" customHeight="1">
+    <row r="40" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B40" s="17"/>
       <c r="J40" s="20"/>
       <c r="K40" s="14"/>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.7">
       <c r="B41" s="18"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
       <c r="M41" s="14"/>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.7">
       <c r="B42" s="18"/>
       <c r="J42" s="6"/>
       <c r="M42" s="14"/>
     </row>
-    <row r="43" spans="1:27" ht="33" customHeight="1">
+    <row r="43" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B43" s="18"/>
       <c r="J43" s="6"/>
       <c r="M43" s="2"/>
     </row>
-    <row r="44" spans="1:27" ht="33.75" customHeight="1">
+    <row r="44" spans="1:27" ht="33.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B44" s="21"/>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
@@ -5920,7 +5946,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="6"/>
     </row>
-    <row r="45" spans="1:27" ht="46.5" customHeight="1">
+    <row r="45" spans="1:27" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B45" s="1"/>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
@@ -5931,7 +5957,7 @@
       <c r="I45" s="20"/>
       <c r="J45" s="14"/>
     </row>
-    <row r="46" spans="1:27" ht="27.75" customHeight="1">
+    <row r="46" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B46" s="22"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -5944,7 +5970,7 @@
       <c r="T46" s="24"/>
       <c r="U46" s="24"/>
     </row>
-    <row r="47" spans="1:27" ht="27.75" customHeight="1">
+    <row r="47" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B47" s="12"/>
       <c r="C47" s="6"/>
       <c r="D47" s="6"/>
@@ -5964,7 +5990,7 @@
       <c r="Z47" s="24"/>
       <c r="AA47" s="24"/>
     </row>
-    <row r="48" spans="1:27" ht="21.75" customHeight="1">
+    <row r="48" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B48" s="12"/>
       <c r="C48" s="6"/>
       <c r="D48" s="6"/>
@@ -5984,15 +6010,15 @@
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
     </row>
-    <row r="49" spans="2:27">
+    <row r="49" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B49" s="12"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
+      <c r="C49" s="99"/>
+      <c r="D49" s="99"/>
+      <c r="E49" s="99"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="99"/>
+      <c r="I49" s="99"/>
       <c r="J49" s="23"/>
       <c r="S49" s="12"/>
       <c r="T49" s="8"/>
@@ -6004,7 +6030,7 @@
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
     </row>
-    <row r="50" spans="2:27">
+    <row r="50" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B50" s="22"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -6023,15 +6049,15 @@
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
     </row>
-    <row r="51" spans="2:27">
+    <row r="51" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B51" s="26"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="47"/>
-      <c r="I51" s="47"/>
+      <c r="C51" s="98"/>
+      <c r="D51" s="98"/>
+      <c r="E51" s="98"/>
+      <c r="F51" s="98"/>
+      <c r="G51" s="98"/>
+      <c r="H51" s="98"/>
+      <c r="I51" s="98"/>
       <c r="S51" s="12"/>
       <c r="T51" s="27"/>
       <c r="U51" s="27"/>
@@ -6042,7 +6068,7 @@
       <c r="Z51" s="27"/>
       <c r="AA51" s="27"/>
     </row>
-    <row r="52" spans="2:27">
+    <row r="52" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B52" s="22"/>
       <c r="C52" s="12"/>
       <c r="D52" s="14"/>
@@ -6061,7 +6087,7 @@
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
     </row>
-    <row r="53" spans="2:27">
+    <row r="53" spans="2:27" x14ac:dyDescent="0.7">
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
@@ -6079,7 +6105,7 @@
       <c r="Z53" s="27"/>
       <c r="AA53" s="27"/>
     </row>
-    <row r="54" spans="2:27">
+    <row r="54" spans="2:27" x14ac:dyDescent="0.7">
       <c r="C54" s="23"/>
       <c r="D54" s="23"/>
       <c r="E54" s="23"/>
@@ -6097,14 +6123,14 @@
       <c r="Z54" s="27"/>
       <c r="AA54" s="27"/>
     </row>
-    <row r="55" spans="2:27">
-      <c r="C55" s="47"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="47"/>
-      <c r="F55" s="47"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="47"/>
-      <c r="I55" s="47"/>
+    <row r="55" spans="2:27" x14ac:dyDescent="0.7">
+      <c r="C55" s="98"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="98"/>
+      <c r="F55" s="98"/>
+      <c r="G55" s="98"/>
+      <c r="H55" s="98"/>
+      <c r="I55" s="98"/>
       <c r="S55" s="12"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
@@ -6115,7 +6141,7 @@
       <c r="Z55" s="27"/>
       <c r="AA55" s="27"/>
     </row>
-    <row r="56" spans="2:27">
+    <row r="56" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S56" s="22"/>
       <c r="T56" s="28"/>
       <c r="U56" s="27"/>
@@ -6126,7 +6152,7 @@
       <c r="Z56" s="14"/>
       <c r="AA56" s="14"/>
     </row>
-    <row r="57" spans="2:27">
+    <row r="57" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S57" s="26"/>
       <c r="T57" s="27"/>
       <c r="U57" s="27"/>
@@ -6137,7 +6163,7 @@
       <c r="Z57" s="27"/>
       <c r="AA57" s="23"/>
     </row>
-    <row r="58" spans="2:27">
+    <row r="58" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S58" s="26"/>
       <c r="T58" s="12"/>
       <c r="U58" s="14"/>
@@ -6148,7 +6174,7 @@
       <c r="Z58" s="27"/>
       <c r="AA58" s="23"/>
     </row>
-    <row r="59" spans="2:27">
+    <row r="59" spans="2:27" x14ac:dyDescent="0.7">
       <c r="S59" s="22"/>
       <c r="T59" s="25"/>
       <c r="U59" s="25"/>
@@ -6159,7 +6185,7 @@
       <c r="Z59" s="14"/>
       <c r="AA59" s="14"/>
     </row>
-    <row r="60" spans="2:27" ht="20.25" customHeight="1">
+    <row r="60" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="T60" s="25"/>
       <c r="U60" s="25"/>
       <c r="V60" s="25"/>
@@ -6169,7 +6195,7 @@
       <c r="Z60" s="25"/>
       <c r="AA60" s="25"/>
     </row>
-    <row r="61" spans="2:27" ht="20.25" customHeight="1">
+    <row r="61" spans="2:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="T61" s="27"/>
       <c r="U61" s="27"/>
       <c r="V61" s="25"/>
@@ -6179,7 +6205,7 @@
       <c r="Z61" s="25"/>
       <c r="AA61" s="25"/>
     </row>
-    <row r="62" spans="2:27">
+    <row r="62" spans="2:27" x14ac:dyDescent="0.7">
       <c r="V62" s="27"/>
       <c r="W62" s="27"/>
       <c r="X62" s="27"/>
@@ -6187,15 +6213,34 @@
       <c r="Z62" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="23">
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="C49:I49"/>
     <mergeCell ref="C51:I51"/>
     <mergeCell ref="C55:I55"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B31:I31"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B35:I35"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0"/>
-  <pageSetup paperSize="9" scale="84" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="81" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -6203,13 +6248,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C44CA069-DD46-44C2-B51F-E28374130FB1}">
   <dimension ref="B1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="17.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15" thickBot="1"/>
-    <row r="2" spans="2:4" ht="24" thickTop="1">
+    <row r="1" spans="2:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" ht="24" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="s">
         <v>21</v>
       </c>
@@ -6220,12 +6265,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="60.6" customHeight="1">
+    <row r="3" spans="2:4" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="34"/>
       <c r="C3" s="30"/>
       <c r="D3" s="35"/>
     </row>
-    <row r="4" spans="2:4" ht="23.4">
+    <row r="4" spans="2:4" ht="23.4" x14ac:dyDescent="0.25">
       <c r="B4" s="36" t="s">
         <v>24</v>
       </c>
@@ -6236,7 +6281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="24" thickBot="1">
+    <row r="5" spans="2:4" ht="24" thickBot="1" x14ac:dyDescent="0.65">
       <c r="B5" s="38" t="s">
         <v>27</v>
       </c>
@@ -6247,7 +6292,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15" thickTop="1"/>
+    <row r="6" spans="2:4" ht="14.4" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6255,12 +6300,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0e05454c-eb7b-40d5-ae38-03182eec583a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="37c8a04e-6aad-4710-b0b6-349bbaa6ed21">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6477,33 +6524,48 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0e05454c-eb7b-40d5-ae38-03182eec583a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="37c8a04e-6aad-4710-b0b6-349bbaa6ed21">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF9D37D0-8E59-47D8-A7D0-68637E9D3071}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0e05454c-eb7b-40d5-ae38-03182eec583a"/>
+    <ds:schemaRef ds:uri="37c8a04e-6aad-4710-b0b6-349bbaa6ed21"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A6DC5B-558C-4B81-92CF-02D705EA61D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="37c8a04e-6aad-4710-b0b6-349bbaa6ed21"/>
+    <ds:schemaRef ds:uri="0e05454c-eb7b-40d5-ae38-03182eec583a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8676498B-F0A8-4913-96CA-3F86D514A29D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03A6DC5B-558C-4B81-92CF-02D705EA61D7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF9D37D0-8E59-47D8-A7D0-68637E9D3071}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/app/Excel/ATA-F-HD-005-Couse Outline.xlsx
+++ b/app/Excel/ATA-F-HD-005-Couse Outline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trainee\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECE0244-6E60-4F48-B5C2-A8934D305137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC3D662-0E37-4FD9-9997-7ECE7000C6FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{BC99A250-FEBB-43EA-840D-941C3158CE7C}"/>
   </bookViews>
@@ -650,7 +650,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -772,18 +772,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="2"/>
-    </xf>
-    <xf numFmtId="188" fontId="5" fillId="2" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -833,20 +821,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -857,8 +833,14 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1065,7 +1047,7 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="1600">
+          <a:endParaRPr lang="th-TH" sz="1600">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -1180,6 +1162,132 @@
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB15E0F8-65D3-0F89-CA9B-49B09ED11896}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="83820" y="8732520"/>
+          <a:ext cx="4229100" cy="3253740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>259080</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1CA39CA5-1936-5FDB-6528-F8F5CEAE683C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4389120" y="3962400"/>
+          <a:ext cx="4861560" cy="1188720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1486,6 +1594,195 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C7F8BD-9A4B-D5B6-8481-7187334A0F07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4404360" y="2682240"/>
+          <a:ext cx="4792980" cy="944880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>144780</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{442C1EDC-75E6-5831-4CC5-51B31CA29F7C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="91440" y="8732520"/>
+          <a:ext cx="4191000" cy="3215640"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1DC388-E8FF-3FFF-D376-9A2B3603FEDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4389120" y="4008120"/>
+          <a:ext cx="4808220" cy="1150620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="th-TH" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1512,6 +1809,28 @@
       <sheetName val="A"/>
       <sheetName val="DATA_STD_VC_EXPORT1"/>
       <sheetName val="Cash_Gen_1"/>
+      <sheetName val="DATA_STD_VC_EXPORT2"/>
+      <sheetName val="Cash_Gen_2"/>
+      <sheetName val="DATA_STD_VC_EXPORT3"/>
+      <sheetName val="Cash_Gen_3"/>
+      <sheetName val="DATA_STD_VC_EXPORT4"/>
+      <sheetName val="Cash_Gen_4"/>
+      <sheetName val="DATA_STD_VC_EXPORT5"/>
+      <sheetName val="Cash_Gen_5"/>
+      <sheetName val="DATA_STD_VC_EXPORT6"/>
+      <sheetName val="Cash_Gen_6"/>
+      <sheetName val="PS"/>
+      <sheetName val="CODE"/>
+      <sheetName val="61B (J)"/>
+      <sheetName val="X61B (E)"/>
+      <sheetName val="DATA_STD_VC_EXPORT7"/>
+      <sheetName val="Cash_Gen_7"/>
+      <sheetName val="61B_(J)"/>
+      <sheetName val="X61B_(E)"/>
+      <sheetName val="DATA_STD_VC_EXPORT8"/>
+      <sheetName val="Cash_Gen_8"/>
+      <sheetName val="61B_(J)1"/>
+      <sheetName val="X61B_(E)1"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -1533,6 +1852,28 @@
       <sheetData sheetId="16" refreshError="1"/>
       <sheetData sheetId="17"/>
       <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33"/>
+      <sheetData sheetId="34"/>
+      <sheetData sheetId="35"/>
+      <sheetData sheetId="36"/>
+      <sheetData sheetId="37"/>
+      <sheetData sheetId="38"/>
+      <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2937,26 +3278,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="8.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="65"/>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="90"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="84"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
     <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A2" s="71"/>
+      <c r="A2" s="65"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -2967,21 +3308,21 @@
       <c r="I2" s="49"/>
       <c r="J2" s="49"/>
       <c r="K2" s="49"/>
-      <c r="L2" s="68" t="s">
+      <c r="L2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="87"/>
+      <c r="O2" s="81"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
     <row r="3" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="71"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -2995,12 +3336,12 @@
       <c r="L3" s="43"/>
       <c r="M3" s="41"/>
       <c r="N3" s="45"/>
-      <c r="O3" s="72"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A4" s="71"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -3014,12 +3355,12 @@
       <c r="L4" s="44"/>
       <c r="M4" s="42"/>
       <c r="N4" s="46"/>
-      <c r="O4" s="72"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A5" s="71"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
       <c r="D5" s="48"/>
@@ -3039,12 +3380,12 @@
       <c r="N5" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="72"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="25.2" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="71"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
@@ -3064,33 +3405,33 @@
       <c r="N6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="72"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.8">
-      <c r="A7" s="71"/>
-      <c r="B7" s="97" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="73"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="67"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A8" s="71"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
       <c r="D8" s="49"/>
@@ -3104,12 +3445,12 @@
       <c r="L8" s="49"/>
       <c r="M8" s="49"/>
       <c r="N8" s="49"/>
-      <c r="O8" s="74"/>
+      <c r="O8" s="68"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" ht="27.6" x14ac:dyDescent="0.8">
-      <c r="A9" s="71"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="50" t="s">
         <v>1</v>
       </c>
@@ -3127,10 +3468,10 @@
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
       <c r="N9" s="50"/>
-      <c r="O9" s="75"/>
+      <c r="O9" s="69"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A10" s="71"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="47"/>
       <c r="C10" s="47"/>
       <c r="D10" s="47"/>
@@ -3140,16 +3481,16 @@
       <c r="H10" s="47"/>
       <c r="I10" s="47"/>
       <c r="J10" s="47"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="76"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="93"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A11" s="71"/>
+      <c r="A11" s="65"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -3159,16 +3500,16 @@
       <c r="H11" s="48"/>
       <c r="I11" s="48"/>
       <c r="J11" s="47"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="76"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="93"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A12" s="71"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
@@ -3178,16 +3519,16 @@
       <c r="H12" s="48"/>
       <c r="I12" s="48"/>
       <c r="J12" s="47"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="76"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
     <row r="13" spans="1:17" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A13" s="71"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
       <c r="D13" s="48"/>
@@ -3203,10 +3544,10 @@
       <c r="L13" s="52"/>
       <c r="M13" s="52"/>
       <c r="N13" s="52"/>
-      <c r="O13" s="75"/>
+      <c r="O13" s="69"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A14" s="71"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="48"/>
@@ -3216,16 +3557,16 @@
       <c r="H14" s="48"/>
       <c r="I14" s="48"/>
       <c r="J14" s="47"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="77"/>
+      <c r="K14" s="93"/>
+      <c r="L14" s="93"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="71"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A15" s="71"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
@@ -3235,16 +3576,16 @@
       <c r="H15" s="48"/>
       <c r="I15" s="48"/>
       <c r="J15" s="47"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="78"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="93"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="93"/>
+      <c r="O15" s="72"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A16" s="71"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="53"/>
       <c r="C16" s="48"/>
       <c r="D16" s="48"/>
@@ -3254,16 +3595,16 @@
       <c r="H16" s="48"/>
       <c r="I16" s="48"/>
       <c r="J16" s="47"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="76"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A17" s="71"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="53"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
@@ -3273,14 +3614,14 @@
       <c r="H17" s="48"/>
       <c r="I17" s="48"/>
       <c r="J17" s="47"/>
-      <c r="K17" s="96"/>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="96"/>
-      <c r="O17" s="75"/>
+      <c r="K17" s="93"/>
+      <c r="L17" s="93"/>
+      <c r="M17" s="93"/>
+      <c r="N17" s="93"/>
+      <c r="O17" s="69"/>
     </row>
     <row r="18" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A18" s="71"/>
+      <c r="A18" s="65"/>
       <c r="B18" s="50" t="s">
         <v>4</v>
       </c>
@@ -3298,10 +3639,10 @@
       <c r="L18" s="52"/>
       <c r="M18" s="52"/>
       <c r="N18" s="52"/>
-      <c r="O18" s="75"/>
+      <c r="O18" s="69"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A19" s="71"/>
+      <c r="A19" s="65"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
@@ -3317,12 +3658,12 @@
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
       <c r="N19" s="48"/>
-      <c r="O19" s="79"/>
+      <c r="O19" s="73"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="9"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A20" s="71"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="47"/>
       <c r="C20" s="47"/>
       <c r="D20" s="48"/>
@@ -3338,12 +3679,12 @@
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
       <c r="N20" s="47"/>
-      <c r="O20" s="75"/>
+      <c r="O20" s="69"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A21" s="71"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="53"/>
       <c r="C21" s="48"/>
       <c r="D21" s="48"/>
@@ -3359,12 +3700,12 @@
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
       <c r="N21" s="56"/>
-      <c r="O21" s="80"/>
+      <c r="O21" s="74"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A22" s="71"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="47"/>
       <c r="C22" s="47"/>
       <c r="D22" s="47"/>
@@ -3378,10 +3719,10 @@
       <c r="L22" s="47"/>
       <c r="M22" s="47"/>
       <c r="N22" s="47"/>
-      <c r="O22" s="75"/>
+      <c r="O22" s="69"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A23" s="71"/>
+      <c r="A23" s="65"/>
       <c r="B23" s="47"/>
       <c r="C23" s="58"/>
       <c r="D23" s="58"/>
@@ -3395,10 +3736,10 @@
       <c r="L23" s="47"/>
       <c r="M23" s="47"/>
       <c r="N23" s="47"/>
-      <c r="O23" s="75"/>
+      <c r="O23" s="69"/>
     </row>
     <row r="24" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A24" s="71"/>
+      <c r="A24" s="65"/>
       <c r="B24" s="47"/>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
@@ -3414,10 +3755,10 @@
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
       <c r="N24" s="52"/>
-      <c r="O24" s="75"/>
+      <c r="O24" s="69"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A25" s="71"/>
+      <c r="A25" s="65"/>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -3427,14 +3768,14 @@
       <c r="H25" s="47"/>
       <c r="I25" s="47"/>
       <c r="J25" s="47"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
-      <c r="O25" s="75"/>
+      <c r="K25" s="93"/>
+      <c r="L25" s="93"/>
+      <c r="M25" s="93"/>
+      <c r="N25" s="93"/>
+      <c r="O25" s="69"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A26" s="71"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="47"/>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -3444,14 +3785,14 @@
       <c r="H26" s="47"/>
       <c r="I26" s="47"/>
       <c r="J26" s="47"/>
-      <c r="K26" s="96"/>
-      <c r="L26" s="96"/>
-      <c r="M26" s="96"/>
-      <c r="N26" s="96"/>
-      <c r="O26" s="75"/>
+      <c r="K26" s="93"/>
+      <c r="L26" s="93"/>
+      <c r="M26" s="93"/>
+      <c r="N26" s="93"/>
+      <c r="O26" s="69"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A27" s="71"/>
+      <c r="A27" s="65"/>
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -3461,14 +3802,14 @@
       <c r="H27" s="47"/>
       <c r="I27" s="47"/>
       <c r="J27" s="47"/>
-      <c r="K27" s="96"/>
-      <c r="L27" s="96"/>
-      <c r="M27" s="96"/>
-      <c r="N27" s="96"/>
-      <c r="O27" s="75"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="69"/>
     </row>
     <row r="28" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A28" s="71"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="50" t="s">
         <v>10</v>
       </c>
@@ -3480,225 +3821,225 @@
       <c r="H28" s="52"/>
       <c r="I28" s="52"/>
       <c r="J28" s="47"/>
-      <c r="K28" s="96"/>
-      <c r="L28" s="96"/>
-      <c r="M28" s="96"/>
-      <c r="N28" s="96"/>
-      <c r="O28" s="75"/>
+      <c r="K28" s="93"/>
+      <c r="L28" s="93"/>
+      <c r="M28" s="93"/>
+      <c r="N28" s="93"/>
+      <c r="O28" s="69"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="S28" s="13"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A29" s="71"/>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96"/>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
       <c r="J29" s="47"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-      <c r="M29" s="96"/>
-      <c r="N29" s="96"/>
-      <c r="O29" s="72"/>
+      <c r="K29" s="93"/>
+      <c r="L29" s="93"/>
+      <c r="M29" s="93"/>
+      <c r="N29" s="93"/>
+      <c r="O29" s="66"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A30" s="71"/>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
       <c r="J30" s="47"/>
-      <c r="K30" s="96"/>
-      <c r="L30" s="96"/>
-      <c r="M30" s="96"/>
-      <c r="N30" s="96"/>
-      <c r="O30" s="72"/>
+      <c r="K30" s="93"/>
+      <c r="L30" s="93"/>
+      <c r="M30" s="93"/>
+      <c r="N30" s="93"/>
+      <c r="O30" s="66"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A31" s="71"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A31" s="65"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
       <c r="J31" s="47"/>
-      <c r="K31" s="50" t="s">
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A32" s="65"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="92"/>
+      <c r="L32" s="92"/>
+      <c r="M32" s="92"/>
+      <c r="N32" s="92"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+    </row>
+    <row r="33" spans="1:27" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A33" s="65"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A32" s="71"/>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A33" s="71"/>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="81"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="75"/>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A34" s="71"/>
-      <c r="B34" s="100"/>
-      <c r="C34" s="100"/>
-      <c r="D34" s="100"/>
-      <c r="E34" s="100"/>
-      <c r="F34" s="100"/>
-      <c r="G34" s="100"/>
-      <c r="H34" s="100"/>
-      <c r="I34" s="100"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="92"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="92"/>
+      <c r="F34" s="92"/>
+      <c r="G34" s="92"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
       <c r="J34" s="47"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="81"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="93"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="75"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A35" s="71"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="96"/>
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
+      <c r="A35" s="65"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="93"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
       <c r="J35" s="47"/>
-      <c r="K35" s="96"/>
-      <c r="L35" s="96"/>
-      <c r="M35" s="96"/>
-      <c r="N35" s="96"/>
-      <c r="O35" s="72"/>
+      <c r="K35" s="93"/>
+      <c r="L35" s="93"/>
+      <c r="M35" s="93"/>
+      <c r="N35" s="93"/>
+      <c r="O35" s="66"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A36" s="71"/>
-      <c r="B36" s="95"/>
-      <c r="C36" s="95"/>
-      <c r="D36" s="95"/>
-      <c r="E36" s="95"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="I36" s="95"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
       <c r="J36" s="47"/>
-      <c r="K36" s="96"/>
-      <c r="L36" s="96"/>
-      <c r="M36" s="96"/>
-      <c r="N36" s="96"/>
-      <c r="O36" s="72"/>
+      <c r="K36" s="93"/>
+      <c r="L36" s="93"/>
+      <c r="M36" s="93"/>
+      <c r="N36" s="93"/>
+      <c r="O36" s="66"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A37" s="71"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="95"/>
-      <c r="D37" s="95"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="95"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
-      <c r="I37" s="95"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="86"/>
+      <c r="C37" s="86"/>
+      <c r="D37" s="86"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="I37" s="86"/>
       <c r="J37" s="47"/>
-      <c r="K37" s="96"/>
-      <c r="L37" s="96"/>
-      <c r="M37" s="96"/>
-      <c r="N37" s="96"/>
-      <c r="O37" s="72"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="93"/>
+      <c r="M37" s="93"/>
+      <c r="N37" s="93"/>
+      <c r="O37" s="66"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A38" s="71"/>
-      <c r="B38" s="96"/>
-      <c r="C38" s="96"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="96"/>
-      <c r="G38" s="96"/>
-      <c r="H38" s="96"/>
-      <c r="I38" s="96"/>
+      <c r="A38" s="65"/>
+      <c r="B38" s="93"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
       <c r="J38" s="47"/>
-      <c r="K38" s="96"/>
-      <c r="L38" s="96"/>
-      <c r="M38" s="96"/>
-      <c r="N38" s="96"/>
-      <c r="O38" s="75"/>
+      <c r="K38" s="93"/>
+      <c r="L38" s="93"/>
+      <c r="M38" s="93"/>
+      <c r="N38" s="93"/>
+      <c r="O38" s="69"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
     <row r="39" spans="1:27" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A39" s="82" t="s">
+      <c r="A39" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="83"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="96"/>
-      <c r="M39" s="96"/>
-      <c r="N39" s="96"/>
-      <c r="O39" s="86"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="93"/>
+      <c r="L39" s="93"/>
+      <c r="M39" s="93"/>
+      <c r="N39" s="93"/>
+      <c r="O39" s="80"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11"/>
     </row>
@@ -3712,7 +4053,7 @@
     <row r="41" spans="1:27" x14ac:dyDescent="0.7">
       <c r="B41" s="18"/>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="2"/>
       <c r="M41" s="14"/>
     </row>
@@ -3803,13 +4144,13 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B49" s="12"/>
-      <c r="C49" s="99"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="99"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="99"/>
-      <c r="I49" s="99"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
       <c r="J49" s="23"/>
       <c r="S49" s="12"/>
       <c r="T49" s="8"/>
@@ -3842,13 +4183,13 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B51" s="26"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="98"/>
-      <c r="G51" s="98"/>
-      <c r="H51" s="98"/>
-      <c r="I51" s="98"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="88"/>
+      <c r="I51" s="88"/>
       <c r="S51" s="12"/>
       <c r="T51" s="27"/>
       <c r="U51" s="27"/>
@@ -3915,13 +4256,13 @@
       <c r="AA54" s="27"/>
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.7">
-      <c r="C55" s="98"/>
-      <c r="D55" s="98"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="98"/>
-      <c r="G55" s="98"/>
-      <c r="H55" s="98"/>
-      <c r="I55" s="98"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="88"/>
+      <c r="E55" s="88"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88"/>
+      <c r="H55" s="88"/>
+      <c r="I55" s="88"/>
       <c r="S55" s="12"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
@@ -4004,40 +4345,11 @@
       <c r="Z62" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
+  <mergeCells count="4">
     <mergeCell ref="C55:I55"/>
     <mergeCell ref="C49:I49"/>
     <mergeCell ref="C51:I51"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B7:N7"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0"/>
@@ -5146,26 +5458,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="8.4" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A1" s="65"/>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="90"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="84"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
     </row>
     <row r="2" spans="1:17" ht="24.75" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A2" s="71"/>
+      <c r="A2" s="65"/>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
@@ -5176,21 +5488,21 @@
       <c r="I2" s="49"/>
       <c r="J2" s="49"/>
       <c r="K2" s="49"/>
-      <c r="L2" s="68" t="s">
+      <c r="L2" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="70" t="s">
+      <c r="N2" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="87"/>
+      <c r="O2" s="81"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
     </row>
     <row r="3" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="71"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
       <c r="D3" s="48"/>
@@ -5204,12 +5516,12 @@
       <c r="L3" s="43"/>
       <c r="M3" s="41"/>
       <c r="N3" s="45"/>
-      <c r="O3" s="72"/>
+      <c r="O3" s="66"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A4" s="71"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
       <c r="D4" s="48"/>
@@ -5223,12 +5535,12 @@
       <c r="L4" s="44"/>
       <c r="M4" s="42"/>
       <c r="N4" s="46"/>
-      <c r="O4" s="72"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A5" s="71"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="48"/>
       <c r="C5" s="48"/>
       <c r="D5" s="48"/>
@@ -5248,12 +5560,12 @@
       <c r="N5" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="O5" s="72"/>
+      <c r="O5" s="66"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="25.2" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A6" s="71"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="48"/>
       <c r="C6" s="48"/>
       <c r="D6" s="48"/>
@@ -5273,33 +5585,33 @@
       <c r="N6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="O6" s="72"/>
+      <c r="O6" s="66"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:17" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.8">
-      <c r="A7" s="71"/>
-      <c r="B7" s="97" t="s">
+      <c r="A7" s="65"/>
+      <c r="B7" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="97"/>
-      <c r="G7" s="97"/>
-      <c r="H7" s="97"/>
-      <c r="I7" s="97"/>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="97"/>
-      <c r="M7" s="97"/>
-      <c r="N7" s="97"/>
-      <c r="O7" s="73"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="67"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A8" s="71"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="49"/>
       <c r="C8" s="49"/>
       <c r="D8" s="49"/>
@@ -5313,12 +5625,12 @@
       <c r="L8" s="49"/>
       <c r="M8" s="49"/>
       <c r="N8" s="49"/>
-      <c r="O8" s="74"/>
+      <c r="O8" s="68"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:17" ht="27.6" x14ac:dyDescent="0.8">
-      <c r="A9" s="71"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="50" t="s">
         <v>13</v>
       </c>
@@ -5336,10 +5648,10 @@
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
       <c r="N9" s="50"/>
-      <c r="O9" s="75"/>
+      <c r="O9" s="69"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A10" s="71"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="47"/>
       <c r="C10" s="47"/>
       <c r="D10" s="47"/>
@@ -5349,16 +5661,16 @@
       <c r="H10" s="47"/>
       <c r="I10" s="47"/>
       <c r="J10" s="47"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="76"/>
+      <c r="K10" s="93"/>
+      <c r="L10" s="93"/>
+      <c r="M10" s="93"/>
+      <c r="N10" s="93"/>
+      <c r="O10" s="70"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A11" s="71"/>
+      <c r="A11" s="65"/>
       <c r="B11" s="48"/>
       <c r="C11" s="48"/>
       <c r="D11" s="48"/>
@@ -5368,16 +5680,16 @@
       <c r="H11" s="48"/>
       <c r="I11" s="48"/>
       <c r="J11" s="47"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="76"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="93"/>
+      <c r="O11" s="70"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A12" s="71"/>
+      <c r="A12" s="65"/>
       <c r="B12" s="48"/>
       <c r="C12" s="48"/>
       <c r="D12" s="48"/>
@@ -5387,16 +5699,16 @@
       <c r="H12" s="48"/>
       <c r="I12" s="48"/>
       <c r="J12" s="47"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="76"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="70"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
     </row>
     <row r="13" spans="1:17" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A13" s="71"/>
+      <c r="A13" s="65"/>
       <c r="B13" s="48"/>
       <c r="C13" s="48"/>
       <c r="D13" s="48"/>
@@ -5412,10 +5724,10 @@
       <c r="L13" s="52"/>
       <c r="M13" s="52"/>
       <c r="N13" s="52"/>
-      <c r="O13" s="75"/>
+      <c r="O13" s="69"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A14" s="71"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="48"/>
       <c r="C14" s="48"/>
       <c r="D14" s="48"/>
@@ -5425,16 +5737,15 @@
       <c r="H14" s="48"/>
       <c r="I14" s="48"/>
       <c r="J14" s="47"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="77"/>
+      <c r="K14" s="93"/>
+      <c r="M14" s="93"/>
+      <c r="N14" s="93"/>
+      <c r="O14" s="71"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A15" s="71"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48"/>
       <c r="D15" s="48"/>
@@ -5444,16 +5755,13 @@
       <c r="H15" s="48"/>
       <c r="I15" s="48"/>
       <c r="J15" s="47"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="78"/>
+      <c r="K15" s="94"/>
+      <c r="O15" s="72"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.7">
-      <c r="A16" s="71"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="53"/>
       <c r="C16" s="48"/>
       <c r="D16" s="48"/>
@@ -5463,16 +5771,16 @@
       <c r="H16" s="48"/>
       <c r="I16" s="48"/>
       <c r="J16" s="47"/>
-      <c r="K16" s="96"/>
-      <c r="L16" s="96"/>
-      <c r="M16" s="96"/>
-      <c r="N16" s="96"/>
-      <c r="O16" s="76"/>
+      <c r="K16" s="93"/>
+      <c r="L16" s="93"/>
+      <c r="M16" s="93"/>
+      <c r="N16" s="93"/>
+      <c r="O16" s="70"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A17" s="71"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="53"/>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
@@ -5482,14 +5790,14 @@
       <c r="H17" s="48"/>
       <c r="I17" s="48"/>
       <c r="J17" s="47"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="91"/>
-      <c r="O17" s="75"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="85"/>
+      <c r="N17" s="85"/>
+      <c r="O17" s="69"/>
     </row>
     <row r="18" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A18" s="71"/>
+      <c r="A18" s="65"/>
       <c r="B18" s="50" t="s">
         <v>16</v>
       </c>
@@ -5507,10 +5815,10 @@
       <c r="L18" s="52"/>
       <c r="M18" s="52"/>
       <c r="N18" s="52"/>
-      <c r="O18" s="75"/>
+      <c r="O18" s="69"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A19" s="71"/>
+      <c r="A19" s="65"/>
       <c r="B19" s="48"/>
       <c r="C19" s="48"/>
       <c r="D19" s="48"/>
@@ -5526,12 +5834,12 @@
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
       <c r="N19" s="48"/>
-      <c r="O19" s="79"/>
+      <c r="O19" s="73"/>
       <c r="P19" s="10"/>
       <c r="Q19" s="9"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A20" s="71"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="47"/>
       <c r="C20" s="47"/>
       <c r="D20" s="48"/>
@@ -5547,12 +5855,12 @@
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
       <c r="N20" s="47"/>
-      <c r="O20" s="75"/>
+      <c r="O20" s="69"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A21" s="71"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="53"/>
       <c r="C21" s="48"/>
       <c r="D21" s="48"/>
@@ -5568,12 +5876,12 @@
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
       <c r="N21" s="56"/>
-      <c r="O21" s="80"/>
+      <c r="O21" s="74"/>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A22" s="71"/>
+      <c r="A22" s="65"/>
       <c r="B22" s="47"/>
       <c r="C22" s="47"/>
       <c r="D22" s="47"/>
@@ -5587,10 +5895,10 @@
       <c r="L22" s="47"/>
       <c r="M22" s="47"/>
       <c r="N22" s="47"/>
-      <c r="O22" s="75"/>
+      <c r="O22" s="69"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A23" s="71"/>
+      <c r="A23" s="65"/>
       <c r="B23" s="47"/>
       <c r="C23" s="58"/>
       <c r="D23" s="58"/>
@@ -5604,10 +5912,10 @@
       <c r="L23" s="47"/>
       <c r="M23" s="47"/>
       <c r="N23" s="47"/>
-      <c r="O23" s="75"/>
+      <c r="O23" s="69"/>
     </row>
     <row r="24" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A24" s="71"/>
+      <c r="A24" s="65"/>
       <c r="B24" s="47"/>
       <c r="C24" s="47"/>
       <c r="D24" s="47"/>
@@ -5623,10 +5931,10 @@
       <c r="L24" s="52"/>
       <c r="M24" s="52"/>
       <c r="N24" s="52"/>
-      <c r="O24" s="75"/>
+      <c r="O24" s="69"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A25" s="71"/>
+      <c r="A25" s="65"/>
       <c r="B25" s="47"/>
       <c r="C25" s="47"/>
       <c r="D25" s="47"/>
@@ -5636,14 +5944,14 @@
       <c r="H25" s="47"/>
       <c r="I25" s="47"/>
       <c r="J25" s="47"/>
-      <c r="K25" s="59"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="60"/>
-      <c r="N25" s="61"/>
-      <c r="O25" s="75"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="69"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A26" s="71"/>
+      <c r="A26" s="65"/>
       <c r="B26" s="47"/>
       <c r="C26" s="47"/>
       <c r="D26" s="47"/>
@@ -5653,14 +5961,14 @@
       <c r="H26" s="47"/>
       <c r="I26" s="47"/>
       <c r="J26" s="47"/>
-      <c r="K26" s="59"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="60"/>
-      <c r="N26" s="61"/>
-      <c r="O26" s="75"/>
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="69"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A27" s="71"/>
+      <c r="A27" s="65"/>
       <c r="B27" s="47"/>
       <c r="C27" s="47"/>
       <c r="D27" s="47"/>
@@ -5670,14 +5978,14 @@
       <c r="H27" s="47"/>
       <c r="I27" s="47"/>
       <c r="J27" s="47"/>
-      <c r="K27" s="59"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="60"/>
-      <c r="N27" s="61"/>
-      <c r="O27" s="75"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="69"/>
     </row>
     <row r="28" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A28" s="71"/>
+      <c r="A28" s="65"/>
       <c r="B28" s="50" t="s">
         <v>19</v>
       </c>
@@ -5689,225 +5997,225 @@
       <c r="H28" s="52"/>
       <c r="I28" s="52"/>
       <c r="J28" s="47"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="62"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="61"/>
-      <c r="O28" s="75"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="90"/>
+      <c r="O28" s="69"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="S28" s="13"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A29" s="71"/>
-      <c r="B29" s="96"/>
-      <c r="C29" s="96"/>
-      <c r="D29" s="96"/>
-      <c r="E29" s="96"/>
-      <c r="F29" s="96"/>
-      <c r="G29" s="96"/>
-      <c r="H29" s="96"/>
-      <c r="I29" s="96"/>
+      <c r="A29" s="65"/>
+      <c r="B29" s="93"/>
+      <c r="C29" s="93"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="93"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
       <c r="J29" s="47"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="64"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="72"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="90"/>
+      <c r="M29" s="90"/>
+      <c r="N29" s="90"/>
+      <c r="O29" s="66"/>
       <c r="P29" s="2"/>
       <c r="Q29" s="2"/>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A30" s="71"/>
-      <c r="B30" s="96"/>
-      <c r="C30" s="96"/>
-      <c r="D30" s="96"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="96"/>
-      <c r="G30" s="96"/>
-      <c r="H30" s="96"/>
-      <c r="I30" s="96"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="93"/>
+      <c r="C30" s="93"/>
+      <c r="D30" s="93"/>
+      <c r="E30" s="93"/>
+      <c r="F30" s="93"/>
+      <c r="G30" s="93"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93"/>
       <c r="J30" s="47"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="64"/>
-      <c r="M30" s="48"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="72"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="90"/>
+      <c r="M30" s="90"/>
+      <c r="N30" s="90"/>
+      <c r="O30" s="66"/>
       <c r="P30" s="2"/>
       <c r="Q30" s="15"/>
     </row>
-    <row r="31" spans="1:19" ht="26.4" x14ac:dyDescent="0.7">
-      <c r="A31" s="71"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A31" s="65"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="93"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93"/>
       <c r="J31" s="47"/>
-      <c r="K31" s="50" t="s">
+      <c r="K31" s="92"/>
+      <c r="L31" s="92"/>
+      <c r="M31" s="92"/>
+      <c r="N31" s="92"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="16"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.7">
+      <c r="A32" s="65"/>
+      <c r="B32" s="93"/>
+      <c r="C32" s="93"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="93"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="90"/>
+      <c r="M32" s="90"/>
+      <c r="N32" s="90"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+    </row>
+    <row r="33" spans="1:27" ht="26.4" x14ac:dyDescent="0.7">
+      <c r="A33" s="65"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="93"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="93"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93"/>
+      <c r="J33" s="47"/>
+      <c r="K33" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.7">
-      <c r="A32" s="71"/>
-      <c r="B32" s="96"/>
-      <c r="C32" s="96"/>
-      <c r="D32" s="96"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="96"/>
-      <c r="G32" s="96"/>
-      <c r="H32" s="96"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="96"/>
-      <c r="L32" s="96"/>
-      <c r="M32" s="96"/>
-      <c r="N32" s="96"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A33" s="71"/>
-      <c r="B33" s="96"/>
-      <c r="C33" s="96"/>
-      <c r="D33" s="96"/>
-      <c r="E33" s="96"/>
-      <c r="F33" s="96"/>
-      <c r="G33" s="96"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="96"/>
-      <c r="L33" s="96"/>
-      <c r="M33" s="96"/>
-      <c r="N33" s="96"/>
-      <c r="O33" s="81"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="75"/>
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A34" s="71"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="96"/>
-      <c r="D34" s="96"/>
-      <c r="E34" s="96"/>
-      <c r="F34" s="96"/>
-      <c r="G34" s="96"/>
-      <c r="H34" s="96"/>
-      <c r="I34" s="96"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="93"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="93"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93"/>
       <c r="J34" s="47"/>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
-      <c r="M34" s="96"/>
-      <c r="N34" s="96"/>
-      <c r="O34" s="81"/>
+      <c r="K34" s="93"/>
+      <c r="L34" s="93"/>
+      <c r="M34" s="93"/>
+      <c r="N34" s="93"/>
+      <c r="O34" s="75"/>
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A35" s="71"/>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="96"/>
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
+      <c r="A35" s="65"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="93"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="93"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93"/>
       <c r="J35" s="47"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="91"/>
-      <c r="O35" s="72"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="90"/>
+      <c r="M35" s="90"/>
+      <c r="N35" s="90"/>
+      <c r="O35" s="66"/>
       <c r="P35" s="2"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A36" s="71"/>
-      <c r="B36" s="96"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96"/>
-      <c r="F36" s="96"/>
-      <c r="G36" s="96"/>
-      <c r="H36" s="96"/>
-      <c r="I36" s="96"/>
+      <c r="A36" s="65"/>
+      <c r="B36" s="93"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="93"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93"/>
       <c r="J36" s="47"/>
-      <c r="K36" s="92"/>
-      <c r="L36" s="92"/>
-      <c r="M36" s="92"/>
-      <c r="N36" s="92"/>
-      <c r="O36" s="72"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="90"/>
+      <c r="M36" s="90"/>
+      <c r="N36" s="90"/>
+      <c r="O36" s="66"/>
       <c r="P36" s="2"/>
       <c r="Q36" s="2"/>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A37" s="71"/>
-      <c r="B37" s="96"/>
-      <c r="C37" s="96"/>
-      <c r="D37" s="96"/>
-      <c r="E37" s="96"/>
-      <c r="F37" s="96"/>
-      <c r="G37" s="96"/>
-      <c r="H37" s="96"/>
-      <c r="I37" s="96"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="93"/>
+      <c r="C37" s="93"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="93"/>
+      <c r="F37" s="93"/>
+      <c r="G37" s="93"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
       <c r="J37" s="47"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="92"/>
-      <c r="O37" s="72"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="90"/>
+      <c r="M37" s="90"/>
+      <c r="N37" s="90"/>
+      <c r="O37" s="66"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.7">
-      <c r="A38" s="71"/>
-      <c r="B38" s="96"/>
-      <c r="C38" s="96"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="96"/>
-      <c r="G38" s="96"/>
-      <c r="H38" s="96"/>
-      <c r="I38" s="96"/>
+      <c r="A38" s="65"/>
+      <c r="B38" s="93"/>
+      <c r="C38" s="93"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="93"/>
+      <c r="F38" s="93"/>
+      <c r="G38" s="93"/>
+      <c r="H38" s="93"/>
+      <c r="I38" s="93"/>
       <c r="J38" s="47"/>
-      <c r="K38" s="92"/>
-      <c r="L38" s="92"/>
-      <c r="M38" s="56"/>
-      <c r="N38" s="92"/>
-      <c r="O38" s="75"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="90"/>
+      <c r="M38" s="90"/>
+      <c r="N38" s="90"/>
+      <c r="O38" s="69"/>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
     <row r="39" spans="1:27" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A39" s="82" t="s">
+      <c r="A39" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="83"/>
-      <c r="C39" s="84"/>
-      <c r="D39" s="84"/>
-      <c r="E39" s="84"/>
-      <c r="F39" s="84"/>
-      <c r="G39" s="84"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93"/>
-      <c r="N39" s="94"/>
-      <c r="O39" s="86"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="78"/>
+      <c r="D39" s="78"/>
+      <c r="E39" s="78"/>
+      <c r="F39" s="78"/>
+      <c r="G39" s="78"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="90"/>
+      <c r="L39" s="90"/>
+      <c r="M39" s="90"/>
+      <c r="N39" s="90"/>
+      <c r="O39" s="80"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11"/>
     </row>
@@ -6012,13 +6320,13 @@
     </row>
     <row r="49" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B49" s="12"/>
-      <c r="C49" s="99"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="99"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="99"/>
-      <c r="I49" s="99"/>
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
       <c r="J49" s="23"/>
       <c r="S49" s="12"/>
       <c r="T49" s="8"/>
@@ -6051,13 +6359,13 @@
     </row>
     <row r="51" spans="2:27" x14ac:dyDescent="0.7">
       <c r="B51" s="26"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="98"/>
-      <c r="G51" s="98"/>
-      <c r="H51" s="98"/>
-      <c r="I51" s="98"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="88"/>
+      <c r="I51" s="88"/>
       <c r="S51" s="12"/>
       <c r="T51" s="27"/>
       <c r="U51" s="27"/>
@@ -6124,13 +6432,13 @@
       <c r="AA54" s="27"/>
     </row>
     <row r="55" spans="2:27" x14ac:dyDescent="0.7">
-      <c r="C55" s="98"/>
-      <c r="D55" s="98"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="98"/>
-      <c r="G55" s="98"/>
-      <c r="H55" s="98"/>
-      <c r="I55" s="98"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="88"/>
+      <c r="E55" s="88"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88"/>
+      <c r="H55" s="88"/>
+      <c r="I55" s="88"/>
       <c r="S55" s="12"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
@@ -6213,30 +6521,11 @@
       <c r="Z62" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="B34:I34"/>
+  <mergeCells count="4">
     <mergeCell ref="B7:N7"/>
     <mergeCell ref="C49:I49"/>
     <mergeCell ref="C51:I51"/>
     <mergeCell ref="C55:I55"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B35:I35"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0"/>
